--- a/workspaces/btc_daily_14days/roc/roc_5.xlsx
+++ b/workspaces/btc_daily_14days/roc/roc_5.xlsx
@@ -575,46 +575,46 @@
         <v>26</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>16.73733091055752</v>
+        <v>16.68330498959986</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>11.28237651787487</v>
+        <v>11.24632665423312</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>10.89017997432953</v>
+        <v>10.85478598268782</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>14.87220660875091</v>
+        <v>14.82425877312262</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>10.48695702814622</v>
+        <v>10.45318833940915</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>3.085467761240359</v>
+        <v>3.075673942264558</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>10.70497260359779</v>
+        <v>10.67096087525096</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>17.94533980940508</v>
+        <v>17.88787863373212</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>14.03473645982667</v>
+        <v>13.99006355912909</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>9.331630134061427</v>
+        <v>9.301782536728396</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>16.83970990972686</v>
+        <v>16.78616404215255</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>16.87858274141979</v>
+        <v>16.82459870121173</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>16.46129732747162</v>
+        <v>16.40859532720169</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>8.999138531573607</v>
+        <v>8.970062967187289</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>38</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>13.29603536399935</v>
+        <v>13.25223212336731</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>11.68737906680227</v>
+        <v>11.64945396185063</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>8.662442243648655</v>
+        <v>8.633659290895153</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>11.42852798065883</v>
+        <v>11.39090683167631</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>10.89238161842154</v>
+        <v>10.85677248497191</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>8.557890663409466</v>
+        <v>8.530323614582294</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.5687025912004131</v>
+        <v>0.5667846616498338</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>5.373429110767447</v>
+        <v>5.35553141301358</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>5.313440288379837</v>
+        <v>5.29613682418033</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-8.724480621557369</v>
+        <v>-8.696671162527238</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>1.620486495637373</v>
+        <v>1.615088961114026</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>1.655651384878574</v>
+        <v>1.649820670344056</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-4.04421338368887</v>
+        <v>-4.031734920553163</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-11.71486088852304</v>
+        <v>-11.67771031216024</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>38</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-5.125017267577199</v>
+        <v>-5.109784348727693</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>1.158486483182216</v>
+        <v>1.154059702130958</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>6.029631025455835</v>
+        <v>6.008857833058549</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>6.161584832829313</v>
+        <v>6.140366447246393</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>2.989950521690929</v>
+        <v>2.979347715768576</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>8.558092367050499</v>
+        <v>8.530000888757108</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>8.475316172441815</v>
+        <v>8.447665308091672</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.1012279712508501</v>
+        <v>0.1001248709447538</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.03993770590351176</v>
+        <v>0.0394443592791589</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.8123071905780321</v>
+        <v>-0.8096839154771232</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-11.57030633624186</v>
+        <v>-11.53293634721778</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-11.53843334502025</v>
+        <v>-11.50149406776079</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-11.96292521433006</v>
+        <v>-11.9244738469465</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-6.435250119739209</v>
+        <v>-6.414552417423401</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>43</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>3.320515168162117</v>
+        <v>3.308313653037672</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-2.942910234847389</v>
+        <v>-2.93395324332365</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-12.6455933102953</v>
+        <v>-12.6054376960749</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-12.51832778559229</v>
+        <v>-12.47861107518971</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-8.4046100150535</v>
+        <v>-8.377995115718697</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-8.109013576317523</v>
+        <v>-8.082923359506744</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-8.195968092010084</v>
+        <v>-8.169414514755921</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-17.98460959204158</v>
+        <v>-17.92631756037893</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-13.38990041334791</v>
+        <v>-13.34628258118256</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-9.583824735351584</v>
+        <v>-9.552330544565457</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-5.12866708050516</v>
+        <v>-5.111694953803131</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-12.09140595659018</v>
+        <v>-12.05189383995334</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-7.850814182742681</v>
+        <v>-7.825085302761181</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-9.935545476226189</v>
+        <v>-9.902924510448912</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>62</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-12.17085767504832</v>
+        <v>-12.13168391729154</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-13.78592268977138</v>
+        <v>-13.7405344669197</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-12.57070263937194</v>
+        <v>-12.52971448066739</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-5.986912590029029</v>
+        <v>-5.967924542772259</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-11.3711180648399</v>
+        <v>-11.33388463685946</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-9.461357672612287</v>
+        <v>-9.430050524861336</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-11.16411151781093</v>
+        <v>-11.12693560675879</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-14.86657376051406</v>
+        <v>-14.81711710818153</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-13.31545233860834</v>
+        <v>-13.27090715152566</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-17.40443372523593</v>
+        <v>-17.34598836451408</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-12.76302302673965</v>
+        <v>-12.72011285110401</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-19.20165986454897</v>
+        <v>-19.13735132350977</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-18.0102863450879</v>
+        <v>-17.9499554957846</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-17.76450538109267</v>
+        <v>-17.70487499806976</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>81</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-3.110722270827537</v>
+        <v>-3.100961180321548</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-2.253758747502815</v>
+        <v>-2.245976087153799</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.1789372431990444</v>
+        <v>-0.1786495678325437</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-3.755134241742375</v>
+        <v>-3.743041272558976</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.6482263527348522</v>
+        <v>0.6458879146362477</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-2.762465632834477</v>
+        <v>-2.752817812399798</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-1.611694779091884</v>
+        <v>-1.605684379922167</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.84342793159351</v>
+        <v>-0.8399148016751994</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.3322180314792931</v>
+        <v>0.3319153546247904</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-6.707670717558969</v>
+        <v>-6.683493902331286</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-5.676784204122043</v>
+        <v>-5.656418587892482</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-5.644088768046331</v>
+        <v>-5.623579991790997</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-3.590262255464829</v>
+        <v>-3.576819975042859</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-4.579626101752901</v>
+        <v>-4.562700565572754</v>
       </c>
     </row>
     <row r="12">
@@ -887,46 +887,46 @@
         <v>95</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.914490951789162</v>
+        <v>-0.9119449877205312</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-4.632594364323495</v>
+        <v>-4.616128022543109</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.2371388702507886</v>
+        <v>0.2359857393215918</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-2.792826628658773</v>
+        <v>-2.783525172353507</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-3.332629424528946</v>
+        <v>-3.321163194706457</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-3.035913359574558</v>
+        <v>-3.024853106539055</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-1.013069501339743</v>
+        <v>-1.008867195302365</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.6277376418284533</v>
+        <v>0.6262744766162172</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.4882515291257477</v>
+        <v>-0.4857005267221339</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-1.341350245895114</v>
+        <v>-1.334787586799038</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-3.657801755538742</v>
+        <v>-3.64352982669142</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-3.624641933404597</v>
+        <v>-3.610221692839325</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-4.047164551128382</v>
+        <v>-4.031488989932932</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-2.741643636571148</v>
+        <v>-2.730341891108814</v>
       </c>
     </row>
     <row r="13">
@@ -939,46 +939,46 @@
         <v>124</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>5.571077808822466</v>
+        <v>5.550326185198529</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>7.187254702468621</v>
+        <v>7.16198198749769</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1.145974473348346</v>
+        <v>1.14146462516991</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>4.505153093360022</v>
+        <v>4.488630706145223</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>7.196698002050127</v>
+        <v>7.170787277153948</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1.84327911507836</v>
+        <v>1.837369324510234</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.9510411814242943</v>
+        <v>0.9483969968213444</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>1.291216748100069</v>
+        <v>1.287265220839423</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>2.846748280971411</v>
+        <v>2.837394880592178</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>1.185922360625185</v>
+        <v>1.183745848220845</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.6364839726015248</v>
+        <v>-0.632268115731911</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.6025559006426917</v>
+        <v>-0.5981854753043621</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-1.024373692090187</v>
+        <v>-1.018674023319441</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.8444898115371728</v>
+        <v>0.8435120987046147</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>169</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>3.71957943126931</v>
+        <v>3.704078611260194</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-4.402142383847163</v>
+        <v>-4.385600371253155</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-1.246086025644942</v>
+        <v>-1.24190486361649</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>1.845199982131405</v>
+        <v>1.837357784931804</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>3.676377172308001</v>
+        <v>3.661608399656643</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>6.345176360721005</v>
+        <v>6.321678644633003</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>2.705506585185447</v>
+        <v>2.69597892237492</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>2.831097778888939</v>
+        <v>2.820965209337565</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>2.177611627479116</v>
+        <v>2.169997348577866</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>3.104624718259075</v>
+        <v>3.094981524949226</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>3.493445669117506</v>
+        <v>3.482351006640513</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>2.341300159758518</v>
+        <v>2.334873855919582</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>1.326414679167186</v>
+        <v>1.323681701739901</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>3.953335049904297</v>
+        <v>3.94047716837408</v>
       </c>
     </row>
     <row r="15">
@@ -1040,49 +1040,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>4.412639027856322</v>
+        <v>4.421786683545292</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>4.459845237259429</v>
+        <v>4.467721407959409</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>2.15501029900868</v>
+        <v>2.1591341097213</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-1.032793093737439</v>
+        <v>-1.034096131871145</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-2.675336854183328</v>
+        <v>-2.67950243152417</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.7192731718459981</v>
+        <v>-0.72031370680088</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.303726123231705</v>
+        <v>0.304154119535049</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>2.052220118076256</v>
+        <v>2.055936705585815</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>1.43851520464915</v>
+        <v>1.441025566406438</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>1.146393583556886</v>
+        <v>1.147695076358211</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.273701630131356</v>
+        <v>-1.276822802523554</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.4229943885982621</v>
+        <v>0.4227350286556373</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.00361027172844075</v>
+        <v>0.002568627661105438</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.2523810850860926</v>
+        <v>0.2521142492420623</v>
       </c>
     </row>
     <row r="16">
@@ -1092,49 +1092,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.9896789217137325</v>
+        <v>-0.9908892735698203</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.03035902314420724</v>
+        <v>0.03117031667859749</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>4.148200570152945</v>
+        <v>4.184639073787196</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>4.105852537928264</v>
+        <v>4.142512426755424</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>2.270452763991358</v>
+        <v>2.29176284148194</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>4.652153707705779</v>
+        <v>4.69201753426001</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>3.443245412975514</v>
+        <v>3.471518512499628</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.4063216924169097</v>
+        <v>-0.4090151808947766</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>1.792640137934335</v>
+        <v>1.80764641047562</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>2.461453272228233</v>
+        <v>2.478682371593742</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>3.013821592329599</v>
+        <v>3.034647125455919</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.03459849156315897</v>
+        <v>0.03011006591614063</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.3819558405434265</v>
+        <v>-0.3901753347262655</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>4.011607885337199</v>
+        <v>4.041721346833867</v>
       </c>
     </row>
     <row r="17">
@@ -1147,46 +1147,46 @@
         <v>329</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.09014830592984424</v>
+        <v>0.08701713730498994</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>2.126822156926856</v>
+        <v>2.119342701640512</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>2.036070265337571</v>
+        <v>2.027101785015375</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>2.774531675310804</v>
+        <v>2.762813318757814</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.019579818586571</v>
+        <v>1.014387996779995</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>2.53341295838473</v>
+        <v>2.522949557957801</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>3.362092739771697</v>
+        <v>3.349843760637185</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>2.895527562133807</v>
+        <v>2.885506912613444</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1.313662110906044</v>
+        <v>1.308641257579836</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-1.669909021770664</v>
+        <v>-1.663510232706109</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.876028540001542</v>
+        <v>-1.868646924911303</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-3.671769382021296</v>
+        <v>-3.65719340707178</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-2.875646327748726</v>
+        <v>-2.863536068022455</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-4.149293581314915</v>
+        <v>-4.134917159065864</v>
       </c>
     </row>
     <row r="18">
@@ -1196,49 +1196,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-1.434614790798264</v>
+        <v>-1.434006557936996</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-2.449115146373416</v>
+        <v>-2.446499310901565</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-2.373839736433247</v>
+        <v>-2.372044550888646</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.361944252661111</v>
+        <v>-0.3628687837263129</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.2783257142888402</v>
+        <v>0.2771085680904335</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.3666523511042996</v>
+        <v>-0.3673539636466288</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.2151189211039579</v>
+        <v>-0.2157132718654324</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.02550411948219278</v>
+        <v>0.02494761792441125</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.4360637806442824</v>
+        <v>0.4350869337693695</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.7657968666497297</v>
+        <v>0.7654011645278018</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>1.268693166362951</v>
+        <v>1.267819567299995</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.3594811219061143</v>
+        <v>0.3604692941713949</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.1745870761161825</v>
+        <v>0.1757805873676119</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.464304896031756</v>
+        <v>-1.461722228745359</v>
       </c>
     </row>
     <row r="19">
@@ -1248,49 +1248,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-2.369981530086484</v>
+        <v>-2.377103707313232</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.7098028816405844</v>
+        <v>0.7128898531159891</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.796415656525475</v>
+        <v>1.807935139955013</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.19827372740464</v>
+        <v>0.2050546444935506</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>2.128988314801546</v>
+        <v>2.143141492882272</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>2.920257413011029</v>
+        <v>2.938839157765315</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>2.474812264883475</v>
+        <v>2.49010967832951</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>2.504947789447556</v>
+        <v>2.519087052302964</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1.951329501042011</v>
+        <v>1.962829176898673</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>2.093264251635041</v>
+        <v>2.101273146551932</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.4047737825714037</v>
+        <v>0.4046398097166417</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.076707270386564</v>
+        <v>1.07563814594932</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.904869483476709</v>
+        <v>0.9029397768951313</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>2.038309512426437</v>
+        <v>2.043159025361405</v>
       </c>
     </row>
     <row r="20">
@@ -1300,49 +1300,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-3.078233641847369</v>
+        <v>-3.078792989112571</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-1.181035324987093</v>
+        <v>-1.181272570699043</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-2.453097014039827</v>
+        <v>-2.453369815050529</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-2.615241542251034</v>
+        <v>-2.615470232250033</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.062711511682636</v>
+        <v>0.06306489067831222</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.8094371938765619</v>
+        <v>-0.8091951794066148</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.5678173929447397</v>
+        <v>0.5682705652149806</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.7762879940611853</v>
+        <v>-0.7762005765671987</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-2.008455810125163</v>
+        <v>-2.008666502443646</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-1.984124877663483</v>
+        <v>-1.984559625764724</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-1.731001039531513</v>
+        <v>-1.731474796661374</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.9411028788118472</v>
+        <v>0.9410125219815413</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.8138616474518656</v>
+        <v>0.8137321154017556</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.1093739455675689</v>
+        <v>-0.1095670801811295</v>
       </c>
     </row>
     <row r="21">
@@ -1352,49 +1352,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.2546323500607244</v>
+        <v>-0.2550498688871272</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-2.985608948099561</v>
+        <v>-2.989558879245905</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-2.261074669621607</v>
+        <v>-2.262767587902481</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-5.115896163879782</v>
+        <v>-5.120660193284863</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-3.042377080444489</v>
+        <v>-3.043773674573544</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-5.730009769594503</v>
+        <v>-5.734477474847729</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-4.69534050179211</v>
+        <v>-4.698741567004035</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-4.215161861749493</v>
+        <v>-4.21886365929366</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.9510881843554984</v>
+        <v>0.9533135599114431</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>1.228137499384886</v>
+        <v>1.229091849579724</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.8439648749459252</v>
+        <v>-0.8462092060014399</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1.060166801003049</v>
+        <v>1.05967577397584</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>2.884604175774015</v>
+        <v>2.886288048051924</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.8889331785657859</v>
+        <v>0.8888183690922489</v>
       </c>
     </row>
     <row r="22">
@@ -1404,49 +1404,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.318220872615079</v>
+        <v>1.321102312512487</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>2.845660712565632</v>
+        <v>2.850579016613992</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-2.481943420039833</v>
+        <v>-2.48655152779564</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-5.042273247073531</v>
+        <v>-5.053524496669517</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-7.37441643523993</v>
+        <v>-7.388464026635241</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-6.180113510977179</v>
+        <v>-6.191946721759152</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-6.713277721523049</v>
+        <v>-6.726422175040071</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-4.489878160663295</v>
+        <v>-4.499440258766569</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-6.349805553460286</v>
+        <v>-6.362491110372872</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-4.963238923274616</v>
+        <v>-4.976235332979414</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-3.822490474115675</v>
+        <v>-3.83523064763186</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-4.687125509206538</v>
+        <v>-4.702494170078623</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-4.847422374520569</v>
+        <v>-4.862471947899081</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-6.845630437133764</v>
+        <v>-6.865002867875006</v>
       </c>
     </row>
     <row r="23">
@@ -1459,46 +1459,46 @@
         <v>190</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-4.072385688630966</v>
+        <v>-4.062448675458178</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-7.78922245949002</v>
+        <v>-7.768663306461875</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-8.710406955560323</v>
+        <v>-8.689035552734651</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-8.053838033479174</v>
+        <v>-8.032261895531569</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-5.434364511709205</v>
+        <v>-5.421729812223916</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-5.663238363467194</v>
+        <v>-5.649791414184413</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-7.853235238634248</v>
+        <v>-7.833996827863224</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-4.109892321626241</v>
+        <v>-4.098931632843758</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-6.283975774462185</v>
+        <v>-6.268334956944464</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-4.509756960364605</v>
+        <v>-4.494701603362849</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-5.772854833920384</v>
+        <v>-5.752086506627641</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-4.156573727027293</v>
+        <v>-4.138755980861312</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-5.104723595702708</v>
+        <v>-5.085326381279806</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-4.327107005695908</v>
+        <v>-4.309289259529926</v>
       </c>
     </row>
     <row r="24">
@@ -1508,49 +1508,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.5453863721580348</v>
+        <v>-0.5522304370360303</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.4404426122803073</v>
+        <v>0.430917617846525</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.902478042368188</v>
+        <v>-1.92106231084459</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-2.421575559111382</v>
+        <v>-2.446505774134401</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-3.60934742353416</v>
+        <v>-3.631268679856412</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-7.20800938192243</v>
+        <v>-7.248672846679817</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-7.292743099194666</v>
+        <v>-7.337148526051003</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-3.863822601872279</v>
+        <v>-3.889485820293466</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-3.282808660369362</v>
+        <v>-3.306257717849235</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.5010883401507371</v>
+        <v>-0.5180934162282469</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-1.997855945373473</v>
+        <v>-2.03003628302956</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.01176435421762534</v>
+        <v>-0.03486881195856739</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.4307746913032062</v>
+        <v>-0.4551234229035401</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>1.118426565034206</v>
+        <v>1.101787451856438</v>
       </c>
     </row>
     <row r="25">
@@ -1560,49 +1560,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-6.547492374264081</v>
+        <v>-6.61757235103147</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-4.555462383624686</v>
+        <v>-4.622472699468538</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-5.85123199112217</v>
+        <v>-5.929259969616723</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-8.423681561217322</v>
+        <v>-8.534762527663773</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-5.358499172685995</v>
+        <v>-5.424095661299603</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-7.763759937673036</v>
+        <v>-7.860995587008198</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.542187348638954</v>
+        <v>-1.590575904025982</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-7.414776152825965</v>
+        <v>-7.505235621201457</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-9.657864669694952</v>
+        <v>-9.768978332210459</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-6.88614370951224</v>
+        <v>-6.982739880874796</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-3.464841071325253</v>
+        <v>-3.551129568828699</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-6.135967161545189</v>
+        <v>-6.244019138756038</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-5.652514326726475</v>
+        <v>-5.755182840609933</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-7.210207885977297</v>
+        <v>-7.323643326515509</v>
       </c>
     </row>
     <row r="26">
@@ -2213,10 +2213,8 @@
           <t>X &gt; -0.1568</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>4089~4102</t>
-        </is>
+      <c r="B6" t="n">
+        <v>4089</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>-0.2018732300100794</v>
@@ -2267,10 +2265,8 @@
           <t>X &gt; -0.1446</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>4063~4076</t>
-        </is>
+      <c r="B7" t="n">
+        <v>4063</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>-0.3099250719273456</v>
@@ -2321,10 +2317,8 @@
           <t>X &gt; -0.1324</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>4025~4038</t>
-        </is>
+      <c r="B8" t="n">
+        <v>4025</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>-0.4379653137711372</v>
@@ -2375,10 +2369,8 @@
           <t>X &gt; -0.1202</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>3987~4000</t>
-        </is>
+      <c r="B9" t="n">
+        <v>3987</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>-0.3934383202099738</v>
@@ -2429,10 +2421,8 @@
           <t>X &gt; -0.108</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>3944~3957</t>
-        </is>
+      <c r="B10" t="n">
+        <v>3944</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>-0.4337971779304723</v>
@@ -2483,10 +2473,8 @@
           <t>X &gt; -0.09577</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>3882~3895</t>
-        </is>
+      <c r="B11" t="n">
+        <v>3882</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>-0.2469684870905979</v>
@@ -2537,10 +2525,8 @@
           <t>X &gt; -0.08357</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>3801~3814</t>
-        </is>
+      <c r="B12" t="n">
+        <v>3801</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>-0.1861493847091893</v>
@@ -2591,10 +2577,8 @@
           <t>X &gt; -0.07136</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>3706~3719</t>
-        </is>
+      <c r="B13" t="n">
+        <v>3706</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>-0.1675442626676187</v>
@@ -2645,10 +2629,8 @@
           <t>X &gt; -0.05916</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>3582~3595</t>
-        </is>
+      <c r="B14" t="n">
+        <v>3582</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>-0.3654828264686714</v>
@@ -2699,10 +2681,8 @@
           <t>X &gt; -0.04695</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>3413~3426</t>
-        </is>
+      <c r="B15" t="n">
+        <v>3413</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>-0.5669934865847566</v>
@@ -2753,10 +2733,8 @@
           <t>X &gt; -0.03475</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>3233~3245</t>
-        </is>
+      <c r="B16" t="n">
+        <v>3233</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>-0.8447480274518853</v>
@@ -2807,10 +2785,8 @@
           <t>X &gt; -0.02254</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2970~2979</t>
-        </is>
+      <c r="B17" t="n">
+        <v>2970</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>-0.8318069002703936</v>
@@ -2861,10 +2837,8 @@
           <t>X &gt; -0.01034</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2641~2650</t>
-        </is>
+      <c r="B18" t="n">
+        <v>2641</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>-0.9462685088892187</v>
@@ -2915,10 +2889,8 @@
           <t>X &gt; 0.001869</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2217~2225</t>
-        </is>
+      <c r="B19" t="n">
+        <v>2217</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>-0.8529888820077218</v>
@@ -2969,10 +2941,8 @@
           <t>X &gt; 0.01407</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1815~1820</t>
-        </is>
+      <c r="B20" t="n">
+        <v>1815</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>-0.51541634218799</v>
@@ -3023,10 +2993,8 @@
           <t>X &gt; 0.02628</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1474~1478</t>
-        </is>
+      <c r="B21" t="n">
+        <v>1474</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>0.07760362836918233</v>
@@ -3077,10 +3045,8 @@
           <t>X &gt; 0.03848</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>1207~1210</t>
-        </is>
+      <c r="B22" t="n">
+        <v>1207</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>0.1511897789635768</v>
@@ -3131,10 +3097,8 @@
           <t>X &gt; 0.05069</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>985~987</t>
-        </is>
+      <c r="B23" t="n">
+        <v>985</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>-0.1124859392575885</v>
@@ -3185,10 +3149,8 @@
           <t>X &gt; 0.06289</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>795~797</t>
-        </is>
+      <c r="B24" t="n">
+        <v>795</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>0.8315303121614193</v>
@@ -3239,10 +3201,8 @@
           <t>X &gt; 0.0751</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>642~643</t>
-        </is>
+      <c r="B25" t="n">
+        <v>642</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>1.161305070147719</v>
@@ -3293,10 +3253,8 @@
           <t>X &gt; 0.0873</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>532~532</t>
-        </is>
+      <c r="B26" t="n">
+        <v>532</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>2.769719574526874</v>
@@ -3347,10 +3305,8 @@
           <t>X &gt; 0.09951</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>429~429</t>
-        </is>
+      <c r="B27" t="n">
+        <v>429</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>1.818915992144341</v>
@@ -3401,10 +3357,8 @@
           <t>X &gt; 0.1117</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>343~343</t>
-        </is>
+      <c r="B28" t="n">
+        <v>343</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>2.900147685620936</v>
@@ -3455,10 +3409,8 @@
           <t>X &gt; 0.1239</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>287~287</t>
-        </is>
+      <c r="B29" t="n">
+        <v>287</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>3.952554711148913</v>
@@ -3509,10 +3461,8 @@
           <t>X &gt; 0.1361</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>241~241</t>
-        </is>
+      <c r="B30" t="n">
+        <v>241</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>4.767972468171763</v>
@@ -3563,10 +3513,8 @@
           <t>X &gt; 0.1483</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>208~208</t>
-        </is>
+      <c r="B31" t="n">
+        <v>208</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>4.237330910559251</v>
@@ -3617,10 +3565,8 @@
           <t>X &gt; 0.1605</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>173~173</t>
-        </is>
+      <c r="B32" t="n">
+        <v>173</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>3.575925841639737</v>
@@ -3671,10 +3617,8 @@
           <t>X &gt; 0.1727</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>134~134</t>
-        </is>
+      <c r="B33" t="n">
+        <v>134</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>5.715516903670625</v>
@@ -3725,10 +3669,8 @@
           <t>X &gt; 0.1849</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>109~109</t>
-        </is>
+      <c r="B34" t="n">
+        <v>109</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>-0.1998603385586009</v>
@@ -3779,10 +3721,8 @@
           <t>X &gt; 0.1971</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B35" t="n">
+        <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>-6.064866891638545</v>
@@ -3967,10 +3907,8 @@
           <t>X &lt; -0.1568</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B6" t="n">
+        <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>9.41132358455193</v>
@@ -4021,10 +3959,8 @@
           <t>X &lt; -0.1446</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>110~110</t>
-        </is>
+      <c r="B7" t="n">
+        <v>110</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>11.14292531615366</v>
@@ -4075,10 +4011,8 @@
           <t>X &lt; -0.1324</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>148~148</t>
-        </is>
+      <c r="B8" t="n">
+        <v>148</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>11.69575086897922</v>
@@ -4129,10 +4063,8 @@
           <t>X &lt; -0.1202</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>186~186</t>
-        </is>
+      <c r="B9" t="n">
+        <v>186</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>8.25924985183304</v>
@@ -4183,10 +4115,8 @@
           <t>X &lt; -0.108</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>229~229</t>
-        </is>
+      <c r="B10" t="n">
+        <v>229</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>7.331889190707052</v>
@@ -4237,10 +4167,8 @@
           <t>X &lt; -0.09577</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>291~291</t>
-        </is>
+      <c r="B11" t="n">
+        <v>291</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>3.176664772573531</v>
@@ -4291,10 +4219,8 @@
           <t>X &lt; -0.08357</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>372~372</t>
-        </is>
+      <c r="B12" t="n">
+        <v>372</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>1.807636948607225</v>
@@ -4345,10 +4271,8 @@
           <t>X &lt; -0.07136</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>467~467</t>
-        </is>
+      <c r="B13" t="n">
+        <v>467</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>1.253885020261109</v>
@@ -4399,10 +4323,8 @@
           <t>X &lt; -0.05916</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>591~591</t>
-        </is>
+      <c r="B14" t="n">
+        <v>591</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>2.159691967438079</v>
@@ -4453,10 +4375,8 @@
           <t>X &lt; -0.04695</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>760~760</t>
-        </is>
+      <c r="B15" t="n">
+        <v>760</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>2.506561679790032</v>
@@ -4507,10 +4427,8 @@
           <t>X &lt; -0.03475</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>940~941</t>
-        </is>
+      <c r="B16" t="n">
+        <v>940</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>2.87319292314816</v>
@@ -4561,10 +4479,8 @@
           <t>X &lt; -0.02254</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1203~1207</t>
-        </is>
+      <c r="B17" t="n">
+        <v>1203</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>2.021888937453653</v>
@@ -4615,10 +4531,8 @@
           <t>X &lt; -0.01034</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1532~1536</t>
-        </is>
+      <c r="B18" t="n">
+        <v>1532</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>1.608124179790025</v>
@@ -4669,10 +4583,8 @@
           <t>X &lt; 0.001869</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1956~1961</t>
-        </is>
+      <c r="B19" t="n">
+        <v>1956</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>0.9486830464396903</v>
@@ -4723,10 +4635,8 @@
           <t>X &lt; 0.01407</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2358~2366</t>
-        </is>
+      <c r="B20" t="n">
+        <v>2358</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>0.3806107076852143</v>
@@ -4777,10 +4687,8 @@
           <t>X &lt; 0.02628</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2699~2708</t>
-        </is>
+      <c r="B21" t="n">
+        <v>2699</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>-0.05621527737392995</v>
@@ -4831,10 +4739,8 @@
           <t>X &lt; 0.03848</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2966~2976</t>
-        </is>
+      <c r="B22" t="n">
+        <v>2966</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>-0.07408348150030264</v>
@@ -4885,10 +4791,8 @@
           <t>X &lt; 0.05069</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>3188~3199</t>
-        </is>
+      <c r="B23" t="n">
+        <v>3188</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>0.0229730583458192</v>
@@ -4939,10 +4843,8 @@
           <t>X &lt; 0.06289</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>3378~3389</t>
-        </is>
+      <c r="B24" t="n">
+        <v>3378</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>-0.2066280516941958</v>
@@ -4993,10 +4895,8 @@
           <t>X &lt; 0.0751</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>3531~3543</t>
-        </is>
+      <c r="B25" t="n">
+        <v>3531</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>-0.2213525172181576</v>
@@ -5047,10 +4947,8 @@
           <t>X &lt; 0.0873</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>3641~3654</t>
-        </is>
+      <c r="B26" t="n">
+        <v>3641</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>-0.4135258954699594</v>
@@ -5101,10 +4999,8 @@
           <t>X &lt; 0.09951</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>3744~3757</t>
-        </is>
+      <c r="B27" t="n">
+        <v>3744</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>-0.2176863904788036</v>
@@ -5155,10 +5051,8 @@
           <t>X &lt; 0.1117</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>3830~3843</t>
-        </is>
+      <c r="B28" t="n">
+        <v>3830</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>-0.268613964238078</v>
@@ -5209,10 +5103,8 @@
           <t>X &lt; 0.1239</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>3886~3899</t>
-        </is>
+      <c r="B29" t="n">
+        <v>3886</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>-0.30056835355186</v>
@@ -5263,10 +5155,8 @@
           <t>X &lt; 0.1361</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>3932~3945</t>
-        </is>
+      <c r="B30" t="n">
+        <v>3932</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>-0.300789397523026</v>
@@ -5317,10 +5207,8 @@
           <t>X &lt; 0.1483</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>3965~3978</t>
-        </is>
+      <c r="B31" t="n">
+        <v>3965</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>-0.2309948812959419</v>
@@ -5371,10 +5259,8 @@
           <t>X &lt; 0.1605</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>4000~4013</t>
-        </is>
+      <c r="B32" t="n">
+        <v>4000</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>-0.1635105853482699</v>
@@ -5425,10 +5311,8 @@
           <t>X &lt; 0.1727</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>4039~4052</t>
-        </is>
+      <c r="B33" t="n">
+        <v>4039</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>-0.1982754376828311</v>
@@ -5479,10 +5363,8 @@
           <t>X &lt; 0.1849</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>4064~4077</t>
-        </is>
+      <c r="B34" t="n">
+        <v>4064</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>-0.003862651826359809</v>
@@ -5533,10 +5415,8 @@
           <t>X &lt; 0.1971</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>4089~4102</t>
-        </is>
+      <c r="B35" t="n">
+        <v>4089</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>0.1150453462941741</v>

--- a/workspaces/btc_daily_14days/roc/roc_5.xlsx
+++ b/workspaces/btc_daily_14days/roc/roc_5.xlsx
@@ -479,7 +479,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that ROC-5 is approximately at value x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that ROC-5 is approximately at value x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -575,46 +575,46 @@
         <v>26</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>16.68330498959986</v>
+        <v>16.695799892627</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>11.24632665423312</v>
+        <v>11.2592058107804</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>10.85478598268782</v>
+        <v>10.86776472661573</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>14.82425877312262</v>
+        <v>14.83721451529629</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>10.45318833940915</v>
+        <v>10.46627533834094</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>3.075673942264558</v>
+        <v>3.088692130534987</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>10.67096087525096</v>
+        <v>10.68400865579012</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>17.88787863373212</v>
+        <v>17.90104633098604</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>13.99006355912909</v>
+        <v>14.00324994115014</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>9.301782536728396</v>
+        <v>9.315176460798739</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>16.78616404215255</v>
+        <v>16.79961422241087</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>16.82459870121173</v>
+        <v>16.8380462773658</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>16.40859532720169</v>
+        <v>16.42214896725419</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>8.970062967187289</v>
+        <v>8.959633331492633</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>38</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>13.25223212336731</v>
+        <v>13.26472406144678</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>11.64945396185063</v>
+        <v>11.6623330612419</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>8.633659290895153</v>
+        <v>8.646636199115704</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>11.39090683167631</v>
+        <v>11.40386023459686</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>10.85677248497191</v>
+        <v>10.86985942209488</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>8.530323614582294</v>
+        <v>8.543344122151943</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.5667846616498338</v>
+        <v>0.5798278640555594</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>5.35553141301358</v>
+        <v>5.368694370179298</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>5.29613682418033</v>
+        <v>5.309320398569866</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-8.696671162527238</v>
+        <v>-8.683281818520697</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>1.615088961114026</v>
+        <v>1.628536270582877</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>1.649820670344056</v>
+        <v>1.663266332442696</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-4.031734920553163</v>
+        <v>-4.018182563808558</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-11.67771031216024</v>
+        <v>-11.6881399478596</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>38</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-5.109784348727693</v>
+        <v>-5.097307742538931</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>1.154059702130958</v>
+        <v>1.16693048764806</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>6.008857833058549</v>
+        <v>6.021832472099398</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>6.140366447246393</v>
+        <v>6.153316204915775</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>2.979347715768576</v>
+        <v>2.992429867811353</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>8.530000888757108</v>
+        <v>8.543021051280029</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>8.447665308091672</v>
+        <v>8.460711540350957</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.1001248709447538</v>
+        <v>0.1132855438570886</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.0394443592791589</v>
+        <v>0.05262602584679854</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.8096839154771232</v>
+        <v>-0.796292930681112</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-11.53293634721778</v>
+        <v>-11.51949170079848</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-11.50149406776079</v>
+        <v>-11.48805018100419</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-11.9244738469465</v>
+        <v>-11.91092206135499</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-6.414552417423401</v>
+        <v>-6.424982053122754</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>43</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>3.308313653037672</v>
+        <v>3.320796255709546</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-2.93395324332365</v>
+        <v>-2.921086378760194</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-12.6054376960749</v>
+        <v>-12.5924767544625</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-12.47861107518971</v>
+        <v>-12.46567377094773</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-8.377995115718697</v>
+        <v>-8.364920067104251</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-8.082923359506744</v>
+        <v>-8.069912097571191</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-8.169414514755921</v>
+        <v>-8.156376078245586</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-17.92631756037893</v>
+        <v>-17.91316424266664</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-13.34628258118256</v>
+        <v>-13.33310555985613</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-9.552330544565457</v>
+        <v>-9.538942099381586</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-5.111694953803131</v>
+        <v>-5.098249374564446</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-12.05189383995334</v>
+        <v>-12.03845022590698</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-7.825085302761181</v>
+        <v>-7.811533356621091</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-9.902924510448912</v>
+        <v>-9.913354146147064</v>
       </c>
     </row>
     <row r="10">
@@ -783,150 +783,150 @@
         <v>62</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-12.13168391729154</v>
+        <v>-12.11921557088648</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-13.7405344669197</v>
+        <v>-13.72767739389591</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-12.52971448066739</v>
+        <v>-12.51675496545323</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-5.967924542772259</v>
+        <v>-5.954984271124829</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-11.33388463685946</v>
+        <v>-11.32081244169935</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-9.430050524861336</v>
+        <v>-9.417040941677527</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-11.12693560675879</v>
+        <v>-11.11389939147742</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-14.81711710818153</v>
+        <v>-14.80396348955512</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-13.27090715152566</v>
+        <v>-13.25773080844518</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-17.34598836451408</v>
+        <v>-17.33260250341218</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-12.72011285110401</v>
+        <v>-12.70666912871604</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-19.13735132350977</v>
+        <v>-19.12390892585186</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-17.9499554957846</v>
+        <v>-17.93640434578427</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-17.70487499806976</v>
+        <v>-17.71530463376718</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.08967</t>
+          <t>X ≈ -0.08966</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>81</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-3.100961180321548</v>
+        <v>-3.088487146161903</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-2.245976087153799</v>
+        <v>-2.233111889982268</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.1786495678325437</v>
+        <v>-0.1656828064190137</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-3.743041272558976</v>
+        <v>-3.730101067701455</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.6458879146362477</v>
+        <v>0.6589658497053605</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-2.752817812399798</v>
+        <v>-2.739805981175884</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-1.605684379922167</v>
+        <v>-1.59264488665611</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.8399148016751994</v>
+        <v>-0.8267566431760969</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.3319153546247904</v>
+        <v>0.3450953873726732</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-6.683493902331286</v>
+        <v>-6.670105994710354</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-5.656418587892482</v>
+        <v>-5.642974008240564</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-5.623579991790997</v>
+        <v>-5.610136194554137</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-3.576819975042859</v>
+        <v>-3.563268060741834</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-4.562700565572754</v>
+        <v>-4.573130201271461</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.07747</t>
+          <t>X ≈ -0.07746</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>95</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.9119449877205312</v>
+        <v>-0.8994712970666114</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-4.616128022543109</v>
+        <v>-4.603268139298159</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.2359857393215918</v>
+        <v>0.2489509176319729</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-2.783525172353507</v>
+        <v>-2.77058623348789</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-3.321163194706457</v>
+        <v>-3.308089388290448</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-3.024853106539055</v>
+        <v>-3.011842981003646</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-1.008867195302365</v>
+        <v>-0.9958287080539208</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.6262744766162172</v>
+        <v>0.6394321705346471</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.4857005267221339</v>
+        <v>-0.472521676587462</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-1.334787586799038</v>
+        <v>-1.321399035411865</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-3.64352982669142</v>
+        <v>-3.630085471146472</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-3.610221692839325</v>
+        <v>-3.596778045993787</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-4.031488989932932</v>
+        <v>-4.01793731808953</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-2.730341891108814</v>
+        <v>-2.74077152680649</v>
       </c>
     </row>
     <row r="13">
@@ -939,46 +939,46 @@
         <v>124</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>5.550326185198529</v>
+        <v>5.562803394872041</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>7.16198198749769</v>
+        <v>7.174849546541743</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1.14146462516991</v>
+        <v>1.154428037360738</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>4.488630706145223</v>
+        <v>4.501572723196411</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>7.170787277153948</v>
+        <v>7.183866031732137</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1.837369324510234</v>
+        <v>1.850380359626044</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.9483969968213444</v>
+        <v>0.9614348171015692</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>1.287265220839423</v>
+        <v>1.300421812057571</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>2.837394880592178</v>
+        <v>2.850573792868481</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>1.183745848220845</v>
+        <v>1.197134137208387</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.632268115731911</v>
+        <v>-0.6188239031954126</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.5981854753043621</v>
+        <v>-0.5847419250960755</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-1.018674023319441</v>
+        <v>-1.005122404667873</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.8435120987046147</v>
+        <v>0.8330824630064626</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>169</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>3.704078611260194</v>
+        <v>3.71655043452018</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-4.385600371253155</v>
+        <v>-4.372747691840942</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-1.24190486361649</v>
+        <v>-1.228947338626597</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>1.837357784931804</v>
+        <v>1.850294674997997</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>3.661608399656643</v>
+        <v>3.6746821573755</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>6.321678644633003</v>
+        <v>6.334690114586351</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>2.69597892237492</v>
+        <v>2.709015390805718</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>2.820965209337565</v>
+        <v>2.834120542746412</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>2.169997348577866</v>
+        <v>2.183174366116276</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>3.094981524949226</v>
+        <v>3.108369042641122</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>3.482351006640513</v>
+        <v>3.495795131501808</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>2.334873855919582</v>
+        <v>2.348317142852387</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>1.323681701739901</v>
+        <v>1.337233130449263</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>3.94047716837408</v>
+        <v>3.930047532675928</v>
       </c>
     </row>
     <row r="15">
@@ -1043,46 +1043,46 @@
         <v>180</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>4.421786683545292</v>
+        <v>4.434342529858363</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>4.467721407959409</v>
+        <v>4.480669734014597</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>2.1591341097213</v>
+        <v>1.871529652563829</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-1.034096131871145</v>
+        <v>-1.021166324592905</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-2.67950243152417</v>
+        <v>-2.666437763501925</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.72031370680088</v>
+        <v>-0.7073105132557558</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.304154119535049</v>
+        <v>0.3171859535410206</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>2.055936705585815</v>
+        <v>2.069088990896255</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>1.441025566406438</v>
+        <v>1.454199993012466</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>1.147695076358211</v>
+        <v>1.161080050863049</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.276822802523554</v>
+        <v>-1.26338137637353</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.4227350286556373</v>
+        <v>0.4361770121931841</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.002568627661105438</v>
+        <v>0.01611943890651446</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.2521142492420623</v>
+        <v>0.2416846135439101</v>
       </c>
     </row>
     <row r="16">
@@ -1095,46 +1095,46 @@
         <v>263</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.9908892735698203</v>
+        <v>-0.9782342356220184</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.03117031667859749</v>
+        <v>0.04422493979240727</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>4.184639073787196</v>
+        <v>4.199127581021223</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>4.142512426755424</v>
+        <v>3.951966744867967</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>2.29176284148194</v>
+        <v>2.098610053512594</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>4.69201753426001</v>
+        <v>4.500008449570736</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>3.471518512499628</v>
+        <v>3.484547758311976</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.4090151808947766</v>
+        <v>-0.3958686541837366</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>1.80764641047562</v>
+        <v>1.820817531520952</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>2.478682371593742</v>
+        <v>2.492064991718458</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>3.034647125455919</v>
+        <v>3.048087573158163</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.03011006591614063</v>
+        <v>0.04355042058030989</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.3901753347262655</v>
+        <v>-0.3766253571273737</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>4.041721346833867</v>
+        <v>4.031291711135793</v>
       </c>
     </row>
     <row r="17">
@@ -1147,150 +1147,150 @@
         <v>329</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.08701713730498994</v>
+        <v>0.09948175293579453</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>2.119342701640512</v>
+        <v>2.132200267421609</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>2.027101785015375</v>
+        <v>2.04110541424653</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>2.762813318757814</v>
+        <v>2.777094500773273</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.014387996779995</v>
+        <v>1.028075670244689</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>2.522949557957801</v>
+        <v>2.537155054299589</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>3.349843760637185</v>
+        <v>3.362865294871696</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>2.885506912613444</v>
+        <v>2.89864850116426</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1.308641257579836</v>
+        <v>1.321806103304219</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-1.663510232706109</v>
+        <v>-1.650134781931257</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.868646924911303</v>
+        <v>-1.85521213819473</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-3.65719340707178</v>
+        <v>-3.643756811530636</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-2.863536068022455</v>
+        <v>-2.849987832432703</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-4.134917159065864</v>
+        <v>-4.145346794764095</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ -0.004235</t>
+          <t>X ≈ -0.004237</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>424</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-1.434006557936996</v>
+        <v>-1.542865045658004</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-2.446499310901565</v>
+        <v>-2.560936248261712</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-2.372044550888646</v>
+        <v>-2.359686741902067</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.3628687837263129</v>
+        <v>-0.349555236474437</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.2771085680904335</v>
+        <v>0.290659616834958</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.3673539636466288</v>
+        <v>-0.3540572926029313</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.2157132718654324</v>
+        <v>-0.202710477562448</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.02494761792441125</v>
+        <v>0.03807339868462378</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.4350869337693695</v>
+        <v>0.4482398387256552</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.7654011645278018</v>
+        <v>0.7787680958255976</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>1.267819567299995</v>
+        <v>1.281248257987642</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.3604692941713949</v>
+        <v>0.3739017038090466</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.1757805873676119</v>
+        <v>0.1893265842845295</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.461722228745359</v>
+        <v>-1.472151864443511</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ 0.007969</t>
+          <t>X ≈ 0.007968</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-2.377103707313232</v>
+        <v>-2.36079949499414</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.7128898531159891</v>
+        <v>0.7241604606684717</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.807935139955013</v>
+        <v>1.814825350403638</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.2050546444935506</v>
+        <v>0.2144330756115238</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>2.143141492882272</v>
+        <v>2.148736867219995</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>2.938839157765315</v>
+        <v>2.942015026182695</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>2.49010967832951</v>
+        <v>2.361697421957459</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>2.519087052302964</v>
+        <v>2.52309494990287</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1.962829176898673</v>
+        <v>1.968578811647355</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>2.101273146551932</v>
+        <v>2.109506133348113</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.4046398097166417</v>
+        <v>0.4182191680993057</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.07563814594932</v>
+        <v>0.9469866832090048</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.9029397768951313</v>
+        <v>0.9177329523052009</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>2.043159025361405</v>
+        <v>2.135811991542198</v>
       </c>
     </row>
     <row r="20">
@@ -1303,46 +1303,46 @@
         <v>341</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-3.078792989112571</v>
+        <v>-3.066270699436949</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-1.181272570699043</v>
+        <v>-1.168362761122992</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-2.453369815050529</v>
+        <v>-2.440362683632927</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-2.615470232250033</v>
+        <v>-2.602491089851569</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.06306489067831222</v>
+        <v>0.0761756950532515</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.8091951794066148</v>
+        <v>-0.7961522831122494</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.5682705652149806</v>
+        <v>0.5813368195154567</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.7762005765671987</v>
+        <v>-0.7632841466706495</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-2.008666502443646</v>
+        <v>-1.994787360703015</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-1.984559625764724</v>
+        <v>-1.969756117152187</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-1.731474796661374</v>
+        <v>-1.884163049069592</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.9410125219815413</v>
+        <v>0.9544648107016513</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.8137321154017556</v>
+        <v>0.8276689357953231</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.1095670801811295</v>
+        <v>-0.1199967158792816</v>
       </c>
     </row>
     <row r="21">
@@ -1355,46 +1355,46 @@
         <v>267</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.2550498688871272</v>
+        <v>-0.2425275792115045</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-2.989558879245905</v>
+        <v>-2.976649069669854</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-2.262767587902481</v>
+        <v>-2.249760456484879</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-5.120660193284863</v>
+        <v>-5.107681050886399</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-3.043773674573544</v>
+        <v>-3.030662870198604</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-5.734477474847729</v>
+        <v>-5.721434578553364</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-4.698741567004035</v>
+        <v>-4.685675312703559</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-4.21886365929366</v>
+        <v>-4.406982921447288</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.9533135599114431</v>
+        <v>0.964955649891003</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>1.229091849579724</v>
+        <v>1.241804683087508</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.8462092060014399</v>
+        <v>-0.8327519122912221</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1.05967577397584</v>
+        <v>1.07312806269595</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>2.886288048051924</v>
+        <v>2.898700824310595</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.8888183690922489</v>
+        <v>0.8783887333940967</v>
       </c>
     </row>
     <row r="22">
@@ -1407,46 +1407,46 @@
         <v>222</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.321102312512487</v>
+        <v>1.33362460218811</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>2.850579016613992</v>
+        <v>2.863488826190043</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-2.48655152779564</v>
+        <v>-2.473544396378038</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-5.053524496669517</v>
+        <v>-5.040545354271053</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-7.388464026635241</v>
+        <v>-7.375353222260301</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-6.191946721759152</v>
+        <v>-6.178903825464786</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-6.726422175040071</v>
+        <v>-6.713355920739595</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-4.499440258766569</v>
+        <v>-4.486259249471331</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-6.362491110372872</v>
+        <v>-6.343963773316091</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-4.976235332979414</v>
+        <v>-4.957315987620703</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-3.83523064763186</v>
+        <v>-3.821773353921643</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-4.702494170078623</v>
+        <v>-4.689041881358513</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-4.862471947899081</v>
+        <v>-5.109565624117778</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-6.865002867875006</v>
+        <v>-6.875432503573158</v>
       </c>
     </row>
     <row r="23">
@@ -1459,202 +1459,202 @@
         <v>190</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-4.062448675458178</v>
+        <v>-4.049926385782555</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-7.768663306461875</v>
+        <v>-7.755753496885823</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-8.689035552734651</v>
+        <v>-8.676028421317049</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-8.032261895531569</v>
+        <v>-8.019282753133105</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-5.421729812223916</v>
+        <v>-5.408619007848976</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-5.649791414184413</v>
+        <v>-5.636748517890048</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-7.833996827863224</v>
+        <v>-7.820930573562748</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-4.098931632843758</v>
+        <v>-4.08575062354852</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-6.268334956944464</v>
+        <v>-6.247475707627004</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-4.494701603362849</v>
+        <v>-4.473851596783483</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-5.752086506627641</v>
+        <v>-5.738629212917424</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-4.138755980861312</v>
+        <v>-4.125303692141202</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-5.085326381279806</v>
+        <v>-5.071770334928203</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-4.309289259529926</v>
+        <v>-4.319718895228078</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.069</t>
+          <t>X ≈ 0.06899</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>153</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.5522304370360303</v>
+        <v>-0.5397081473604075</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.430917617846525</v>
+        <v>0.4438274274225762</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.92106231084459</v>
+        <v>-1.908055179426988</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-2.446505774134401</v>
+        <v>-2.433526631735937</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-3.631268679856412</v>
+        <v>-3.618157875481472</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-7.248672846679817</v>
+        <v>-7.235629950385452</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-7.337148526051003</v>
+        <v>-7.324082271750527</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-3.889485820293466</v>
+        <v>-3.876304810998228</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-3.306257717849235</v>
+        <v>-3.285332333722714</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.5180934162282469</v>
+        <v>-0.8897837002744353</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-2.03003628302956</v>
+        <v>-2.016578989319342</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.03486881195856739</v>
+        <v>-0.02141652323845733</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.4551234229035401</v>
+        <v>-0.4415673765519372</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>1.101787451856438</v>
+        <v>1.091357816158286</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 0.0812</t>
+          <t>X ≈ 0.08119</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>110</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-6.61757235103147</v>
+        <v>-6.605050061355847</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-4.622472699468538</v>
+        <v>-4.609562889892487</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-5.929259969616723</v>
+        <v>-5.916252838199121</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-8.534762527663773</v>
+        <v>-8.521783385265309</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-5.424095661299603</v>
+        <v>-5.410984856924664</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-7.860995587008198</v>
+        <v>-7.847952690713832</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.590575904025982</v>
+        <v>-1.577509649725506</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-7.505235621201457</v>
+        <v>-7.492054611906219</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-9.768978332210459</v>
+        <v>-10.28030949570168</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-6.982739880874796</v>
+        <v>-6.969334753221965</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-3.551129568828699</v>
+        <v>-3.537672275118481</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-6.244019138756038</v>
+        <v>-6.230566850035927</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-5.755182840609933</v>
+        <v>-5.74162679425833</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-7.323643326515509</v>
+        <v>-7.334072962213661</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 0.09341</t>
+          <t>X ≈ 0.0934</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>103</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>6.729862650663861</v>
+        <v>6.742384940339484</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1.234793892068481</v>
+        <v>1.247703701644532</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-4.985317532974705</v>
+        <v>-4.972310401557102</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-1.94244304114396</v>
+        <v>-1.929463898745496</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-7.335233188254911</v>
+        <v>-7.322122383879972</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-7.037791250539193</v>
+        <v>-7.024748354244828</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-8.093398754219294</v>
+        <v>-8.080332499918818</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-6.618834580185258</v>
+        <v>-6.60565357089002</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-9.592455825590861</v>
+        <v>-9.579257086636098</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-7.529959651395487</v>
+        <v>-7.516554523742656</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-5.792965402897536</v>
+        <v>-5.779508109187319</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-4.787708459144341</v>
+        <v>-4.774256170424231</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-5.207963070089349</v>
+        <v>-5.194407023737746</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-4.958241737812955</v>
+        <v>-4.968671373511107</v>
       </c>
     </row>
     <row r="27">
@@ -1667,46 +1667,46 @@
         <v>86</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-2.493438320210011</v>
+        <v>-2.480916030534388</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>6.360104345895529</v>
+        <v>6.37301415547158</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>4.802444941624529</v>
+        <v>4.815452073042131</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>3.769907376557612</v>
+        <v>3.782886518956076</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>6.719858254508758</v>
+        <v>6.732969058883697</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>5.85450949454993</v>
+        <v>5.867552390844295</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>3.444194381928824</v>
+        <v>3.4572606362293</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>2.977010983147387</v>
+        <v>2.990191992442625</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>5.241592492313849</v>
+        <v>5.254791231268612</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>4.391467307285922</v>
+        <v>4.404872434938753</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>7.675086075991608</v>
+        <v>7.688543369701826</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>8.872259931011456</v>
+        <v>8.885712219731566</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>7.289214622392173</v>
+        <v>7.302770668743776</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>5.213354559319548</v>
+        <v>5.202924923621396</v>
       </c>
     </row>
     <row r="28">
@@ -1719,46 +1719,46 @@
         <v>56</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-2.493438320209975</v>
+        <v>-2.480916030534353</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.5335833617456629</v>
+        <v>-0.5206735521696118</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>8.000119360229121</v>
+        <v>8.013126491646723</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>9.916086778550969</v>
+        <v>9.929065920949434</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-1.336620150806922</v>
+        <v>-1.323509346431983</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>4.317964644051642</v>
+        <v>4.331007540346008</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.6618023553507939</v>
+        <v>0.6748686096512699</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0.1946189565692933</v>
+        <v>0.2077999658645311</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>5.490761927529853</v>
+        <v>5.503960666484616</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>4.640636742501869</v>
+        <v>4.6540418701547</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>4.435883418184289</v>
+        <v>4.449340711894507</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>6.255980861244012</v>
+        <v>6.269433149964122</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>7.621440536013445</v>
+        <v>7.634996582365048</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>6.085447582575455</v>
+        <v>6.075017946877303</v>
       </c>
     </row>
     <row r="29">
@@ -1771,46 +1771,46 @@
         <v>46</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.3195252767315964</v>
+        <v>-0.3070029870559736</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>6.764553284217079</v>
+        <v>6.777463093793131</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>2.021858490664023</v>
+        <v>2.034865622081625</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>10.84776379718456</v>
+        <v>10.86074293958303</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>3.787603451677555</v>
+        <v>3.800714256052494</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>8.432871476349668</v>
+        <v>8.445914372644033</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>4.000311672120937</v>
+        <v>4.013377926421413</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>5.707041316817701</v>
+        <v>5.720222326112939</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>5.6460414306354</v>
+        <v>5.659240169590163</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>13.4915684195205</v>
+        <v>13.50497354717334</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>15.46072813868119</v>
+        <v>15.47418543239141</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>15.49511129602662</v>
+        <v>15.50856358474673</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>12.90094364160345</v>
+        <v>12.91449968795506</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>13.15066497387974</v>
+        <v>13.14023533818159</v>
       </c>
     </row>
     <row r="30">
@@ -1823,46 +1823,46 @@
         <v>33</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>8.112622285850541</v>
+        <v>8.125144575526164</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>9.531351703189401</v>
+        <v>9.544261512765452</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>15.19708905719888</v>
+        <v>15.21009618861648</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>9.266736129200225</v>
+        <v>9.27971527159869</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>2.667708853522086</v>
+        <v>2.680819657897025</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>15.08636291244987</v>
+        <v>15.09940580874424</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>8.941023134571438</v>
+        <v>8.954089388871914</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>11.50414276609298</v>
+        <v>11.51732377538821</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>14.47344591021371</v>
+        <v>14.48664464916847</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>19.68392678579191</v>
+        <v>19.69733191344474</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>19.47917346147433</v>
+        <v>19.49263075518455</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>7.392344497607738</v>
+        <v>7.405796786327848</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>10.00239291696577</v>
+        <v>10.01594896331737</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>10.25211424924198</v>
+        <v>10.24168461354383</v>
       </c>
     </row>
     <row r="31">
@@ -1875,46 +1875,46 @@
         <v>35</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>7.506561679790025</v>
+        <v>7.519083969465647</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.1807023525400524</v>
+        <v>0.1936121621161035</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>19.78583364594343</v>
+        <v>19.79884077736103</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>14.20180106426525</v>
+        <v>14.21478020666371</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>16.52052270633594</v>
+        <v>16.53363351071088</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>19.67510750119446</v>
+        <v>19.68815039748883</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>22.44751664106507</v>
+        <v>22.46058289536555</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>16.26604752799778</v>
+        <v>16.27922853729302</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>13.3479047846727</v>
+        <v>13.36110352362746</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>12.49777959964477</v>
+        <v>12.5111847272976</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>15.15016913247001</v>
+        <v>15.16362642618023</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>15.18455228981537</v>
+        <v>15.19800457853548</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>17.6214405360134</v>
+        <v>17.63499658236501</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>20.72830472543262</v>
+        <v>20.71787508973447</v>
       </c>
     </row>
     <row r="32">
@@ -1927,46 +1927,46 @@
         <v>39</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-3.775489602261288</v>
+        <v>-3.762967312585666</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>2.305244477082177</v>
+        <v>2.318154286658228</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.6537267936168973</v>
+        <v>-0.6407196621992952</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>4.604731467195656</v>
+        <v>4.61771060959412</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>9.19451538032861</v>
+        <v>9.20762618470355</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1.799649625736578</v>
+        <v>1.812692522030943</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>6.843121036669352</v>
+        <v>6.856187290969828</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>6.375937637887965</v>
+        <v>6.389118647183203</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>1.186732623500497</v>
+        <v>1.19993136245526</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>8.02891513078022</v>
+        <v>8.042320258433051</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>7.824161806462683</v>
+        <v>7.837619100172901</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>2.73033983560299</v>
+        <v>2.7437921243231</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>7.438290352863213</v>
+        <v>7.451846399214816</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>7.6880116851395</v>
+        <v>7.677582049441348</v>
       </c>
     </row>
     <row r="33">
@@ -1979,46 +1979,46 @@
         <v>25</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>31.50656167979008</v>
+        <v>31.5190839694657</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>21.8949880668258</v>
+        <v>21.90789787640185</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>17.50011936022915</v>
+        <v>17.51312649164675</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>21.63037249283662</v>
+        <v>21.64335163523508</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>21.09195127776454</v>
+        <v>21.10506208213948</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>21.38939321548017</v>
+        <v>21.40243611177453</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>25.30465949820795</v>
+        <v>25.31772575250842</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>36.83747609942639</v>
+        <v>36.85065710872163</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>24.77647621324403</v>
+        <v>24.78967495219879</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>15.9263510282161</v>
+        <v>15.93975615586893</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>23.72159770389858</v>
+        <v>23.7350549976088</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>27.75598086124401</v>
+        <v>27.76943314996412</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>27.33572625029905</v>
+        <v>27.34928229665066</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>27.58544758257534</v>
+        <v>27.57501794687719</v>
       </c>
     </row>
     <row r="34">
@@ -2031,46 +2031,46 @@
         <v>25</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>19.50656167979002</v>
+        <v>19.51908396946565</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>5.894988066825746</v>
+        <v>5.907897876401798</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>1.500119360229149</v>
+        <v>1.513126491646752</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>25.63037249283673</v>
+        <v>25.6433516352352</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>25.09195127776448</v>
+        <v>25.10506208213942</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>21.38939321548017</v>
+        <v>21.40243611177453</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>21.30465949820789</v>
+        <v>21.31772575250837</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>12.83747609942639</v>
+        <v>12.85065710872163</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>16.77647621324409</v>
+        <v>16.78967495219885</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>15.92635102821622</v>
+        <v>15.93975615586905</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>15.72159770389858</v>
+        <v>15.7350549976088</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>19.75598086124401</v>
+        <v>19.76943314996412</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>19.33572625029917</v>
+        <v>19.34928229665077</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>19.58544758257545</v>
+        <v>19.5750179468773</v>
       </c>
     </row>
   </sheetData>
@@ -2121,7 +2121,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that ROC-5 is above threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that ROC-5 is above threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -2214,49 +2214,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4089</v>
+        <v>4090</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.2018732300100794</v>
+        <v>-0.2020956551992299</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.02064226723909002</v>
+        <v>-0.02091733568984466</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.2071977129415501</v>
+        <v>-0.2074294703137198</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.1612840087490781</v>
+        <v>-0.1615264135453387</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.1008256866083528</v>
+        <v>-0.1010857587973675</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.01472882690315913</v>
+        <v>0.01444196828991551</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.04098762320789007</v>
+        <v>0.04069377789279827</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.07094880899851574</v>
+        <v>-0.07121789127837275</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.0280639025455045</v>
+        <v>0.02777019029409189</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.02673961434430794</v>
+        <v>-0.02702449874752233</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.05102096880572304</v>
+        <v>0.05071588204564392</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.04749017273301348</v>
+        <v>-0.04777115111114938</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.06280675703585104</v>
+        <v>-0.0630863173800833</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.1171691941426332</v>
+        <v>-0.1169135934650498</v>
       </c>
     </row>
     <row r="7">
@@ -2266,49 +2266,49 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4063</v>
+        <v>4064</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.3099250719273456</v>
+        <v>-0.3102022704166174</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.09274199452392651</v>
+        <v>-0.09308347786706861</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.2779856962263949</v>
+        <v>-0.2782845512980074</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.257179680008889</v>
+        <v>-0.2574829253932336</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.1683630640822571</v>
+        <v>-0.1686919075487481</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.004858811048947587</v>
+        <v>-0.005225970740198704</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.02703583348743877</v>
+        <v>-0.02739829563705598</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.1858711603426002</v>
+        <v>-0.1861979281334101</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.06128189885030366</v>
+        <v>-0.06163986716708791</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.08643480901029221</v>
+        <v>-0.08679251669737909</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.05607076634244379</v>
+        <v>-0.05643750300590256</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.1554582531471382</v>
+        <v>-0.1558004948956935</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.1682107575749043</v>
+        <v>-0.1685528817010677</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.1753203229131515</v>
+        <v>-0.1749820531227542</v>
       </c>
     </row>
     <row r="8">
@@ -2318,49 +2318,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4025</v>
+        <v>4026</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.4379653137711372</v>
+        <v>-0.438331232316969</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.2035999936151569</v>
+        <v>-0.2040387258765364</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.3621204811979766</v>
+        <v>-0.3625237436764834</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.3671491924173509</v>
+        <v>-0.367550247817384</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.2724513003217623</v>
+        <v>-0.2728809166213964</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.08543941531576849</v>
+        <v>-0.08591292144311069</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.03264208909370581</v>
+        <v>-0.03312969009019184</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.2381875076190099</v>
+        <v>-0.2386286055640809</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.1118612557385461</v>
+        <v>-0.1123344747423545</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.005145621076472651</v>
+        <v>-0.005653273411411419</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.07184817494947993</v>
+        <v>-0.07234137866322499</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.1725018802508984</v>
+        <v>-0.1729700277915853</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.1317352499492728</v>
+        <v>-0.1322175791873761</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.06672633046807874</v>
+        <v>-0.06631339937213454</v>
       </c>
     </row>
     <row r="9">
@@ -2370,49 +2370,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3987</v>
+        <v>3988</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.3934383202099738</v>
+        <v>-0.3939377750982089</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.2165398151447278</v>
+        <v>-0.2171021235981883</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.4228421205111843</v>
+        <v>-0.4233576293834744</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.4291721656571923</v>
+        <v>-0.429684883023981</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.3034441176308889</v>
+        <v>-0.3039947104550009</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.1675529672482412</v>
+        <v>-0.1681344587960325</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.1134676925782969</v>
+        <v>-0.1140639846631046</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.2414119546682798</v>
+        <v>-0.2419818497160335</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.1133033458741508</v>
+        <v>-0.1139063150187809</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.002522413833794701</v>
+        <v>0.001880404365984134</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.03738717758278653</v>
+        <v>0.03673377485760909</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.06452553133558325</v>
+        <v>-0.06515331620128961</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.01933894528765023</v>
+        <v>-0.01998318341948391</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.006225354470004163</v>
+        <v>-0.005724279802791443</v>
       </c>
     </row>
     <row r="10">
@@ -2422,49 +2422,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3944</v>
+        <v>3945</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.4337971779304723</v>
+        <v>-0.4344279052185342</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.186912843184345</v>
+        <v>-0.1876290379272163</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.2900197042461627</v>
+        <v>-0.2907157732672729</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.2978015081749561</v>
+        <v>-0.2984941296194776</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.2154102198322576</v>
+        <v>-0.2161316457310676</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.08125455779917701</v>
+        <v>-0.0820060840261192</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.02563662935475008</v>
+        <v>-0.02640380214749882</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.04859984994070032</v>
+        <v>-0.04936820132645892</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.03097102205644831</v>
+        <v>0.0301812813127782</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.1066955064329775</v>
+        <v>0.1058741604271134</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.09352575051626388</v>
+        <v>0.09270444036462777</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.06616839292166077</v>
+        <v>0.06535410258636887</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.06576427311279787</v>
+        <v>0.06494372594620756</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.1016747631027783</v>
+        <v>0.1022676300204708</v>
       </c>
     </row>
     <row r="11">
@@ -2474,101 +2474,101 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3882</v>
+        <v>3883</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.2469684870905979</v>
+        <v>-0.2478564822797296</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.0295540657985498</v>
+        <v>0.02856539886651177</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.0945377165753456</v>
+        <v>-0.09550216782933063</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.2072431289516103</v>
+        <v>-0.2081767490443269</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.03783540946243136</v>
+        <v>-0.03882280994687903</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.06805645455472131</v>
+        <v>0.06704675171285146</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.151663869511566</v>
+        <v>0.1506306368271311</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.1872703381095135</v>
+        <v>0.1862189498118809</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.2434172989142738</v>
+        <v>0.2423498493181881</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.3854349191065296</v>
+        <v>0.3843149415649023</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.298174280475159</v>
+        <v>0.2970724963221372</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.372870665569458</v>
+        <v>0.3717497522807278</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.3534960159442306</v>
+        <v>0.352371895002932</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.3860658205970395</v>
+        <v>0.3867614441731533</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.08357</t>
+          <t>X &gt; -0.08356</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3801</v>
+        <v>3802</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.1861493847091893</v>
+        <v>-0.1873380488829781</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.07804602643762593</v>
+        <v>0.07674947577255864</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.09274527775612995</v>
+        <v>-0.09400699904296772</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.1318946286537397</v>
+        <v>-0.1331436428341064</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.05240567761607196</v>
+        <v>-0.05368890185425101</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.1281697972601563</v>
+        <v>0.1268455605934378</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.1891132797205017</v>
+        <v>0.1877703836451516</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.2091598399044514</v>
+        <v>0.2077999658644885</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.2415313892819242</v>
+        <v>0.2401608991386937</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.5360750755223336</v>
+        <v>0.5346063923377216</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.4250677354443226</v>
+        <v>0.4236226717218088</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.5006561176205508</v>
+        <v>0.499191299280632</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.4372517631870636</v>
+        <v>0.4357929461379584</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.4915249306416953</v>
+        <v>0.4924298353570009</v>
       </c>
     </row>
     <row r="13">
@@ -2578,101 +2578,101 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3706</v>
+        <v>3707</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.1675442626676187</v>
+        <v>-0.1690880735451117</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.1983769855993032</v>
+        <v>0.1966851848180582</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.101172003774046</v>
+        <v>-0.1027960473526832</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.06392244795987523</v>
+        <v>-0.06555339570378749</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.03138600185602769</v>
+        <v>0.02971224360338454</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.2089947232884626</v>
+        <v>0.2072813338472059</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.2198224392259363</v>
+        <v>0.2181027045816037</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.1984674787367311</v>
+        <v>0.1967384445686449</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.2601733299242284</v>
+        <v>0.2584249521988511</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.5840329689169721</v>
+        <v>0.5821705994152069</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.5293626000970164</v>
+        <v>0.5275078277974785</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.606034798676589</v>
+        <v>0.6041594912960235</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.5518039411542475</v>
+        <v>0.5499295458416498</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.5741146090190057</v>
+        <v>0.5752877067909239</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.05916</t>
+          <t>X &gt; -0.05915</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3582</v>
+        <v>3583</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.3654828264686714</v>
+        <v>-0.3674566312017546</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.04268583412024896</v>
+        <v>-0.04481422373726218</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.1441890171713212</v>
+        <v>-0.1463058956653995</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.2215206029316903</v>
+        <v>-0.2236119049819436</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.2157624510018579</v>
+        <v>-0.2178777842302679</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.1526244132517576</v>
+        <v>0.1504171755450656</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.1946009860875222</v>
+        <v>0.1923775630933307</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.1607759879436657</v>
+        <v>0.1585423135140474</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.1709562801523674</v>
+        <v>0.1687162008053136</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.5632723890638971</v>
+        <v>0.5608880209372913</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.5695753886963502</v>
+        <v>0.5671799278932426</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.6477219326725816</v>
+        <v>0.6453048375512864</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.6061700125095513</v>
+        <v>0.6037465823650052</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.5647887327708148</v>
+        <v>0.5663659792523461</v>
       </c>
     </row>
     <row r="15">
@@ -2682,49 +2682,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3413</v>
+        <v>3414</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.5669934865847566</v>
+        <v>-0.5696233547246052</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.172360329599492</v>
+        <v>0.1694273568454889</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.08983391079885905</v>
+        <v>-0.09271292441161449</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.3234691665264577</v>
+        <v>-0.326274532989153</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.4077564954675168</v>
+        <v>-0.4105674825698671</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.1528458958907706</v>
+        <v>-0.1557170150518843</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.07074136955291976</v>
+        <v>0.06779883055572355</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.0290525837785367</v>
+        <v>0.02609570521286031</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.07197065443777007</v>
+        <v>0.06899639121611045</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.4379108760358861</v>
+        <v>0.4347824870568147</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.4253447764981146</v>
+        <v>0.4222074705382681</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.56417998276671</v>
+        <v>0.5610022366151739</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.5706413059523001</v>
+        <v>0.5674374943081091</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.3976362728771861</v>
+        <v>0.3998568455298539</v>
       </c>
     </row>
     <row r="16">
@@ -2734,49 +2734,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3233</v>
+        <v>3234</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.8447480274518853</v>
+        <v>-0.8481372258516657</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.06678751887090328</v>
+        <v>-0.07053047490789055</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.2150471009298869</v>
+        <v>-0.2020399695122848</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.2839044112644586</v>
+        <v>-0.2875978098943222</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.2812751256901507</v>
+        <v>-0.2850088398463697</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.1212516472165319</v>
+        <v>-0.1250160782316314</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.05774591796097184</v>
+        <v>0.05391828567713475</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.08379589810370902</v>
+        <v>-0.08761449621664497</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.004252631721946898</v>
+        <v>-0.008102139496116934</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.3983930424268465</v>
+        <v>0.394357761798581</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.520114391166814</v>
+        <v>0.5160250315908783</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.5720550498066075</v>
+        <v>0.567949837232355</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.6022692311278064</v>
+        <v>0.5981231003601479</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.4057383341992775</v>
+        <v>0.4086604948055097</v>
       </c>
     </row>
     <row r="17">
@@ -2786,49 +2786,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2970</v>
+        <v>2971</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.8318069002703936</v>
+        <v>-0.8366207285209342</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.075461899594643</v>
+        <v>-0.08068889768344434</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.6046489406438909</v>
+        <v>-0.5916418092262887</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.6758733097153709</v>
+        <v>-0.6628941673169066</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.509123268911118</v>
+        <v>-0.4960124645361788</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.5474771673270808</v>
+        <v>-0.5344342710327155</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.2445511165049084</v>
+        <v>-0.2497692105540921</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.05499701885318586</v>
+        <v>-0.06032710357263227</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.1647002573441512</v>
+        <v>-0.1700024671559888</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.2141788695073572</v>
+        <v>0.2086637188942007</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.2974470143593919</v>
+        <v>0.2918808214151198</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.6200454642049849</v>
+        <v>0.6143709232570913</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.6901523694509137</v>
+        <v>0.6844101566776288</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.08376408089190335</v>
+        <v>0.08797654667529287</v>
       </c>
     </row>
     <row r="18">
@@ -2838,101 +2838,101 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2641</v>
+        <v>2642</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.9462685088892187</v>
+        <v>-0.9531906438878011</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.3488775428382596</v>
+        <v>-0.3562530669944124</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.9324967213110256</v>
+        <v>-0.9194895898934234</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-1.10424434370541</v>
+        <v>-1.091265201306946</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.6989131993966922</v>
+        <v>-0.6858023950217529</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.9299725829343259</v>
+        <v>-0.9169296866399606</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.6923193537558561</v>
+        <v>-0.699639290904237</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.4213074290964727</v>
+        <v>-0.4287990846318479</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.348240340043894</v>
+        <v>-0.3557727244161839</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.4480901586509418</v>
+        <v>0.4401340848183466</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.5672860548819401</v>
+        <v>0.5592515949622907</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>1.152878326245904</v>
+        <v>1.144622257377137</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.132849641669289</v>
+        <v>1.124537688251166</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.6093021831054983</v>
+        <v>0.6151390672406123</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; 0.001869</t>
+          <t>X &gt; 0.001866</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2217</v>
+        <v>2218</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.8529888820077218</v>
+        <v>-0.8404665923320991</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.05229143761228272</v>
+        <v>0.06520124718833387</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.6571840105573372</v>
+        <v>-0.6441768791397351</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.246032001545338</v>
+        <v>-1.233052859146873</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.8855768121231335</v>
+        <v>-0.8724660077481943</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.03757307665466</v>
+        <v>-1.024530180360294</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.7834699981949811</v>
+        <v>-0.7946337980534324</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.5066534552294755</v>
+        <v>-0.5180479272495973</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.4980512395011871</v>
+        <v>-0.5094703469464434</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.3874046076848714</v>
+        <v>0.375399720225424</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.4333094156102888</v>
+        <v>0.4212323951774621</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.304426106850137</v>
+        <v>1.291955672486644</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.315888558685039</v>
+        <v>1.303315645005831</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1.005384434176662</v>
+        <v>1.014152302152269</v>
       </c>
     </row>
     <row r="20">
@@ -2945,98 +2945,98 @@
         <v>1815</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.51541634218799</v>
+        <v>-0.5028940525123673</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.0940229221852249</v>
+        <v>-0.08111311260917375</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.203177343067523</v>
+        <v>-1.190170211649921</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.567429704965519</v>
+        <v>-1.554450562567055</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.556400370587141</v>
+        <v>-1.543289566212202</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-1.918299092212138</v>
+        <v>-1.905256195917772</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.50852731497892</v>
+        <v>-1.495461060678444</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-1.176817468468059</v>
+        <v>-1.193298935234417</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-1.043105744951731</v>
+        <v>-1.059692832298126</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.007803972630028966</v>
+        <v>-0.009638783624957625</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.4396593779073967</v>
+        <v>0.4219014478014316</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>1.355099803975286</v>
+        <v>1.368552092695396</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1.407351594651729</v>
+        <v>1.388929873743223</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.7755302272035038</v>
+        <v>0.7651005915053517</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 0.02628</t>
+          <t>X &gt; 0.02627</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>1474</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.07760362836918233</v>
+        <v>0.09012591804480508</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.1575049815754284</v>
+        <v>0.1704147911514795</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.9139537114893628</v>
+        <v>-0.9009465800717606</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.324972568056417</v>
+        <v>-1.311993425657953</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.931052781775414</v>
+        <v>-1.917941977400474</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-2.174882833234314</v>
+        <v>-2.161839936939948</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.988980555919305</v>
+        <v>-1.975914301618829</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.269497495698864</v>
+        <v>-1.292779968409626</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.8197297488155328</v>
+        <v>-0.8433649936373016</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.4687239095720912</v>
+        <v>0.4438211965194014</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.9419366869494255</v>
+        <v>0.9553939806596432</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1.450896115481299</v>
+        <v>1.464348404201409</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.544681474179711</v>
+        <v>1.518773822074444</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.9802915445835438</v>
+        <v>0.9698619088853917</v>
       </c>
     </row>
     <row r="22">
@@ -3049,98 +3049,98 @@
         <v>1207</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.1511897789635768</v>
+        <v>0.1637120686391995</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.8536657527761733</v>
+        <v>0.8665755623522244</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.6155831191096581</v>
+        <v>-0.602575987692056</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.4853299865021583</v>
+        <v>-0.4723508441036941</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.684908226367718</v>
+        <v>-1.671797421992778</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-1.387466288652057</v>
+        <v>-1.374423392357691</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.389555377825168</v>
+        <v>-1.376489123524692</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.6170693551190709</v>
+        <v>-0.6038883458238331</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.211943968724484</v>
+        <v>-1.243382899040817</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.3005232136466205</v>
+        <v>0.2672995801866094</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>1.337491743633677</v>
+        <v>1.350949037343895</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>1.537437814886395</v>
+        <v>1.550890103606505</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>1.247905206388587</v>
+        <v>1.213520707246737</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1.000526290114756</v>
+        <v>0.9900966544166039</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.05069</t>
+          <t>X &gt; 0.05068</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>985</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.1124859392575885</v>
+        <v>-0.0999636495819658</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.4036000222462306</v>
+        <v>0.4165098318222817</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.1939029295377921</v>
+        <v>-0.18089579812019</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.5442529386320132</v>
+        <v>0.5572320810304774</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.3994367668150289</v>
+        <v>-0.3863259624400897</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.304629074286801</v>
+        <v>-0.2915861779924356</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.186728546371647</v>
+        <v>-0.173662292071171</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.2579421581903176</v>
+        <v>0.2711231674855554</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.05110999365246727</v>
+        <v>-0.09381035681837346</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>1.489802804865903</v>
+        <v>1.444827149783798</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>2.50332359222346</v>
+        <v>2.516780885933677</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>2.943798120127255</v>
+        <v>2.957250408847365</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>2.625066351821957</v>
+        <v>2.63862239817356</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>2.773264841458641</v>
+        <v>2.762835205760489</v>
       </c>
     </row>
     <row r="24">
@@ -3153,202 +3153,202 @@
         <v>795</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.8315303121614193</v>
+        <v>0.844052601837042</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>2.35671955992489</v>
+        <v>2.369629369500942</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.836380338899197</v>
+        <v>1.849387470316799</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>2.593986043652237</v>
+        <v>2.606965186050701</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.8008596842889801</v>
+        <v>0.8139704886639194</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.9728311075755229</v>
+        <v>0.9858740038698883</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1.640920476877909</v>
+        <v>1.653986731178385</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>1.299207592525512</v>
+        <v>1.31238860182075</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>1.434767670530526</v>
+        <v>1.376876959727078</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>2.92006172004006</v>
+        <v>2.859354145818735</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>4.476314685030651</v>
+        <v>4.489771978740869</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>4.636484005898097</v>
+        <v>4.649936294618207</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>4.467801721997219</v>
+        <v>4.481357768348822</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>4.465950727229483</v>
+        <v>4.455521091531331</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.0751</t>
+          <t>X &gt; 0.07509</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>642</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1.161305070147719</v>
+        <v>1.173827359823342</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>2.815672359205244</v>
+        <v>2.828582168781296</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2.731845643277389</v>
+        <v>2.744852774694991</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>3.795224747891112</v>
+        <v>3.808203890289576</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1.857114574809607</v>
+        <v>1.870225379184546</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>2.932161489197121</v>
+        <v>2.945204385491486</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>3.780553743931058</v>
+        <v>3.793619998231534</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>2.535765368477705</v>
+        <v>2.548946377772943</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>2.564638207013559</v>
+        <v>2.487964221250166</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>3.739435140365686</v>
+        <v>3.752840268018517</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>6.026893654054341</v>
+        <v>6.040350947764558</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>5.74975033164899</v>
+        <v>5.7632026203691</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>5.64102220045487</v>
+        <v>5.654578246806473</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>5.267690573229601</v>
+        <v>5.257260937531449</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.0873</t>
+          <t>X &gt; 0.08729</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>532</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>2.769719574526874</v>
+        <v>2.782241864202497</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>4.353634683367119</v>
+        <v>4.36654449294317</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>4.52267575120662</v>
+        <v>4.535682882624222</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>6.344658207122386</v>
+        <v>6.35763734952085</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>3.362627969493836</v>
+        <v>3.375738773868775</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>5.16382930570574</v>
+        <v>5.176872202000105</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>4.891125663621423</v>
+        <v>4.904191917921899</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>4.61191218965196</v>
+        <v>4.625093198947198</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>5.114822077905743</v>
+        <v>5.128020816860506</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>5.956426216186088</v>
+        <v>5.969831343838919</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>8.007311989612873</v>
+        <v>8.020769283323091</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>8.229665071770327</v>
+        <v>8.243117360490437</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>7.997380385637449</v>
+        <v>8.010936431989052</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>7.87116186828969</v>
+        <v>7.860732232591538</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 0.09951</t>
+          <t>X &gt; 0.0995</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>429</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1.818915992144341</v>
+        <v>1.831438281819963</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>5.102447274284977</v>
+        <v>5.115357083861028</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>6.80548066559048</v>
+        <v>6.818487797008082</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>8.33433519679938</v>
+        <v>8.347314339197844</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>5.931112116925355</v>
+        <v>5.944222921300295</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>8.093355919442871</v>
+        <v>8.106398815737236</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>8.008622202170592</v>
+        <v>8.021688456471068</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>7.308338570288868</v>
+        <v>7.321519579584105</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>8.645940082707959</v>
+        <v>8.659138821662722</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>9.194416296281432</v>
+        <v>9.207821423934263</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>11.32066530296618</v>
+        <v>11.33412259667639</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>11.35504846031161</v>
+        <v>11.36850074903172</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>11.16789408246695</v>
+        <v>11.18145012881855</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>10.95141494854276</v>
+        <v>10.94098531284461</v>
       </c>
     </row>
     <row r="28">
@@ -3361,46 +3361,46 @@
         <v>343</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>2.900147685620936</v>
+        <v>2.912669975296559</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>4.787116346709148</v>
+        <v>4.800026156285199</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>7.307699535156289</v>
+        <v>7.320706666573891</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>9.478768994294406</v>
+        <v>9.49174813669287</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>5.733350694674129</v>
+        <v>5.746461499049069</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>8.654699337929152</v>
+        <v>8.667742234223518</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>9.153055999665618</v>
+        <v>9.166122253966094</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>8.394327411379741</v>
+        <v>8.407508420674979</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>9.499508283214929</v>
+        <v>9.512707022169693</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>10.39865423521324</v>
+        <v>10.41205936286607</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>12.23471723742628</v>
+        <v>12.2481745311365</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>11.97755520526734</v>
+        <v>11.99100749398745</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>12.14039097333119</v>
+        <v>12.15394701968279</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>12.39011230560747</v>
+        <v>12.37968266990932</v>
       </c>
     </row>
     <row r="29">
@@ -3413,46 +3413,46 @@
         <v>287</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>3.952554711148913</v>
+        <v>3.965077000824536</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>5.825301655675936</v>
+        <v>5.838211465251987</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>7.172593227825004</v>
+        <v>7.185600359242606</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>9.393438694927269</v>
+        <v>9.406417837325733</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>7.112857201109456</v>
+        <v>7.125968005484395</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>9.500891473319882</v>
+        <v>9.513934369614248</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>10.80988597904412</v>
+        <v>10.82295223334459</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>9.994270524513489</v>
+        <v>10.00745153380873</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>10.28170269408032</v>
+        <v>10.29490143303508</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>11.52216984354718</v>
+        <v>11.53557497120001</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>13.7564409094735</v>
+        <v>13.76989820318371</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>13.09395995532067</v>
+        <v>13.10741224404078</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>13.0221374001249</v>
+        <v>13.0356934464765</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>13.62029078815031</v>
+        <v>13.60986115245216</v>
       </c>
     </row>
     <row r="30">
@@ -3465,46 +3465,46 @@
         <v>241</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>4.767972468171763</v>
+        <v>4.780494757847386</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>5.646025411224109</v>
+        <v>5.65893522080016</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>8.155721019980213</v>
+        <v>8.168728151397815</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>9.115849671259909</v>
+        <v>9.128828813658373</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>7.747552937515543</v>
+        <v>7.760663741890482</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>9.704745912575603</v>
+        <v>9.717788808869969</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>12.10963875131991</v>
+        <v>12.12270500562039</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>10.81257983386622</v>
+        <v>10.82576084316145</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>11.16651770702001</v>
+        <v>11.17971644597478</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>11.1462680406643</v>
+        <v>11.15967316831713</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>13.43114127236331</v>
+        <v>13.44459856607352</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>12.63564891103654</v>
+        <v>12.64910119975665</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>13.04526981876383</v>
+        <v>13.05882586511544</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>13.70992891037622</v>
+        <v>13.69949927467807</v>
       </c>
     </row>
     <row r="31">
@@ -3517,46 +3517,46 @@
         <v>208</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>4.237330910559251</v>
+        <v>4.249853200234874</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>5.029603451441155</v>
+        <v>5.042513261017206</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>7.038580898690718</v>
+        <v>7.05158803010832</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>9.091910954375138</v>
+        <v>9.104890096773602</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>8.553489739302968</v>
+        <v>8.566600543677907</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>8.850931677018629</v>
+        <v>8.863974573312994</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>12.6123518059002</v>
+        <v>12.62541806020067</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>10.702860714811</v>
+        <v>10.71604172410624</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>10.6418608286287</v>
+        <v>10.65505956758346</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>9.791735643600774</v>
+        <v>9.805140771253605</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>12.47159770389858</v>
+        <v>12.4850549976088</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>13.46751932278246</v>
+        <v>13.48097161150258</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>13.5280339426068</v>
+        <v>13.54158998895841</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>14.25852450565233</v>
+        <v>14.24809486995418</v>
       </c>
     </row>
     <row r="32">
@@ -3569,46 +3569,46 @@
         <v>173</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>3.575925841639737</v>
+        <v>3.58844813131536</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>6.010595003241953</v>
+        <v>6.023504812818004</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>4.459656932483519</v>
+        <v>4.472664063901121</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>8.058118157576565</v>
+        <v>8.07109729997503</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>6.941662260423463</v>
+        <v>6.954773064798403</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>6.661069516058205</v>
+        <v>6.674112412352571</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>10.62257857335239</v>
+        <v>10.63564482765287</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>9.57736049248998</v>
+        <v>9.590541501785218</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>10.09439528838859</v>
+        <v>10.10759402734335</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>9.244270103360662</v>
+        <v>9.257675231013494</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>11.92969018944771</v>
+        <v>11.94314748315793</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>13.12014271095499</v>
+        <v>13.1335949996751</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>12.69988810001009</v>
+        <v>12.7134441463617</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>12.94960943228638</v>
+        <v>12.93917979658823</v>
       </c>
     </row>
     <row r="33">
@@ -3621,46 +3621,46 @@
         <v>134</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>5.715516903670625</v>
+        <v>5.728039193346248</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>7.089017917572036</v>
+        <v>7.101927727148087</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>5.947880554259022</v>
+        <v>5.960887685676624</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>9.063208313732204</v>
+        <v>9.076187456130668</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>6.285981128510777</v>
+        <v>6.299091932885716</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>8.075960379659278</v>
+        <v>8.089003275953644</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>11.72256994596909</v>
+        <v>11.73563620026957</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>10.50911789047117</v>
+        <v>10.5222988997664</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>12.68692397443811</v>
+        <v>12.70012271339287</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>9.597992819260938</v>
+        <v>9.611397946913769</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>13.12458277852545</v>
+        <v>13.13804007223567</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>16.14404056273655</v>
+        <v>16.15749285145666</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>14.23124863835881</v>
+        <v>14.24480468471042</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>14.4809699706351</v>
+        <v>14.47054033493695</v>
       </c>
     </row>
     <row r="34">
@@ -3673,46 +3673,46 @@
         <v>109</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.1998603385586009</v>
+        <v>-0.1873380488829781</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>3.693153204440442</v>
+        <v>3.706063014016493</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>3.298284497843852</v>
+        <v>3.311291629261454</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>6.180831208433013</v>
+        <v>6.193810350831477</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>2.890116415379183</v>
+        <v>2.903227219754122</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>5.022420738415946</v>
+        <v>5.035463634710311</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>8.607411791785871</v>
+        <v>8.620478046086347</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>4.470503622362166</v>
+        <v>4.483684631657404</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>9.914090892143172</v>
+        <v>9.927289631097935</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>8.1465345144547</v>
+        <v>8.159939642107531</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>10.69407476811877</v>
+        <v>10.70753206182899</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>13.48075150344584</v>
+        <v>13.49420379216595</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>11.22563450717985</v>
+        <v>11.23919055353146</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>11.47535583945614</v>
+        <v>11.46492620375799</v>
       </c>
     </row>
     <row r="35">
@@ -3725,46 +3725,46 @@
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-6.064866891638545</v>
+        <v>-6.052344601962922</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>3.037845209682906</v>
+        <v>3.050755019258958</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>3.833452693562514</v>
+        <v>3.846459824980116</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.3922772547414439</v>
+        <v>0.4052563971399081</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-3.717572531759302</v>
+        <v>-3.704461727384363</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.1512979773849352</v>
+        <v>0.1643408736793006</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>4.828469022017416</v>
+        <v>4.841535276317892</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>1.980333242283528</v>
+        <v>1.993514251578766</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>7.871714308482183</v>
+        <v>7.884913047436946</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>5.831112932978066</v>
+        <v>5.844518060630897</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>9.197788180089063</v>
+        <v>9.211245473799281</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>11.61312371838687</v>
+        <v>11.62657600710698</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>8.811916726489592</v>
+        <v>8.825472772841195</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>9.06163805876588</v>
+        <v>9.051208423067727</v>
       </c>
     </row>
   </sheetData>
@@ -3815,7 +3815,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that ROC-5 is below threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that ROC-5 is below threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -3911,46 +3911,46 @@
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>9.41132358455193</v>
+        <v>9.423845874227553</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>1.847369019206724</v>
+        <v>1.860278828782775</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>9.78583364594347</v>
+        <v>9.798840777361072</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>7.535134397598583</v>
+        <v>7.548113539997047</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>4.615760801574034</v>
+        <v>4.628871605948973</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.1512979773849352</v>
+        <v>0.1643408736793006</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.06656426011265637</v>
+        <v>0.0796305144131324</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>5.551761813712098</v>
+        <v>5.564942823007335</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>1.919333356101227</v>
+        <v>1.93253209505599</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>4.640636742501869</v>
+        <v>4.6540418701547</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.86445484675572</v>
+        <v>0.8779121404659378</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>5.660742766005917</v>
+        <v>5.674195054726027</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>6.430964345537205</v>
+        <v>6.444520391888808</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>9.06163805876588</v>
+        <v>9.051208423067727</v>
       </c>
     </row>
     <row r="7">
@@ -3963,46 +3963,46 @@
         <v>110</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>11.14292531615366</v>
+        <v>11.15544760582928</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>4.076806248643948</v>
+        <v>4.089716058219999</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>10.04557390568372</v>
+        <v>10.05858103710133</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>9.266736129200311</v>
+        <v>9.279715271598775</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>6.001042186855422</v>
+        <v>6.014152991230361</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.8439386700256222</v>
+        <v>0.8569815663199876</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>2.577386770935163</v>
+        <v>2.590453025235639</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>8.473839735790023</v>
+        <v>8.48702074508526</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>4.776476213244088</v>
+        <v>4.789674952198851</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>5.744532846397973</v>
+        <v>5.757937974050805</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>4.630688612989495</v>
+        <v>4.644145906699713</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>8.301435406698559</v>
+        <v>8.314887695418669</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>8.790271704844564</v>
+        <v>8.803827751196167</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>9.039993037120851</v>
+        <v>9.029563401422699</v>
       </c>
     </row>
     <row r="8">
@@ -4015,46 +4015,46 @@
         <v>148</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>11.69575086897922</v>
+        <v>11.70827315865484</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>6.030123201960897</v>
+        <v>6.043033011536949</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>9.689308549418371</v>
+        <v>9.702315680835973</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>9.819561682025871</v>
+        <v>9.832540824424335</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>7.25411343992667</v>
+        <v>7.267224244301609</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>2.821825647912604</v>
+        <v>2.834868544206969</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>2.061416254964648</v>
+        <v>2.074482509265124</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>7.675313937264228</v>
+        <v>7.688494946559466</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>4.911611348379218</v>
+        <v>4.924810087333981</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>2.034459136324266</v>
+        <v>2.047864263977097</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>3.856732839033711</v>
+        <v>3.870190132743929</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>6.593818699081851</v>
+        <v>6.607270987801961</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>5.497888412461272</v>
+        <v>5.511444458812875</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>3.720582717710528</v>
+        <v>3.710153082012376</v>
       </c>
     </row>
     <row r="9">
@@ -4067,46 +4067,46 @@
         <v>186</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>8.25924985183304</v>
+        <v>8.271772141508663</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>5.034773013062328</v>
+        <v>5.047682822638379</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>8.940979575282938</v>
+        <v>8.95398670670054</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>9.071232707890438</v>
+        <v>9.084211850288902</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>6.382273858409668</v>
+        <v>6.395384662784608</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>3.991543753114584</v>
+        <v>4.004586649408949</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>3.369175627240153</v>
+        <v>3.382241881540629</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>6.12779868007155</v>
+        <v>6.140979689366787</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>3.916261159480648</v>
+        <v>3.929459898435411</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>1.453232748646272</v>
+        <v>1.466637876299103</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.7108450157265409</v>
+        <v>0.7243023094367587</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>2.895765807480572</v>
+        <v>2.909218096200682</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>1.937876787933526</v>
+        <v>1.951432834285129</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>1.649963711607661</v>
+        <v>1.639534075909509</v>
       </c>
     </row>
     <row r="10">
@@ -4119,46 +4119,46 @@
         <v>229</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>7.331889190707052</v>
+        <v>7.344411480382675</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>3.536909464205685</v>
+        <v>3.549819273781736</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>4.888765648438792</v>
+        <v>4.901772779856394</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>5.019018781046292</v>
+        <v>5.031997923444756</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>3.607235120559274</v>
+        <v>3.620345924934213</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1.72127094473781</v>
+        <v>1.734313841032176</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>1.199856004758104</v>
+        <v>1.21292225905858</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>1.606035051391451</v>
+        <v>1.619216060686689</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.6716727197943015</v>
+        <v>0.6848714587490647</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.6151336879410465</v>
+        <v>-0.6017285602882154</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.3832057895512051</v>
+        <v>-0.3697484958409873</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.08785859050165357</v>
+        <v>0.1013108792217636</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.1042852022641725</v>
+        <v>0.1178412486157754</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.5193559108743884</v>
+        <v>-0.5297855465725405</v>
       </c>
     </row>
     <row r="11">
@@ -4171,98 +4171,98 @@
         <v>291</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>3.176664772573531</v>
+        <v>3.189187062249154</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.153121898809971</v>
+        <v>-0.1402120892339198</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1.170222453012684</v>
+        <v>1.183229584430286</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>2.675046032355574</v>
+        <v>2.688025174754038</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.4184117588641669</v>
+        <v>0.4315225632391062</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.6587167501555697</v>
+        <v>-0.6456738538612043</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-1.430735690795544</v>
+        <v>-1.417669436495068</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-1.897919089577044</v>
+        <v>-1.884738080281807</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-2.302561587443194</v>
+        <v>-2.28936284848843</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-4.183614607522664</v>
+        <v>-4.170209479869833</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-3.013797485104853</v>
+        <v>-3.000340191394635</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-4.010342162810964</v>
+        <v>-3.996889874090854</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-3.743311550388171</v>
+        <v>-3.729755504036568</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-4.180875441479579</v>
+        <v>-4.191305077177731</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.08357</t>
+          <t>X &lt; -0.08356</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>372</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1.807636948607225</v>
+        <v>1.820159238282848</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.610388277260256</v>
+        <v>-0.5974784676842049</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.876463446250682</v>
+        <v>0.8894705776682841</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1.275533783159254</v>
+        <v>1.288512925557718</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.4682953637860123</v>
+        <v>0.4814061681609516</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-1.115983128605855</v>
+        <v>-1.102940232311489</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-1.469534050179213</v>
+        <v>-1.456467795878737</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-1.667900244659634</v>
+        <v>-1.654719235364396</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-1.728900130841936</v>
+        <v>-1.715701391887173</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-4.729562950278464</v>
+        <v>-4.716157822625632</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-3.590230253090667</v>
+        <v>-3.576772959380449</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-4.36229870864846</v>
+        <v>-4.34884641992835</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-3.707284502389065</v>
+        <v>-3.693728456037462</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-4.264014783016002</v>
+        <v>-4.274444418714154</v>
       </c>
     </row>
     <row r="13">
@@ -4275,98 +4275,98 @@
         <v>467</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>1.253885020261109</v>
+        <v>1.266407309936731</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-1.428352404266313</v>
+        <v>-1.415442594690262</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.746372036888701</v>
+        <v>0.7593791683063031</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.4483596448709406</v>
+        <v>0.4613387872694048</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.3041943325138661</v>
+        <v>-0.2910835281389268</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-1.505681730986637</v>
+        <v>-1.492638834692272</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-1.376282685946286</v>
+        <v>-1.36321643164581</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-1.201067797789889</v>
+        <v>-1.187886788494652</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-1.476200446284828</v>
+        <v>-1.463001707330065</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-4.039387729813811</v>
+        <v>-4.02598260216098</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-3.6017427671935</v>
+        <v>-3.588285473483282</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-4.209757896785959</v>
+        <v>-4.196305608065849</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-3.773481458480333</v>
+        <v>-3.75992541212873</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-3.952025650829313</v>
+        <v>-3.962455286527465</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.05916</t>
+          <t>X &lt; -0.05915</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>591</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>2.159691967438079</v>
+        <v>2.172214257113701</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.3789136167411726</v>
+        <v>0.3918234263172238</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.8300685988078556</v>
+        <v>0.8430757302254577</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>1.298731206880674</v>
+        <v>1.311710349279139</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1.267924205006466</v>
+        <v>1.281035009381405</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.8035001855350643</v>
+        <v>-0.7904572892406989</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.8882339028073432</v>
+        <v>-0.8751676485068671</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.6785983506582056</v>
+        <v>-0.6654173413629678</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.5703934991078583</v>
+        <v>-0.5571947601530951</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-2.943361323729697</v>
+        <v>-2.929956196076866</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-2.978909910314613</v>
+        <v>-2.965452616604395</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-3.45214096616715</v>
+        <v>-3.43868867744704</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-3.195576626181428</v>
+        <v>-3.182020579829825</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-2.94585529390514</v>
+        <v>-2.956284929603292</v>
       </c>
     </row>
     <row r="15">
@@ -4379,46 +4379,46 @@
         <v>760</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>2.506561679790032</v>
+        <v>2.519083969465655</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.6839593015952872</v>
+        <v>-0.671049492019236</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.368540412860753</v>
+        <v>0.3815475442783551</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1.419846177047198</v>
+        <v>1.432825319445662</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.802477593553988</v>
+        <v>1.815588397928927</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.7841300575854291</v>
+        <v>0.7971729538797945</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.0900773438973772</v>
+        <v>-0.07701108959690117</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.100633994163239</v>
+        <v>0.1138150034584768</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.03963410798093747</v>
+        <v>0.05283284693570067</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-1.599964761257525</v>
+        <v>-1.586559633604693</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.541560190838254</v>
+        <v>-1.528102897128036</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-2.16507177033494</v>
+        <v>-2.15161948161483</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-2.190589539174574</v>
+        <v>-2.177033492822972</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-1.414552417424595</v>
+        <v>-1.424982053122747</v>
       </c>
     </row>
     <row r="16">
@@ -4431,46 +4431,46 @@
         <v>940</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>2.87319292314816</v>
+        <v>2.885715212823783</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.3051899796844282</v>
+        <v>0.3180997892604793</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.7128853176759833</v>
+        <v>0.6672178837828113</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.949521429006893</v>
+        <v>0.9625005714053572</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.9430151075517372</v>
+        <v>0.9561259119266765</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.4957761942035717</v>
+        <v>0.5088190904979371</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.01448943796232527</v>
+        <v>-0.001423183661849237</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.475773971766813</v>
+        <v>0.4889549810620508</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.3083911068611087</v>
+        <v>0.3215898458158719</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.073648971783832</v>
+        <v>-1.060243844131001</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-1.491168253548231</v>
+        <v>-1.477710959838014</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.669551053649599</v>
+        <v>-1.656098764929489</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.770656728424292</v>
+        <v>-1.757100682072689</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.095403481254387</v>
+        <v>-1.105833116952539</v>
       </c>
     </row>
     <row r="17">
@@ -4483,46 +4483,46 @@
         <v>1203</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>2.021888937453653</v>
+        <v>2.034411227129276</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.2446152416393517</v>
+        <v>0.2575250512154028</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1.470268613960513</v>
+        <v>1.436904453535753</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.646970003210122</v>
+        <v>1.613500888966477</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.238130679757866</v>
+        <v>1.204647144380111</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1.415993381731205</v>
+        <v>1.382502556957256</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.7493810277174475</v>
+        <v>0.7624472820179236</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.2821976289359469</v>
+        <v>0.2953786382311847</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.6368253404261282</v>
+        <v>0.6500240793808914</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.2964253641362902</v>
+        <v>-0.2830202364834591</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.5011786884538694</v>
+        <v>-0.4877213947436516</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.298050726453404</v>
+        <v>-1.284598437733294</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.468928778794819</v>
+        <v>-1.455372732443216</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.02767534649892411</v>
+        <v>0.01724571080077197</v>
       </c>
     </row>
     <row r="18">
@@ -4535,98 +4535,98 @@
         <v>1532</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.608124179790025</v>
+        <v>1.620646469465647</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.647592233492432</v>
+        <v>0.6605020430684831</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1.59132457195556</v>
+        <v>1.56781399164678</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1.888521123866667</v>
+        <v>1.864850006570649</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>1.191103267327456</v>
+        <v>1.167643568449748</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1.655711753339176</v>
+        <v>1.632051245499255</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>1.309881430322768</v>
+        <v>1.322947684623244</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.8426980315412678</v>
+        <v>0.8558790408365056</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.7816981453589662</v>
+        <v>0.7948968843137294</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.5906202511572047</v>
+        <v>-0.5772151235043737</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.7953735754747839</v>
+        <v>-0.7819162817645662</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.805376841105854</v>
+        <v>-1.791924552385744</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.768712391998541</v>
+        <v>-1.755156345646938</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.8662495453619385</v>
+        <v>-0.8766791810600907</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; 0.001869</t>
+          <t>X &lt; 0.001866</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>1956</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.9486830464396903</v>
+        <v>0.9339667421465876</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.02337928011300505</v>
+        <v>-0.03804806954412498</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.7323807180648103</v>
+        <v>0.7172081242998374</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1.401567589874475</v>
+        <v>1.386077515786447</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.9938419267169891</v>
+        <v>0.9784022251425171</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.217614074375874</v>
+        <v>1.202129520052509</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.9795061239747653</v>
+        <v>0.9925723782752414</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.6656969583220942</v>
+        <v>0.678877967617332</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.7069465608923551</v>
+        <v>0.7201452998471183</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.2965528572644089</v>
+        <v>-0.2831477296115779</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.3479319484531516</v>
+        <v>-0.3344746547429338</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-1.336043678633281</v>
+        <v>-1.322591389913171</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.347300334567969</v>
+        <v>-1.333744288216366</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.9953295135391258</v>
+        <v>-1.005759149237278</v>
       </c>
     </row>
     <row r="20">
@@ -4636,101 +4636,101 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2358</v>
+        <v>2359</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.3806107076852143</v>
+        <v>0.3707949960816137</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.102176227502305</v>
+        <v>0.09217513760216178</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.9146709676741835</v>
+        <v>0.9042469990463644</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1.195332289705064</v>
+        <v>1.184806795979647</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1.188479643556207</v>
+        <v>1.177850909900769</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.509681229033745</v>
+        <v>1.498964477566233</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1.236862888038395</v>
+        <v>1.226239094312689</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.9815438960365555</v>
+        <v>0.9947249053317933</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.9205440098542539</v>
+        <v>0.9337427488090171</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.1127917061822572</v>
+        <v>0.1261968338350883</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.2190802622031143</v>
+        <v>-0.2056229684928965</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.9239682697436962</v>
+        <v>-0.9339566805443553</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.9627052884885074</v>
+        <v>-0.9491492421369045</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.4773174725560736</v>
+        <v>-0.4690685304436499</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 0.02628</t>
+          <t>X &lt; 0.02627</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2699</v>
+        <v>2700</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.05621527737392995</v>
+        <v>-0.06304965917960459</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.05994359183695508</v>
+        <v>-0.06699134073259927</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.4890328857280721</v>
+        <v>0.4817264177642571</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.7135517904337192</v>
+        <v>0.7061749907414239</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.046093289598829</v>
+        <v>1.038518644061817</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.216252260985165</v>
+        <v>1.208649129526016</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1.152179853500272</v>
+        <v>1.144584798013362</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.7590156997224682</v>
+        <v>0.772196709017706</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.5499773235327581</v>
+        <v>0.5631760624875213</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.1521093714877608</v>
+        <v>-0.1387042438349297</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.4102053320140371</v>
+        <v>-0.4174246470988194</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.6884635832004307</v>
+        <v>-0.6955798081995184</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.7383478237749657</v>
+        <v>-0.7247917774233628</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.430854751622455</v>
+        <v>-0.4249820531227471</v>
       </c>
     </row>
     <row r="22">
@@ -4740,101 +4740,101 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2966</v>
+        <v>2967</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.07408348150030264</v>
+        <v>-0.07916930564352498</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.3234993281322147</v>
+        <v>-0.3286612633831325</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.2412088020583596</v>
+        <v>0.2358155672770295</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.1880583320563147</v>
+        <v>0.1826925901779788</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.677415611546472</v>
+        <v>0.6718296569796749</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.5896624850863645</v>
+        <v>0.5841319394999758</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.6245248180732119</v>
+        <v>0.6189711244370102</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.3106994069373314</v>
+        <v>0.3052025632670805</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.5865132627557088</v>
+        <v>0.599712001710472</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.02784230287174694</v>
+        <v>-0.01443717521891585</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.44956132575102</v>
+        <v>-0.4549079528795801</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.5311778849642792</v>
+        <v>-0.5364967691733469</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.4121672448138014</v>
+        <v>-0.3986111984621985</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.312057474740854</v>
+        <v>-0.3076918610095092</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.05069</t>
+          <t>X &lt; 0.05068</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3188</v>
+        <v>3189</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.0229730583458192</v>
+        <v>0.0190839694656475</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.1025103696970504</v>
+        <v>-0.1064816171899281</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.05126105556855265</v>
+        <v>0.04721029402326593</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.1768865810056184</v>
+        <v>-0.1808585618245999</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.1154254561682606</v>
+        <v>0.111319904417293</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.1170074922491153</v>
+        <v>0.1129212447948831</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.112050666388285</v>
+        <v>0.1079574369166281</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.02467928904479066</v>
+        <v>-0.02876663070837537</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.1022907495849452</v>
+        <v>0.1154894885397084</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.3718945858189286</v>
+        <v>-0.3584894581660976</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.6845445712502709</v>
+        <v>-0.6885038996343127</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.8208216465929752</v>
+        <v>-0.8247379562721662</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.721972087737889</v>
+        <v>-0.7259528130671526</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.7683792681146926</v>
+        <v>-0.764900522862483</v>
       </c>
     </row>
     <row r="24">
@@ -4844,205 +4844,205 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3378</v>
+        <v>3379</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.2066280516941958</v>
+        <v>-0.2095295998558839</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.5335833617456629</v>
+        <v>-0.5364809964220285</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.4402408405384577</v>
+        <v>-0.4431899192150865</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.6188891728455417</v>
+        <v>-0.6217797494710808</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.196084172752478</v>
+        <v>-0.1991316567855321</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.207533498467825</v>
+        <v>-0.2105624111205842</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.3353050303170875</v>
+        <v>-0.3383026162859579</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.2541856391898207</v>
+        <v>-0.257235294470803</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.2560489198132814</v>
+        <v>-0.2428501808585182</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.6035129575910574</v>
+        <v>-0.5901078299382263</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.9693221423007685</v>
+        <v>-0.9722188048749416</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-1.007332748223448</v>
+        <v>-1.010217840866986</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.9673219888248852</v>
+        <v>-0.9702443305682138</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.9675423522973148</v>
+        <v>-0.9647867290623893</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.0751</t>
+          <t>X &lt; 0.07509</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3531</v>
+        <v>3532</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.2213525172181576</v>
+        <v>-0.2235796874192317</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.4912344063532288</v>
+        <v>-0.4934569076794659</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.5038343251704234</v>
+        <v>-0.5060717014644496</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.6973111229825264</v>
+        <v>-0.6994893701305784</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.3446127233657563</v>
+        <v>-0.3469153189904901</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.5122461287821238</v>
+        <v>-0.5144895734472783</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.6382299561319513</v>
+        <v>-0.6404427042468654</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.4113926788541491</v>
+        <v>-0.4136912090618026</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.3875509360771758</v>
+        <v>-0.3743521971224126</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.5998158741883657</v>
+        <v>-0.6020990477509116</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.015244401364569</v>
+        <v>-1.017420249915951</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.9652192519742187</v>
+        <v>-0.9674089552990282</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.9451344518526454</v>
+        <v>-0.9473494610622737</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.8778772545812146</v>
+        <v>-0.8757181799630729</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.0873</t>
+          <t>X &lt; 0.08729</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3641</v>
+        <v>3642</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.4135258954699594</v>
+        <v>-0.4152525558421516</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.6147299731413867</v>
+        <v>-0.6164589927826398</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.6663647580621728</v>
+        <v>-0.6680944226702223</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.9322131001515501</v>
+        <v>-0.9338663275249885</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.4970898181259074</v>
+        <v>-0.4988820427578418</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.732832051716322</v>
+        <v>-0.7345501895953319</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.6657352386342126</v>
+        <v>-0.6674756725395952</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.6245474815991088</v>
+        <v>-0.6263165754889073</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.6705890637718213</v>
+        <v>-0.6723486288266471</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.7924418387248551</v>
+        <v>-0.7941988633301307</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.091794173159592</v>
+        <v>-1.093477238330848</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-1.124612056680775</v>
+        <v>-1.126285840156626</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-1.090413233500996</v>
+        <v>-1.092112158468694</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-1.072613389684975</v>
+        <v>-1.070781064654881</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 0.09951</t>
+          <t>X &lt; 0.0995</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3744</v>
+        <v>3745</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.2176863904788036</v>
+        <v>-0.2190746255316895</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.5640108682115113</v>
+        <v>-0.5653520570557333</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.7848340352435272</v>
+        <v>-0.7861280344448005</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.9599311832421691</v>
+        <v>-0.9611756617022706</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.6847606859978228</v>
+        <v>-0.686094018020377</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.9059159529633334</v>
+        <v>-0.9071828597149434</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.8696940075239112</v>
+        <v>-0.8709736078327879</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.7891905672402828</v>
+        <v>-0.7905052479832548</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.9157083693112611</v>
+        <v>-0.9169917144678124</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.9775977444625994</v>
+        <v>-0.9788888161235363</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.221023059378702</v>
+        <v>-1.222255568026199</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.225332539717009</v>
+        <v>-1.226563647473832</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-1.203659597497953</v>
+        <v>-1.204908840562318</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-1.179509682381862</v>
+        <v>-1.177986058463212</v>
       </c>
     </row>
     <row r="28">
@@ -5052,49 +5052,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3830</v>
+        <v>3831</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.268613964238078</v>
+        <v>-0.2696777370900207</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.4090202621695482</v>
+        <v>-0.4100828678084341</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.6597348444050297</v>
+        <v>-0.6607412855525965</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.8540025071633224</v>
+        <v>-0.8549560971262267</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.5188848774842469</v>
+        <v>-0.5199379178605597</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.7544316933265023</v>
+        <v>-0.7554174959358093</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.7730053441168394</v>
+        <v>-0.773988682092984</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.7047553917102078</v>
+        <v>-0.7057671810881203</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.7776306967950291</v>
+        <v>-0.7786253606270108</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.8571648820603102</v>
+        <v>-0.8581577945873349</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-1.021423428373794</v>
+        <v>-1.022378492219062</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.9987164247685101</v>
+        <v>-0.9996772074582623</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-1.013007761708195</v>
+        <v>-1.01397448831797</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-1.035962339095619</v>
+        <v>-1.034744517231346</v>
       </c>
     </row>
     <row r="29">
@@ -5104,49 +5104,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3886</v>
+        <v>3887</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.30056835355186</v>
+        <v>-0.3014288510471701</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.4108097782229763</v>
+        <v>-0.4116712438854364</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.5352924950441107</v>
+        <v>-0.5361295370859054</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.6991962956643505</v>
+        <v>-0.6999893963276023</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.5306417902714387</v>
+        <v>-0.5314882258687703</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.6814850587879349</v>
+        <v>-0.6822878933602539</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.7523659320515463</v>
+        <v>-0.7531525217597377</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.6918147536054633</v>
+        <v>-0.6926257065878971</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.6874148173393024</v>
+        <v>-0.68822843937361</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.7780191517324226</v>
+        <v>-0.7788251856884472</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.9428404550111651</v>
+        <v>-0.9436082414657463</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.8942249000728637</v>
+        <v>-0.8950050089456241</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.8886112850752141</v>
+        <v>-0.8894008309213035</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.9333378008522857</v>
+        <v>-0.93231418587294</v>
       </c>
     </row>
     <row r="30">
@@ -5156,49 +5156,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3932</v>
+        <v>3933</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.300789397523026</v>
+        <v>-0.30149383083846</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.3271214666427937</v>
+        <v>-0.3278435684650987</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.5054601477596563</v>
+        <v>-0.5061432852294914</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.5644524691115649</v>
+        <v>-0.5651190723479189</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.4802385217787517</v>
+        <v>-0.4809348737205141</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.5750737895959688</v>
+        <v>-0.5757420156042983</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.6968637310381069</v>
+        <v>-0.6975026738875698</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.6170693551190709</v>
+        <v>-0.6177358844238441</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.6134145665374717</v>
+        <v>-0.6140833007214184</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.6112505978001082</v>
+        <v>-0.6119329475092172</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.7510833634457654</v>
+        <v>-0.7517336202773777</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.7025854834433289</v>
+        <v>-0.7032479173802244</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.7273299409035303</v>
+        <v>-0.7279927414784169</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.7685707287165684</v>
+        <v>-0.7677229633693869</v>
       </c>
     </row>
     <row r="31">
@@ -5208,49 +5208,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3965</v>
+        <v>3966</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.2309948812959419</v>
+        <v>-0.2316071589585817</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.2453186970666152</v>
+        <v>-0.2459482774443345</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.375132148825152</v>
+        <v>-0.3757344588183926</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.4828350543331297</v>
+        <v>-0.4834089281451455</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.4540980428192825</v>
+        <v>-0.4546863455335028</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.4449888635533057</v>
+        <v>-0.445575966735781</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.6167906528495095</v>
+        <v>-0.617335913738799</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.5163390604829488</v>
+        <v>-0.5169159023559189</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.4880074139599415</v>
+        <v>-0.4885924867334097</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.4425076263567789</v>
+        <v>-0.4431153806549375</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.5828377799723796</v>
+        <v>-0.5834131303831427</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.6352467666864143</v>
+        <v>-0.6358087855197496</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.6380508550967505</v>
+        <v>-0.6386178798050466</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.676847499391819</v>
+        <v>-0.6761166976008184</v>
       </c>
     </row>
     <row r="32">
@@ -5260,49 +5260,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4000</v>
+        <v>4001</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.1635105853482699</v>
+        <v>-0.1640251486210502</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.2416021624863021</v>
+        <v>-0.2421145831047866</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.1992074909301351</v>
+        <v>-0.1997349241059538</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.3546649136471061</v>
+        <v>-0.3551524784522115</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.3059035488755555</v>
+        <v>-0.3064092395563165</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.2692894192503701</v>
+        <v>-0.2698013539276332</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.4153305192615377</v>
+        <v>-0.4158071816233715</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.3697131167493453</v>
+        <v>-0.3702063801728102</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.3670943235848725</v>
+        <v>-0.367589151645376</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.3293932275280937</v>
+        <v>-0.3299067654793291</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.4452771399685176</v>
+        <v>-0.445764183210386</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.4968927019743745</v>
+        <v>-0.4973667501108281</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.478320238078787</v>
+        <v>-0.4788036603707795</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.4895524174245978</v>
+        <v>-0.4889660571217576</v>
       </c>
     </row>
     <row r="33">
@@ -5312,49 +5312,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4039</v>
+        <v>4040</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.1982754376828311</v>
+        <v>-0.1986559762535691</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.2170830267313804</v>
+        <v>-0.2174723111598809</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.2035843434745246</v>
+        <v>-0.2039803955415707</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.3068959685118031</v>
+        <v>-0.3072656487154717</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.2143728329074293</v>
+        <v>-0.2147699751586458</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.2493515337167693</v>
+        <v>-0.2497378012689495</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.3453652175607687</v>
+        <v>-0.3457286581662089</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.3046747040346744</v>
+        <v>-0.3050522338389285</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.3521093456085325</v>
+        <v>-0.3524758512622128</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.2487664587984284</v>
+        <v>-0.2491657036760131</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.3654878972889435</v>
+        <v>-0.3658601643996136</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.4657464339799446</v>
+        <v>-0.4660938168839692</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.4018975120771344</v>
+        <v>-0.4022643502188714</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.4105910408462421</v>
+        <v>-0.4101305679742353</v>
       </c>
     </row>
     <row r="34">
@@ -5364,49 +5364,49 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4064</v>
+        <v>4065</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.003862651826359809</v>
+        <v>-0.004211763736904572</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.08145943072084805</v>
+        <v>-0.0818004311772853</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.09497266431069562</v>
+        <v>-0.09531315506568205</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.1722784644534556</v>
+        <v>-0.1725992850102571</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.08359500261849462</v>
+        <v>-0.08394135428666516</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.116500694146545</v>
+        <v>-0.1168371511766111</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.187848485088594</v>
+        <v>-0.1881681571183478</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.07652881457852345</v>
+        <v>-0.07687912316242773</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.1977189206954577</v>
+        <v>-0.1980400355161365</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.1493618528064502</v>
+        <v>-0.1497007131405894</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.217423687790621</v>
+        <v>-0.217747362273208</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.2922237624647934</v>
+        <v>-0.2925289842871663</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.2313094200575918</v>
+        <v>-0.2316326074319193</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.2383713150624018</v>
+        <v>-0.2380201835040552</v>
       </c>
     </row>
     <row r="35">
@@ -5416,49 +5416,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4089</v>
+        <v>4090</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.1150453462941741</v>
+        <v>0.1147456804088591</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.04502656375213832</v>
+        <v>-0.04529568771324932</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.0852464934293522</v>
+        <v>-0.08550798774849255</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.01490684358683581</v>
+        <v>-0.01518495013070975</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.06998934511442911</v>
+        <v>0.0696876005585807</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.01472882690315913</v>
+        <v>0.01444196828991551</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.05666862679210993</v>
+        <v>-0.05693863606864369</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.002311264261557255</v>
+        <v>0.002024296221627253</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.0940660437173193</v>
+        <v>-0.09432993180602978</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.05117157134406369</v>
+        <v>-0.05145048800008567</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.1200445248404236</v>
+        <v>-0.1203078169526535</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.1697096789662069</v>
+        <v>-0.1699607894298225</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.1117065125370829</v>
+        <v>-0.1119741198733593</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.1171691941426332</v>
+        <v>-0.1169135934650498</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/btc_daily_14days/roc/roc_5.xlsx
+++ b/workspaces/btc_daily_14days/roc/roc_5.xlsx
@@ -568,469 +568,469 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ -0.1507</t>
+          <t>X ≈ -0.1506</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>26</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>16.695799892627</v>
+        <v>16.66684611571527</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>11.2592058107804</v>
+        <v>11.25811239425642</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>10.86776472661573</v>
+        <v>10.86769395440176</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>14.83721451529629</v>
+        <v>14.83682169828336</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>10.46627533834094</v>
+        <v>10.51477558815385</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>3.088692130534987</v>
+        <v>3.112617810005908</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>10.68400865579012</v>
+        <v>10.7319854331504</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>17.90104633098604</v>
+        <v>17.95029171946178</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>14.00324994115014</v>
+        <v>14.07646159496358</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>9.315176460798739</v>
+        <v>9.414449118404278</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>16.79961422241087</v>
+        <v>16.89948041698761</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>16.8380462773658</v>
+        <v>16.96170338552266</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>16.42214896725419</v>
+        <v>16.57081223289838</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>8.959633331492633</v>
+        <v>9.131632091061043</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ -0.1385</t>
+          <t>X ≈ -0.1384</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>38</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>13.26472406144678</v>
+        <v>13.23574635175674</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>11.6623330612419</v>
+        <v>11.6612458233316</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>8.646636199115704</v>
+        <v>8.646551537132062</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>11.40386023459686</v>
+        <v>11.40344744064041</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>10.86985942209488</v>
+        <v>10.91836241375022</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>8.543344122151943</v>
+        <v>8.567299036458103</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.5798278640555594</v>
+        <v>0.6277570950834104</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>5.368694370179298</v>
+        <v>5.417890056030373</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>5.309320398569866</v>
+        <v>5.382502692648842</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-8.683281818520697</v>
+        <v>-8.584058622761148</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>1.628536270582877</v>
+        <v>1.728371556998745</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>1.663266332442696</v>
+        <v>1.786902643868437</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-4.018182563808558</v>
+        <v>-3.86953336964887</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-11.6881399478596</v>
+        <v>-11.51614118829173</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ -0.1263</t>
+          <t>X ≈ -0.1262</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>38</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-5.097307742538931</v>
+        <v>-5.126443142824535</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>1.16693048764806</v>
+        <v>1.16576035777075</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>6.021832472099398</v>
+        <v>6.021730527300278</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>6.153316204915775</v>
+        <v>6.152870349490186</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>2.992429867811353</v>
+        <v>3.0408845454172</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>8.543021051280029</v>
+        <v>8.566976805162291</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>8.460711540350957</v>
+        <v>8.508677246358651</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.1132855438570886</v>
+        <v>0.1624589619462427</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.05262602584679854</v>
+        <v>0.1257891429164459</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.796292930681112</v>
+        <v>-0.6970508007066201</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-11.51949170079848</v>
+        <v>-11.419684915978</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-11.48805018100419</v>
+        <v>-11.36443310077092</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-11.91092206135499</v>
+        <v>-11.7622791266083</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-6.424982053122754</v>
+        <v>-6.252983293556092</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ -0.1141</t>
+          <t>X ≈ -0.114</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>43</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>3.320796255709546</v>
+        <v>3.291738105292929</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-2.921086378760194</v>
+        <v>-2.922290405929061</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-12.5924767544625</v>
+        <v>-12.5927205668827</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-12.46567377094773</v>
+        <v>-12.46624860471199</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-8.364920067104251</v>
+        <v>-8.316538716007464</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-8.069912097571191</v>
+        <v>-8.046048877632558</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-8.156376078245586</v>
+        <v>-8.108492303888418</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-17.91316424266664</v>
+        <v>-17.86406842914242</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-13.33310555985613</v>
+        <v>-13.25999146740867</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-9.538942099381586</v>
+        <v>-9.439726790072982</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-5.098249374564446</v>
+        <v>-4.998431585051641</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-12.03845022590698</v>
+        <v>-11.91483587276618</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-7.811533356621091</v>
+        <v>-7.662888655950866</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-9.913354146147064</v>
+        <v>-9.741355386580402</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -0.1019</t>
+          <t>X ≈ -0.1018</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-12.11921557088648</v>
+        <v>-12.78631538248906</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-13.72767739389591</v>
+        <v>-14.36704000245624</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-12.51675496545323</v>
+        <v>-11.59793224362755</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-5.954984271124829</v>
+        <v>-5.138359224473433</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-11.32081244169935</v>
+        <v>-10.37845909783226</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-9.417040941677527</v>
+        <v>-8.524513782179014</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-11.11389939147742</v>
+        <v>-10.17158105510075</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-14.80396348955512</v>
+        <v>-13.80905152355994</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-13.25773080844518</v>
+        <v>-12.26414045439075</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-17.33260250341218</v>
+        <v>-16.26154588800003</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-12.70666912871604</v>
+        <v>-11.71150078611888</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-19.12390892585186</v>
+        <v>-18.00235383258023</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-17.93640434578427</v>
+        <v>-16.81515476507155</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-17.71530463376718</v>
+        <v>-16.57044361101713</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.08966</t>
+          <t>X ≈ -0.08962</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>81</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-3.088487146161903</v>
+        <v>-1.887181755474643</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-2.233111889982268</v>
+        <v>-1.003576362986294</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.1656828064190137</v>
+        <v>-0.1658690927776405</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-3.730101067701455</v>
+        <v>-3.730647606854134</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.6589658497053605</v>
+        <v>0.7073660508711512</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-2.739805981175884</v>
+        <v>-2.715942759651405</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-1.59264488665611</v>
+        <v>-2.777063334501918</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.8267566431760969</v>
+        <v>-2.010243157075621</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.3450953873726732</v>
+        <v>-0.8147169927558267</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-6.670105994710354</v>
+        <v>-6.570903045505581</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-5.642974008240564</v>
+        <v>-5.543172238940905</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-5.610136194554137</v>
+        <v>-5.486524027630246</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-3.563268060741834</v>
+        <v>-3.414626340504057</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-4.573130201271461</v>
+        <v>-4.401131441703676</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.07746</t>
+          <t>X ≈ -0.07742</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.8994712970666114</v>
+        <v>-1.441927000360153</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-4.603268139298159</v>
+        <v>-5.140319406409255</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.2489509176319729</v>
+        <v>-0.2313359006488156</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-2.77058623348789</v>
+        <v>-3.284867188939621</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-3.308089388290448</v>
+        <v>-3.7735974506787</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-3.011842981003646</v>
+        <v>-3.501999914613513</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.9958287080539208</v>
+        <v>-0.3778614009619901</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.6394321705346471</v>
+        <v>1.281165791614107</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.472521676587462</v>
+        <v>0.1821678371740774</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-1.321399035411865</v>
+        <v>-1.703194320805892</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-3.630085471146472</v>
+        <v>-4.033798896983484</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-3.596778045993787</v>
+        <v>-3.976816376190321</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-4.01793731808953</v>
+        <v>-4.373082507015958</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-2.74077152680649</v>
+        <v>-3.061493931853967</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.06526</t>
+          <t>X ≈ -0.06523</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>124</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>5.562803394872041</v>
+        <v>5.499242260868996</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>7.174849546541743</v>
+        <v>7.912828376495128</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1.154428037360738</v>
+        <v>0.280006378459845</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>4.501572723196411</v>
+        <v>5.239245630708744</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>7.183866031732137</v>
+        <v>7.157940201092202</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1.850380359626044</v>
+        <v>2.603399477124533</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.9614348171015692</v>
+        <v>1.737072328174641</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>1.300421812057571</v>
+        <v>2.070553347172634</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>2.850573792868481</v>
+        <v>3.283864616701806</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>1.197134137208387</v>
+        <v>1.646841950480301</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.6188239031954126</v>
+        <v>-0.5190139988264519</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.5847419250960755</v>
+        <v>-0.4611258535368847</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-1.005122404667873</v>
+        <v>-0.8564812466733684</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.8330824630064626</v>
+        <v>1.005081222572947</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.05305</t>
+          <t>X ≈ -0.05303</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>169</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>3.71655043452018</v>
+        <v>3.66688217294967</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-4.372747691840942</v>
+        <v>-5.016921084851568</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-1.228947338626597</v>
+        <v>-0.6914283570711177</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>1.850294674997997</v>
+        <v>1.803655014836224</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>3.6746821573755</v>
+        <v>3.673083889245341</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>6.334690114586351</v>
+        <v>6.901380621695516</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>2.709015390805718</v>
+        <v>3.294434643696611</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>2.834120542746412</v>
+        <v>3.150360515168906</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>2.183174366116276</v>
+        <v>2.521909787746296</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>3.108369042641122</v>
+        <v>3.208355656083825</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>3.495795131501808</v>
+        <v>3.595607986149801</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>2.348317142852387</v>
+        <v>2.471931660075867</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>1.337233130449263</v>
+        <v>1.485872233335542</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>3.930047532675928</v>
+        <v>4.102046292242591</v>
       </c>
     </row>
     <row r="15">
@@ -1040,49 +1040,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>4.434342529858363</v>
+        <v>4.097459656633326</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>4.480669734014597</v>
+        <v>4.161822294331238</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1.871529652563829</v>
+        <v>1.562960867099711</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-1.021166324592905</v>
+        <v>-1.614902958188452</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-2.666437763501925</v>
+        <v>-3.209970344546413</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.7073105132557558</v>
+        <v>-1.281789321091544</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.3171859535410206</v>
+        <v>-0.2398485390236686</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>2.069088990896255</v>
+        <v>2.05290115450839</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>1.454199993012466</v>
+        <v>1.463353481397768</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>1.161080050863049</v>
+        <v>1.185803761159221</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.26338137637353</v>
+        <v>-1.2279214646125</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.4361770121931841</v>
+        <v>0.2468964507041278</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.01611943890651446</v>
+        <v>-0.1482271798377965</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.2416846135439101</v>
+        <v>0.1006078666650225</v>
       </c>
     </row>
     <row r="16">
@@ -1092,985 +1092,985 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.9782342356220184</v>
+        <v>-0.8120169535832176</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.04422493979240727</v>
+        <v>-0.1308310163819613</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>4.199127581021223</v>
+        <v>3.995131352986292</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>3.951966744867967</v>
+        <v>3.74930358137032</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>2.098610053512594</v>
+        <v>1.754677818575864</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>4.500008449570736</v>
+        <v>3.912863882487223</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>3.484547758311976</v>
+        <v>2.722412089230396</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.3958686541837366</v>
+        <v>-1.137161814266186</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>1.820817531520952</v>
+        <v>1.088580141358875</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>2.492064991718458</v>
+        <v>1.773999579787834</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>3.048087573158163</v>
+        <v>2.324297120856855</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.04355042058030989</v>
+        <v>-0.6343786601176546</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.3766253571273737</v>
+        <v>-1.029792887668265</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>4.031291711135793</v>
+        <v>3.36965821587787</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -0.01644</t>
+          <t>X ≈ -0.01646</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>329</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.09948175293579453</v>
+        <v>-0.2420614321064178</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>2.132200267421609</v>
+        <v>2.109023694946124</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>2.04110541424653</v>
+        <v>2.323611156651211</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>2.777094500773273</v>
+        <v>3.062863780729053</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.028075670244689</v>
+        <v>1.660180557620613</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>2.537155054299589</v>
+        <v>3.01018312794335</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>3.362865294871696</v>
+        <v>3.721423129018589</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>2.89864850116426</v>
+        <v>3.256071039834289</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1.321806103304219</v>
+        <v>1.70043711611973</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-1.650134781931257</v>
+        <v>-1.2485357239186</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.85521213819473</v>
+        <v>-1.452448485097179</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-3.643756811530636</v>
+        <v>-3.216412220990314</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-2.849987832432703</v>
+        <v>-2.397511012051545</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-4.145346794764095</v>
+        <v>-3.669396667416351</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ -0.004237</t>
+          <t>X ≈ -0.004266</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>424</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-1.542865045658004</v>
+        <v>-1.223948497283068</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-2.560936248261712</v>
+        <v>-2.349369710132123</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-2.359686741902067</v>
+        <v>-2.271174928848609</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.349555236474437</v>
+        <v>-0.4887027146199614</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.290659616834958</v>
+        <v>-0.1489760215444775</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.3540572926029313</v>
+        <v>-0.8170966184374322</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.202710477562448</v>
+        <v>-0.6433265714610243</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.03807339868462378</v>
+        <v>-0.4049915979873902</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.4482398387256552</v>
+        <v>0.02920031093273678</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.7787680958255976</v>
+        <v>0.3769688159767099</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>1.281248257987642</v>
+        <v>1.11462380940366</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.3739017038090466</v>
+        <v>0.2269042096501934</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.1893265842845295</v>
+        <v>-0.03410576245532582</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.472151864443511</v>
+        <v>-1.536002161480567</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ 0.007968</t>
+          <t>X ≈ 0.007924</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-2.36079949499414</v>
+        <v>-2.507346287174293</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.7241604606684717</v>
+        <v>0.6091015371186472</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.814825350403638</v>
+        <v>1.699803447703616</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.2144330756115238</v>
+        <v>0.3458274398868681</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>2.148736867219995</v>
+        <v>2.331825823687396</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>2.942015026182695</v>
+        <v>3.099660847456761</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>2.361697421957459</v>
+        <v>2.543955253280863</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>2.52309494990287</v>
+        <v>2.325647245372799</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1.968578811647355</v>
+        <v>2.041149883760696</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>2.109506133348113</v>
+        <v>2.207420312846729</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.4182191680993057</v>
+        <v>0.5181313504592211</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.9469866832090048</v>
+        <v>1.071347592774593</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.9177329523052009</v>
+        <v>0.9237144186859609</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>2.135811991542198</v>
+        <v>1.915333538127072</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 0.02017</t>
+          <t>X ≈ 0.02012</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-3.066270699436949</v>
+        <v>-2.953959821568183</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-1.168362761122992</v>
+        <v>-1.016324715911452</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-2.440362683632927</v>
+        <v>-2.290905443741664</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-2.602491089851569</v>
+        <v>-2.886554621848745</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.0761756950532515</v>
+        <v>-0.1405096451535996</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.7961522831122494</v>
+        <v>-1.04419471456994</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.5813368195154567</v>
+        <v>0.3657374314986939</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.7632841466706495</v>
+        <v>-0.688330623002372</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-1.994787360703015</v>
+        <v>-2.195891467433185</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-1.969756117152187</v>
+        <v>-2.137367107071732</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-1.884163049069592</v>
+        <v>-2.047389907549068</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.9544648107016513</v>
+        <v>0.6578356533453089</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.8276689357953231</v>
+        <v>0.5567953738403659</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.1199967158792816</v>
+        <v>-0.3706303523796208</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 0.03238</t>
+          <t>X ≈ 0.03231</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.2425275792115045</v>
+        <v>-0.1112094252039952</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-2.976649069669854</v>
+        <v>-2.799308710939087</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-2.249760456484879</v>
+        <v>-2.088502913117779</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-5.107681050886399</v>
+        <v>-4.541644702161399</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-3.030662870198604</v>
+        <v>-2.447868012854926</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-5.721434578553364</v>
+        <v>-5.127112014331246</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-4.685675312703559</v>
+        <v>-4.449760723482868</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-4.406982921447288</v>
+        <v>-4.177586103792365</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.964955649891003</v>
+        <v>0.951492947587397</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>1.241804683087508</v>
+        <v>1.234675436883123</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.8327519122912221</v>
+        <v>-0.8144834608374651</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1.07312806269595</v>
+        <v>1.088701726711925</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>2.898700824310595</v>
+        <v>2.907565940369494</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.8783887333940967</v>
+        <v>0.942588662163466</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.04458</t>
+          <t>X ≈ 0.0445</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>222</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.33362460218811</v>
+        <v>1.06935387329262</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>2.863488826190043</v>
+        <v>2.866393544689139</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-2.473544396378038</v>
+        <v>-2.685225096555691</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-5.040545354271053</v>
+        <v>-4.807593307593265</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-7.375353222260301</v>
+        <v>-7.098644250346979</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-6.178903825464786</v>
+        <v>-6.375408281077654</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-6.713355920739595</v>
+        <v>-5.985613919852611</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-4.486259249471331</v>
+        <v>-4.649644878434209</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-6.343963773316091</v>
+        <v>-5.587518388471857</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-4.957315987620703</v>
+        <v>-5.059995617935584</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-3.821773353921643</v>
+        <v>-3.462334263669774</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-4.689041881358513</v>
+        <v>-4.305068427205825</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-5.109565624117778</v>
+        <v>-5.150676804220055</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-6.875432503573158</v>
+        <v>-6.703433744006546</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.05679</t>
+          <t>X ≈ 0.05669</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-4.049926385782555</v>
+        <v>-3.551778491553655</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-7.755753496885823</v>
+        <v>-7.739122243376165</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-8.676028421317049</v>
+        <v>-8.653693565024241</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-8.019282753133105</v>
+        <v>-8.523809523809533</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-5.408619007848976</v>
+        <v>-5.888058664761537</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-5.636748517890048</v>
+        <v>-5.615273145942524</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-7.820930573562748</v>
+        <v>-8.280095901834734</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-4.08575062354852</v>
+        <v>-3.537595328884656</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-6.247475707627004</v>
+        <v>-6.699567938021517</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-4.473851596783483</v>
+        <v>-3.877563185503043</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-5.738629212917424</v>
+        <v>-5.644203633039275</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-4.125303692141202</v>
+        <v>-4.023536895674297</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-5.071770334928203</v>
+        <v>-4.418694822238187</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-4.319718895228078</v>
+        <v>-4.169649960222756</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.06899</t>
+          <t>X ≈ 0.06889</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.5397081473604075</v>
+        <v>-0.5620598768350433</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.4438274274225762</v>
+        <v>0.4521656354117027</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.908055179426988</v>
+        <v>-1.889624300954907</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-2.433526631735937</v>
+        <v>-2.409090909090921</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-3.618157875481472</v>
+        <v>-3.547690699393449</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-7.235629950385452</v>
+        <v>-7.171009076678452</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-7.324082271750527</v>
+        <v>-7.23166516590387</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-3.876304810998228</v>
+        <v>-3.801394030183324</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-3.285332333722714</v>
+        <v>-3.189015989969462</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.8897837002744353</v>
+        <v>-0.7660913240312723</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-2.016578989319342</v>
+        <v>-2.268933070268595</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.02141652323845733</v>
+        <v>-0.2627143848517903</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.4415673765519372</v>
+        <v>-0.6578723114156162</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>1.091357816158286</v>
+        <v>0.889873849301047</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 0.08119</t>
+          <t>X ≈ 0.08108</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>110</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-6.605050061355847</v>
+        <v>-7.055566370341474</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-4.609562889892487</v>
+        <v>-4.093288910042837</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-5.916252838199121</v>
+        <v>-6.305208716539362</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-8.521783385265309</v>
+        <v>-7.993506493506501</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-5.410984856924664</v>
+        <v>-5.755482907185687</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-7.847952690713832</v>
+        <v>-7.300879206548579</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.577509649725506</v>
+        <v>-0.997898932137673</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-7.492054611906219</v>
+        <v>-6.918277147066526</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-10.28030949570168</v>
+        <v>-9.682522483476049</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-6.969334753221965</v>
+        <v>-6.869987427927292</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-3.537672275118481</v>
+        <v>-4.346855148190706</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-6.230566850035927</v>
+        <v>-7.01596113809854</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-5.74162679425833</v>
+        <v>-6.502028155571459</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-7.334072962213661</v>
+        <v>-8.071165111737912</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 0.0934</t>
+          <t>X ≈ 0.09327</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>6.742384940339484</v>
+        <v>7.105272790497573</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1.247703701644532</v>
+        <v>0.7144033976494768</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-4.972310401557102</v>
+        <v>-4.487026898357541</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-1.929463898745496</v>
+        <v>-2.434065934065934</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-7.322122383879972</v>
+        <v>-6.769468921171757</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-7.024748354244828</v>
+        <v>-7.458221863891239</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-8.080332499918818</v>
+        <v>-8.48041641465516</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-6.60565357089002</v>
+        <v>-7.023172251961633</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-9.579257086636098</v>
+        <v>-9.944760245713759</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-7.516554523742656</v>
+        <v>-7.883973441913355</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-5.779508109187319</v>
+        <v>-5.203498504834066</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-4.774256170424231</v>
+        <v>-4.183793305930706</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-5.194407023737746</v>
+        <v>-4.578951232494589</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-4.968671373511107</v>
+        <v>-4.329906370479165</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 0.1056</t>
+          <t>X ≈ 0.1055</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>86</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-2.480916030534388</v>
+        <v>-2.510111824887019</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>6.37301415547158</v>
+        <v>6.371827369026924</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>4.815452073042131</v>
+        <v>4.81529868303781</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>3.782886518956076</v>
+        <v>3.782392026578073</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>6.732969058883697</v>
+        <v>6.781514978649469</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>5.867552390844295</v>
+        <v>5.891509799793909</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>3.4572606362293</v>
+        <v>3.505272315219621</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>2.990191992442625</v>
+        <v>3.039439554836342</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>5.254791231268612</v>
+        <v>5.328048341048309</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>4.404872434938753</v>
+        <v>4.504219760233326</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>7.688543369701826</v>
+        <v>7.788451405720501</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>8.885712219731566</v>
+        <v>9.009408840759811</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>7.302770668743776</v>
+        <v>7.451460216521603</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>5.202924923621396</v>
+        <v>5.374923683188058</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 0.1178</t>
+          <t>X ≈ 0.1177</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>56</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-2.480916030534353</v>
+        <v>-2.510111824886984</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.5206735521696118</v>
+        <v>-0.5218603386142675</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>8.013126491646723</v>
+        <v>8.012973101642402</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>9.929065920949434</v>
+        <v>9.928571428571431</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-1.323509346431983</v>
+        <v>-1.274963426666211</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>4.331007540346008</v>
+        <v>4.354964949295621</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.6748686096512699</v>
+        <v>0.7228802886415906</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0.2077999658645311</v>
+        <v>0.2570475282582478</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>5.503960666484616</v>
+        <v>5.577217776264312</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>4.6540418701547</v>
+        <v>4.753389195449273</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>4.449340711894507</v>
+        <v>4.549248747913182</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>6.269433149964122</v>
+        <v>6.393129770992367</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>7.634996582365048</v>
+        <v>7.783686130142875</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>6.075017946877303</v>
+        <v>6.247016706443965</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 0.13</t>
+          <t>X ≈ 0.1298</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>46</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.3070029870559736</v>
+        <v>-0.3361987814086049</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>6.777463093793131</v>
+        <v>6.776276307348475</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>2.034865622081625</v>
+        <v>2.034712232077304</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>10.86074293958303</v>
+        <v>10.86024844720502</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>3.800714256052494</v>
+        <v>3.849260175818266</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>8.445914372644033</v>
+        <v>8.469871781593646</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>4.013377926421413</v>
+        <v>4.061389605411733</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>5.720222326112939</v>
+        <v>5.769469888506656</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>5.659240169590163</v>
+        <v>5.732497279369859</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>13.50497354717334</v>
+        <v>13.60432087246791</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>15.47418543239141</v>
+        <v>15.57409346841008</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>15.50856358474673</v>
+        <v>15.63226020577498</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>12.91449968795506</v>
+        <v>13.06318923573289</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>13.14023533818159</v>
+        <v>13.31223409774825</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 0.1422</t>
+          <t>X ≈ 0.142</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>8.125144575526164</v>
+        <v>5.55440430414518</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>9.544261512765452</v>
+        <v>7.197033670602323</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>15.21009618861648</v>
+        <v>16.48071503712633</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>9.27971527159869</v>
+        <v>6.933179723502299</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>2.680819657897025</v>
+        <v>-0.007682320675328924</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>15.09940580874424</v>
+        <v>13.16832900459521</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>8.954089388871914</v>
+        <v>6.656060012143762</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>11.51732377538821</v>
+        <v>9.416033703373323</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>14.48664464916847</v>
+        <v>15.83067399746242</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>19.69733191344474</v>
+        <v>18.23265186826033</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>19.49263075518455</v>
+        <v>18.02851142072424</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>7.405796786327848</v>
+        <v>5.183452351637527</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>10.01594896331737</v>
+        <v>8.01410087668652</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>10.24168461354383</v>
+        <v>8.263145738701972</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 0.1544</t>
+          <t>X ≈ 0.1542</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>7.519083969465647</v>
+        <v>9.652050337275178</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.1936121621161035</v>
+        <v>2.663467846713921</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>19.79884077736103</v>
+        <v>18.4859460746154</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>14.21478020666371</v>
+        <v>15.91312741312734</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>16.53363351071088</v>
+        <v>18.12658097487812</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>19.68815039748883</v>
+        <v>21.10206919639975</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>22.46058289536555</v>
+        <v>23.7441158098771</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>16.27922853729302</v>
+        <v>17.87287764408828</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>13.36110352362746</v>
+        <v>12.43049962954608</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>12.5111847272976</v>
+        <v>14.30937375143387</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>15.16362642618023</v>
+        <v>16.80793600660044</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>15.19800457853548</v>
+        <v>16.86610274396534</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>17.63499658236501</v>
+        <v>19.1736475201043</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>20.71787508973447</v>
+        <v>22.12539508482228</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 0.1666</t>
+          <t>X ≈ 0.1664</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-3.762967312585666</v>
+        <v>-2.510111824886948</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>2.318154286658228</v>
+        <v>1.169868984694013</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.6407196621992952</v>
+        <v>0.7761309963793366</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>4.61771060959412</v>
+        <v>3.537593984962406</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>9.20762618470355</v>
+        <v>8.311502738747322</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1.812692522030943</v>
+        <v>0.689551415460997</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>6.856187290969828</v>
+        <v>5.892053220972372</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>6.389118647183203</v>
+        <v>5.426220460589057</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>1.19993136245526</v>
+        <v>0.1260899567153473</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>8.042320258433051</v>
+        <v>7.196998218005632</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>7.837619100172901</v>
+        <v>6.992857770469577</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>2.7437921243231</v>
+        <v>1.787866613097634</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>7.451846399214816</v>
+        <v>6.655866581270644</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>7.677582049441348</v>
+        <v>6.904911443286011</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 0.1788</t>
+          <t>X ≈ 0.1786</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>31.5190839694657</v>
+        <v>28.25911894434373</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>21.90789787640185</v>
+        <v>22.82978801303411</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>17.51312649164675</v>
+        <v>14.74374233241173</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>21.64335163523508</v>
+        <v>22.56593406593402</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>21.10506208213948</v>
+        <v>22.07668492498217</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>21.40243611177453</v>
+        <v>22.34947044380108</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>25.31772575250842</v>
+        <v>26.1349682007294</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>36.85065710872163</v>
+        <v>37.20759697880765</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>24.78967495219879</v>
+        <v>25.63216283120932</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>15.93975615586893</v>
+        <v>17.11602655808659</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>23.7350549976088</v>
+        <v>24.60419380285825</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>27.76943314996412</v>
+        <v>28.50851438637698</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>27.34928229665066</v>
+        <v>28.1133564598131</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>27.57501794687719</v>
+        <v>28.36240132182846</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 0.191</t>
+          <t>X ≈ 0.1908</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>25</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>19.51908396946565</v>
+        <v>19.48988817511302</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>5.907897876401798</v>
+        <v>5.906711089957142</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>1.513126491646752</v>
+        <v>1.51297310164243</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>25.6433516352352</v>
+        <v>25.6428571428572</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>25.10506208213942</v>
+        <v>25.15360800190519</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>21.40243611177453</v>
+        <v>21.42639352072415</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>21.31772575250837</v>
+        <v>21.36573743149869</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>12.85065710872163</v>
+        <v>12.89990467111534</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>16.78967495219885</v>
+        <v>16.86293206197855</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>15.93975615586905</v>
+        <v>16.03910348116362</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>15.7350549976088</v>
+        <v>15.83496303362747</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>19.76943314996412</v>
+        <v>19.89312977099237</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>19.34928229665077</v>
+        <v>19.4979718444286</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>19.5750179468773</v>
+        <v>19.74701670644397</v>
       </c>
     </row>
   </sheetData>
@@ -2210,521 +2210,521 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.1568</t>
+          <t>X &gt; -0.1567</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4090</v>
+        <v>4101</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.2020956551992299</v>
+        <v>-0.200923686821838</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.02091733568984466</v>
+        <v>-0.02083571286316754</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.2074294703137198</v>
+        <v>-0.2068712563341961</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.1615264135453387</v>
+        <v>-0.1610835041873742</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.1010857587973675</v>
+        <v>-0.1018664506495242</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.01444196828991551</v>
+        <v>0.0138843944160385</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.04069377789279827</v>
+        <v>0.0395446369514616</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.07121789127837275</v>
+        <v>-0.07209435493773242</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.02777019029409189</v>
+        <v>0.02610790221235249</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.02702449874752233</v>
+        <v>-0.02910601944545022</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.05071588204564392</v>
+        <v>0.04841332602513404</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.04777115111114938</v>
+        <v>-0.0503262368068107</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.0630863173800833</v>
+        <v>-0.06614322139301265</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.1169135934650498</v>
+        <v>-0.1203327205251199</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; -0.1446</t>
+          <t>X &gt; -0.1445</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4064</v>
+        <v>4075</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.3102022704166174</v>
+        <v>-0.3085462671570411</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.09308347786706861</v>
+        <v>-0.09279955354663372</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.2782845512980074</v>
+        <v>-0.2775310589057582</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.2574829253932336</v>
+        <v>-0.2567756600804358</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.1686919075487481</v>
+        <v>-0.1696045348234776</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.005225970740198704</v>
+        <v>-0.005886665413491698</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.02739829563705598</v>
+        <v>-0.02867707119607132</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.1861979281334101</v>
+        <v>-0.1870838120995515</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.06163986716708791</v>
+        <v>-0.0635385262567425</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.08679251669737909</v>
+        <v>-0.08935937738019817</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.05643750300590256</v>
+        <v>-0.05910268486198333</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.1558004948956935</v>
+        <v>-0.1588692478940672</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.1685528817010677</v>
+        <v>-0.1722931212240653</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.1749820531227542</v>
+        <v>-0.17936366165425</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -0.1324</t>
+          <t>X &gt; -0.1323</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4026</v>
+        <v>4037</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.438331232316969</v>
+        <v>-0.4360377508129076</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.2040387258765364</v>
+        <v>-0.2034395645254179</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.3625237436764834</v>
+        <v>-0.361532827211299</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.367550247817384</v>
+        <v>-0.366532528504365</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.2728809166213964</v>
+        <v>-0.2739747959197985</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.08591292144311069</v>
+        <v>-0.08658546567881586</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.03312969009019184</v>
+        <v>-0.03485604031140355</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.2386286055640809</v>
+        <v>-0.2398430409796362</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.1123344747423545</v>
+        <v>-0.1148017331723707</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.005653273411411419</v>
+        <v>-0.009399364666677457</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.07234137866322499</v>
+        <v>-0.07592805548143389</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.1729700277915853</v>
+        <v>-0.1771846632735432</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.1322175791873761</v>
+        <v>-0.1374912561162844</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.06631339937213454</v>
+        <v>-0.07265136390536497</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.1202</t>
+          <t>X &gt; -0.1201</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3988</v>
+        <v>3999</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.3939377750982089</v>
+        <v>-0.3914677570903677</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.2171021235981883</v>
+        <v>-0.2164502164502125</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.4233576293834744</v>
+        <v>-0.4221889931206348</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.429684883023981</v>
+        <v>-0.4284823432990095</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.3039947104550009</v>
+        <v>-0.3054738344221235</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.1681344587960325</v>
+        <v>-0.1688148646015364</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.1140639846631046</v>
+        <v>-0.1160399025003116</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.2419818497160335</v>
+        <v>-0.2436658657136164</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.1139063150187809</v>
+        <v>-0.1170879180414346</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.001880404365984134</v>
+        <v>-0.002865042443737309</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.03673377485760909</v>
+        <v>0.03186458285286164</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.06515331620128961</v>
+        <v>-0.07087922675819414</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.01998318341948391</v>
+        <v>-0.02702815557146465</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.005724279802791443</v>
+        <v>-0.01392352861486046</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.108</t>
+          <t>X &gt; -0.1079</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3945</v>
+        <v>3956</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.4344279052185342</v>
+        <v>-0.4315026034206184</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.1876290379272163</v>
+        <v>-0.1870389100428369</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.2907157732672729</v>
+        <v>-0.2899006064493008</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.2984941296194776</v>
+        <v>-0.297637057848867</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.2161316457310676</v>
+        <v>-0.2183970422309685</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.0820060840261192</v>
+        <v>-0.08319275576425156</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.02640380214749882</v>
+        <v>-0.02916541987653432</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.04936820132645892</v>
+        <v>-0.05213975089374401</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.0301812813127782</v>
+        <v>0.02576972923429821</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.1058741604271134</v>
+        <v>0.0997095417696201</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.09270444036462777</v>
+        <v>0.08654171511270192</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.06535410258636887</v>
+        <v>0.05785943243754588</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.06494372594620756</v>
+        <v>0.0559703281283106</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.1022676300204708</v>
+        <v>0.09180942636302092</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; -0.09577</t>
+          <t>X &gt; -0.09571</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3883</v>
+        <v>3893</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.2478564822797296</v>
+        <v>-0.2315659979540641</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.02856539886651177</v>
+        <v>0.04243452145524884</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.09550216782933063</v>
+        <v>-0.1069039475378659</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.2081767490443269</v>
+        <v>-0.2193001720288521</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.03882280994687903</v>
+        <v>-0.0539778515032836</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.06704675171285146</v>
+        <v>0.05341223387462435</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.1506306368271311</v>
+        <v>0.1349682007294604</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.1862189498118809</v>
+        <v>0.1704868716795858</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.2423498493181881</v>
+        <v>0.224656022984199</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.3843149415649023</v>
+        <v>0.3644819774427503</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.2970724963221372</v>
+        <v>0.2774681670976946</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.3717497522807278</v>
+        <v>0.3501259199012239</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.352371895002932</v>
+        <v>0.3289939296879183</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.3867614441731533</v>
+        <v>0.3614528739240086</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.08356</t>
+          <t>X &gt; -0.08352</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3802</v>
+        <v>3812</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.1873380488829781</v>
+        <v>-0.1963863346908994</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.07674947577255864</v>
+        <v>0.06466088075214316</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.09400699904296772</v>
+        <v>-0.1056510155429962</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.1331436428341064</v>
+        <v>-0.1446886446886495</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.05368890185425101</v>
+        <v>-0.07015541081396748</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.1268455605934378</v>
+        <v>0.1122573950696975</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.1877703836451516</v>
+        <v>0.1968450512944457</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.2077999658644885</v>
+        <v>0.216824524441698</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.2401608991386937</v>
+        <v>0.2467413362777364</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.5346063923377216</v>
+        <v>0.5118498124004631</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.4236226717218088</v>
+        <v>0.4011491410979815</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.499191299280632</v>
+        <v>0.4741470756593813</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.4357929461379584</v>
+        <v>0.408540950119594</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.4924298353570009</v>
+        <v>0.4626515437996304</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.07136</t>
+          <t>X &gt; -0.07132</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3707</v>
+        <v>3718</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.1690880735451117</v>
+        <v>-0.1648960650370768</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.1966851848180582</v>
+        <v>0.1962553258820989</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.1027960473526832</v>
+        <v>-0.1024733987597983</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.06555339570378749</v>
+        <v>-0.06529736358063332</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.02971224360338454</v>
+        <v>0.02347652887061003</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.2072813338472059</v>
+        <v>0.2036345298492108</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.2181027045816037</v>
+        <v>0.2113750153913045</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.1967384445686449</v>
+        <v>0.1899154122539031</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.2584249521988511</v>
+        <v>0.2483739099506082</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.5821705994152069</v>
+        <v>0.5678514661178937</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.5275078277974785</v>
+        <v>0.5132753152721889</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.6041594912960235</v>
+        <v>0.5866781580891356</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.5499295458416498</v>
+        <v>0.5294319143398099</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.5752877067909239</v>
+        <v>0.5517504342545578</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.05915</t>
+          <t>X &gt; -0.05913</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3583</v>
+        <v>3594</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.3674566312017546</v>
+        <v>-0.3603198692697873</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.04481422373726218</v>
+        <v>-0.06998147386081399</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.1463058956653995</v>
+        <v>-0.1156696960261456</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.2236119049819436</v>
+        <v>-0.2483144284921153</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.2178777842302679</v>
+        <v>-0.2226763635488282</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.1504171755450656</v>
+        <v>0.1208379651685902</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.1923775630933307</v>
+        <v>0.1587354865139687</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.1585423135140474</v>
+        <v>0.1250297405983929</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.1687162008053136</v>
+        <v>0.1436435683709902</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.5608880209372913</v>
+        <v>0.5306241928677693</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.5671799278932426</v>
+        <v>0.5488913071887751</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.6453048375512864</v>
+        <v>0.622829437288253</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.6037465823650052</v>
+        <v>0.5772486177247913</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.5663659792523461</v>
+        <v>0.536109639109462</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.04695</t>
+          <t>X &gt; -0.04694</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3414</v>
+        <v>3425</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.5696233547246052</v>
+        <v>-0.5590343641997393</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.1694273568454889</v>
+        <v>0.1741156923457439</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.09271292441161449</v>
+        <v>-0.08725999859063904</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.326274532989153</v>
+        <v>-0.3495648915351737</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.4105674825698671</v>
+        <v>-0.4149051176283081</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.1557170150518843</v>
+        <v>-0.2137347965695255</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.06779883055572355</v>
+        <v>0.004010477006268331</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.02609570521286031</v>
+        <v>-0.02424935455560728</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.06899639121611045</v>
+        <v>0.02629262207189242</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.4347824870568147</v>
+        <v>0.3984967133689352</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.4222074705382681</v>
+        <v>0.3985569659495312</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.5610022366151739</v>
+        <v>0.53158906483538</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.5674374943081091</v>
+        <v>0.5324143429691119</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.3998568455298539</v>
+        <v>0.3601553925753009</v>
       </c>
     </row>
     <row r="16">
@@ -2734,1037 +2734,1037 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3234</v>
+        <v>3244</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.8481372258516657</v>
+        <v>-0.8188449122178554</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.07053047490789055</v>
+        <v>-0.04837965135320133</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.2020399695122848</v>
+        <v>-0.1793345906652277</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.2875978098943222</v>
+        <v>-0.2789649562502703</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.2850088398463697</v>
+        <v>-0.258953574449464</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.1250160782316314</v>
+        <v>-0.1541423585490307</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.05391828567713475</v>
+        <v>0.01761666748143398</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.08761449621664497</v>
+        <v>-0.140144620320271</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.008102139496116934</v>
+        <v>-0.05388864042441099</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.394357761798581</v>
+        <v>0.3545686690871648</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.5160250315908783</v>
+        <v>0.4893068413908708</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.567949837232355</v>
+        <v>0.5474735787557634</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.5981231003601479</v>
+        <v>0.5703909507459457</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.4086604948055097</v>
+        <v>0.3746369283921211</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.02254</t>
+          <t>X &gt; -0.02256</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2971</v>
+        <v>2979</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.8366207285209342</v>
+        <v>-0.8194523002803535</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.08068889768344434</v>
+        <v>-0.04104510562221009</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.5916418092262887</v>
+        <v>-0.5506784896473178</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.6628941673169066</v>
+        <v>-0.6373037150517078</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.4960124645361788</v>
+        <v>-0.4380782200190154</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.5344342710327155</v>
+        <v>-0.515927069483773</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.2497692105540921</v>
+        <v>-0.2229911830601878</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.06032710357263227</v>
+        <v>-0.05145393337979698</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.1700024671559888</v>
+        <v>-0.1555181225232971</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.2086637188942007</v>
+        <v>0.228301736782484</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.2918808214151198</v>
+        <v>0.3260733992765878</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.6143709232570913</v>
+        <v>0.6526064566683161</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.6844101566776288</v>
+        <v>0.7127369450996781</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.08797654667529287</v>
+        <v>0.1082117383338073</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.01034</t>
+          <t>X &gt; -0.01036</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2642</v>
+        <v>2650</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.9531906438878011</v>
+        <v>-0.8911359212725216</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.3562530669944124</v>
+        <v>-0.3079781755795636</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.9194895898934234</v>
+        <v>-0.9075242608292768</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-1.091265201306946</v>
+        <v>-1.096683000376935</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.6858023950217529</v>
+        <v>-0.6985790267523981</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.9169296866399606</v>
+        <v>-0.9536969770134078</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.699639290904237</v>
+        <v>-0.7126939410503326</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.4287990846318479</v>
+        <v>-0.4620862791109062</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.3557727244161839</v>
+        <v>-0.3859367163019911</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.4401340848183466</v>
+        <v>0.4116525007714102</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.5592515949622907</v>
+        <v>0.5468785690724189</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>1.144622257377137</v>
+        <v>1.132948775517249</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.124537688251166</v>
+        <v>1.098877163176184</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.6151390672406123</v>
+        <v>0.5772053856891972</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; 0.001866</t>
+          <t>X &gt; 0.001828</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2218</v>
+        <v>2226</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.8404665923320991</v>
+        <v>-0.8277430496514526</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.06520124718833387</v>
+        <v>0.08085830719235076</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.6441768791397351</v>
+        <v>-0.647781276444654</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.233052859146873</v>
+        <v>-1.212488769092545</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.8724660077481943</v>
+        <v>-0.8032653134586596</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.024530180360294</v>
+        <v>-0.9797160929326409</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.7946337980534324</v>
+        <v>-0.7259067733530671</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.5180479272495973</v>
+        <v>-0.4729614564677647</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.5094703469464434</v>
+        <v>-0.4650104357752696</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.375399720225424</v>
+        <v>0.4182589169227739</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.4212323951774621</v>
+        <v>0.4387366185331345</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.291955672486644</v>
+        <v>1.305528692825256</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.303315645005831</v>
+        <v>1.31468343472504</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1.014152302152269</v>
+        <v>0.9797211089596303</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; 0.01407</t>
+          <t>X &gt; 0.01402</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1815</v>
+        <v>1822</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.5028940525123673</v>
+        <v>-0.4553173043390402</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.08111311260917375</v>
+        <v>-0.03627136618318616</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.190170211649921</v>
+        <v>-1.168321467748662</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.554450562567055</v>
+        <v>-1.558021013015534</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.543289566212202</v>
+        <v>-1.498422733550321</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-1.905256195917772</v>
+        <v>-1.884254119231947</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.495461060678444</v>
+        <v>-1.45094753008199</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-1.193298935234417</v>
+        <v>-1.093509159839655</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-1.059692832298126</v>
+        <v>-1.020712284893015</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.009638783624957625</v>
+        <v>0.02154036371021562</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.4219014478014316</v>
+        <v>0.421132078632958</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>1.368552092695396</v>
+        <v>1.35745468866525</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1.388929873743223</v>
+        <v>1.401374698435134</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.7651005915053517</v>
+        <v>0.7722636877830951</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 0.02627</t>
+          <t>X &gt; 0.02621</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1474</v>
+        <v>1482</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.09012591804480508</v>
+        <v>0.1179205201264892</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.1704147911514795</v>
+        <v>0.1885721823374737</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.9009465800717606</v>
+        <v>-0.9107785852671313</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.311993425657953</v>
+        <v>-1.253229226913447</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.917941977400474</v>
+        <v>-1.809954751131215</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-2.161839936939948</v>
+        <v>-2.076980298439153</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.975914301618829</v>
+        <v>-1.867730854601177</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.292779968409626</v>
+        <v>-1.186465099464947</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.8433649936373016</v>
+        <v>-0.7511030257407469</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.4438211965194014</v>
+        <v>0.5168362746858293</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.9553939806596432</v>
+        <v>0.9874596598083087</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1.464348404201409</v>
+        <v>1.517961080034205</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.518773822074444</v>
+        <v>1.595137836331375</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.9698619088853917</v>
+        <v>1.034466099156461</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.03848</t>
+          <t>X &gt; 0.0384</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1207</v>
+        <v>1211</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.1637120686391995</v>
+        <v>0.1691956771740166</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.8665755623522244</v>
+        <v>0.8572061394621144</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.602575987692056</v>
+        <v>-0.6472250816771066</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.4723508441036941</v>
+        <v>-0.5173410404624263</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.671797421992778</v>
+        <v>-1.667201246649697</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-1.374423392357691</v>
+        <v>-1.394415727830769</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.376489123524692</v>
+        <v>-1.289919050747393</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.6038883458238331</v>
+        <v>-0.5171060638144667</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.243382899040817</v>
+        <v>-1.132113355032189</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.2672995801866094</v>
+        <v>0.3561967924765241</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>1.350949037343895</v>
+        <v>1.390702092256703</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>1.550890103606505</v>
+        <v>1.614021595930438</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>1.213520707246737</v>
+        <v>1.301440052521031</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.9900966544166039</v>
+        <v>1.05502661560989</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.05068</t>
+          <t>X &gt; 0.0506</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>985</v>
+        <v>989</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.0999636495819658</v>
+        <v>-0.03286207766757343</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.4165098318222817</v>
+        <v>0.4062055287842625</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.18089579812019</v>
+        <v>-0.1897569286912102</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.5572320810304774</v>
+        <v>0.4456882854253905</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.3863259624400897</v>
+        <v>-0.4480097938480725</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.2915861779924356</v>
+        <v>-0.2763365096095214</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.173662292071171</v>
+        <v>-0.235880364254605</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.2711231674855554</v>
+        <v>0.4105214557462844</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.09381035681837346</v>
+        <v>-0.1320123262924398</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>1.444827149783798</v>
+        <v>1.571964957402194</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>2.516780885933677</v>
+        <v>2.480059090250322</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>2.957250408847365</v>
+        <v>2.942674765936758</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>2.63862239817356</v>
+        <v>2.749741308533693</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>2.762835205760489</v>
+        <v>2.796561701388299</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.06289</t>
+          <t>X &gt; 0.06279</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.844052601837042</v>
+        <v>0.8148568074844107</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>2.369629369500942</v>
+        <v>2.368442583056286</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.849387470316799</v>
+        <v>1.849234080312478</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>2.606965186050701</v>
+        <v>2.606470693672698</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.8139704886639194</v>
+        <v>0.8625164084296912</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.9858740038698883</v>
+        <v>1.009831412819501</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1.653986731178385</v>
+        <v>1.701998410168706</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>1.31238860182075</v>
+        <v>1.361636164214467</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>1.376876959727078</v>
+        <v>1.450134069506774</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>2.859354145818735</v>
+        <v>2.884774748415765</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>4.489771978740869</v>
+        <v>4.437221502887205</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>4.649936294618207</v>
+        <v>4.620858754681201</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>4.481357768348822</v>
+        <v>4.476641856975597</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>4.455521091531331</v>
+        <v>4.474745690132742</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.07509</t>
+          <t>X &gt; 0.07498</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1.173827359823342</v>
+        <v>1.144631565470711</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>2.828582168781296</v>
+        <v>2.82739538233664</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2.744852774694991</v>
+        <v>2.744699384690669</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>3.808203890289576</v>
+        <v>3.807709397911573</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1.870225379184546</v>
+        <v>1.918771298950318</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>2.945204385491486</v>
+        <v>2.969161794441099</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>3.793619998231534</v>
+        <v>3.841631677221855</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>2.548946377772943</v>
+        <v>2.598193940166659</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>2.487964221250166</v>
+        <v>2.561221331029863</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>3.752840268018517</v>
+        <v>3.759165689561705</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>6.040350947764558</v>
+        <v>6.043361167375529</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>5.7632026203691</v>
+        <v>5.790485914071688</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>5.654578246806473</v>
+        <v>5.706369978176596</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>5.257260937531449</v>
+        <v>5.333330858854481</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.08729</t>
+          <t>X &gt; 0.08717</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>2.782241864202497</v>
+        <v>2.836980107570795</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>4.36654449294317</v>
+        <v>4.255679195022829</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>4.535682882624222</v>
+        <v>4.612410249860098</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>6.35763734952085</v>
+        <v>6.243232377378718</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>3.375738773868775</v>
+        <v>3.502576106970885</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>5.176872202000105</v>
+        <v>5.088682451305758</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>4.904191917921899</v>
+        <v>4.840409101292309</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>4.625093198947198</v>
+        <v>4.562193601696954</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>5.128020816860506</v>
+        <v>5.088072774924136</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>5.969831343838919</v>
+        <v>5.952799541201088</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>8.020769283323091</v>
+        <v>8.187683483908899</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>8.243117360490437</v>
+        <v>8.433467482061779</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>8.010936431989052</v>
+        <v>8.225926816285956</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>7.860732232591538</v>
+        <v>8.099737156725332</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 0.0995</t>
+          <t>X &gt; 0.09937</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>429</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1.831438281819963</v>
+        <v>1.802242487467332</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>5.115357083861028</v>
+        <v>5.114170297416372</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>6.818487797008082</v>
+        <v>6.818334407003761</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>8.347314339197844</v>
+        <v>8.346819846819841</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>5.944222921300295</v>
+        <v>5.992768841066066</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>8.106398815737236</v>
+        <v>8.130356224686849</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>8.021688456471068</v>
+        <v>8.069700135461389</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>7.321519579584105</v>
+        <v>7.370767141977822</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>8.659138821662722</v>
+        <v>8.732395931442419</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>9.207821423934263</v>
+        <v>9.307168749228836</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>11.33412259667639</v>
+        <v>11.43403063269507</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>11.36850074903172</v>
+        <v>11.49219737005996</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>11.18145012881855</v>
+        <v>11.33013967659638</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>10.94098531284461</v>
+        <v>11.11298407241127</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 0.1117</t>
+          <t>X &gt; 0.1116</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>343</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>2.912669975296559</v>
+        <v>2.883474180943928</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>4.800026156285199</v>
+        <v>4.798839369840543</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>7.320706666573891</v>
+        <v>7.320553276569569</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>9.49174813669287</v>
+        <v>9.491253644314867</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>5.746461499049069</v>
+        <v>5.795007418814841</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>8.667742234223518</v>
+        <v>8.691699643173131</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>9.166122253966094</v>
+        <v>9.214133932956415</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>8.407508420674979</v>
+        <v>8.456755983068696</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>9.512707022169693</v>
+        <v>9.585964131949389</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>10.41205936286607</v>
+        <v>10.51140668816065</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>12.2481745311365</v>
+        <v>12.34808256715517</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>11.99100749398745</v>
+        <v>12.11470411501569</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>12.15394701968279</v>
+        <v>12.30263656746062</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>12.37968266990932</v>
+        <v>12.55168142947598</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 0.1239</t>
+          <t>X &gt; 0.1237</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>287</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>3.965077000824536</v>
+        <v>3.935881206471905</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>5.838211465251987</v>
+        <v>5.837024678807332</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>7.185600359242606</v>
+        <v>7.185446969238285</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>9.406417837325733</v>
+        <v>9.40592334494773</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>7.125968005484395</v>
+        <v>7.174513925250167</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>9.513934369614248</v>
+        <v>9.537891778563861</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>10.82295223334459</v>
+        <v>10.87096391233491</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>10.00745153380873</v>
+        <v>10.05669909620244</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>10.29490143303508</v>
+        <v>10.36815854281478</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>11.53557497120001</v>
+        <v>11.63492229649458</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>13.76989820318371</v>
+        <v>13.86980623920239</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>13.10741224404078</v>
+        <v>13.23110886506903</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>13.0356934464765</v>
+        <v>13.18438299425433</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>13.60986115245216</v>
+        <v>13.78185991201882</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 0.1361</t>
+          <t>X &gt; 0.1359</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>241</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>4.780494757847386</v>
+        <v>4.751298963494754</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>5.65893522080016</v>
+        <v>5.657748434355504</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>8.168728151397815</v>
+        <v>8.168574761393494</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>9.128828813658373</v>
+        <v>9.12833432128037</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>7.760663741890482</v>
+        <v>7.809209661656254</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>9.717788808869969</v>
+        <v>9.741746217819582</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>12.12270500562039</v>
+        <v>12.17071668461071</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>10.82576084316145</v>
+        <v>10.87500840555517</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>11.17971644597478</v>
+        <v>11.25297355575447</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>11.15967316831713</v>
+        <v>11.2590204936117</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>13.44459856607352</v>
+        <v>13.5445066020922</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>12.64910119975665</v>
+        <v>12.77279782078489</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>13.05882586511544</v>
+        <v>13.20751541289327</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>13.69949927467807</v>
+        <v>13.87149803424473</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 0.1483</t>
+          <t>X &gt; 0.1481</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>4.249853200234874</v>
+        <v>4.632745317970155</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>5.042513261017206</v>
+        <v>5.430520613766689</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>7.05158803010832</v>
+        <v>6.941544530213889</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>9.104890096773602</v>
+        <v>9.452380952380942</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>8.566600543677907</v>
+        <v>8.963131811429022</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>8.863974573312994</v>
+        <v>9.23591733024795</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>12.62541806020067</v>
+        <v>12.98478505054631</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>10.71604172410624</v>
+        <v>11.09038086159153</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>10.65505956758346</v>
+        <v>10.57721777626426</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>9.805140771253605</v>
+        <v>10.22957967163975</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>12.4850549976088</v>
+        <v>12.88258208124653</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>13.48097161150258</v>
+        <v>13.89312977099237</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>13.54158998895841</v>
+        <v>13.97416232061902</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>14.24809486995418</v>
+        <v>14.69939765882486</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 0.1605</t>
+          <t>X &gt; 0.1603</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>173</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>3.58844813131536</v>
+        <v>3.559252336962729</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>6.023504812818004</v>
+        <v>6.022318026373348</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>4.472664063901121</v>
+        <v>4.472510673896799</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>8.07109729997503</v>
+        <v>8.070602807597027</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>6.954773064798403</v>
+        <v>7.003318984564174</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>6.674112412352571</v>
+        <v>6.698069821302184</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>10.63564482765287</v>
+        <v>10.68365650664319</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>9.590541501785218</v>
+        <v>9.639789064178935</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>10.10759402734335</v>
+        <v>10.18085113712305</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>9.257675231013494</v>
+        <v>9.357022556308067</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>11.94314748315793</v>
+        <v>12.0430555191766</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>13.1335949996751</v>
+        <v>13.25729162070335</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>12.7134441463617</v>
+        <v>12.86213369413952</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>12.93917979658823</v>
+        <v>13.11117855615489</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 0.1727</t>
+          <t>X &gt; 0.1725</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>5.728039193346248</v>
+        <v>5.267665952890788</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>7.101927727148087</v>
+        <v>7.388192571438644</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>5.960887685676624</v>
+        <v>5.512973101642459</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>9.076187456130668</v>
+        <v>9.346560846560848</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>6.299091932885716</v>
+        <v>6.6350894833867</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>8.089003275953644</v>
+        <v>8.389356483687109</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>11.73563620026957</v>
+        <v>12.03240409816534</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>10.5222988997664</v>
+        <v>10.82583059704127</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>12.70012271339287</v>
+        <v>13.0110802101267</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>9.611397946913769</v>
+        <v>9.965029407089489</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>13.13804007223567</v>
+        <v>13.46459266325711</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>16.15749285145666</v>
+        <v>16.48572236358496</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>14.24480468471042</v>
+        <v>14.60908295553966</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>14.47054033493695</v>
+        <v>14.85812781755502</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 0.1849</t>
+          <t>X &gt; 0.1847</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>109</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.1873380488829781</v>
+        <v>-0.2165338432356094</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>3.706063014016493</v>
+        <v>3.704876227571837</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>3.311291629261454</v>
+        <v>3.311138239257133</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>6.193810350831477</v>
+        <v>6.193315858453474</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>2.903227219754122</v>
+        <v>2.951773139519894</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>5.035463634710311</v>
+        <v>5.059421043659924</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>8.620478046086347</v>
+        <v>8.668489725076668</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>4.483684631657404</v>
+        <v>4.532932194051121</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>9.927289631097935</v>
+        <v>10.00054674087763</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>8.159939642107531</v>
+        <v>8.259286967402105</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>10.70753206182899</v>
+        <v>10.80744009784766</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>13.49420379216595</v>
+        <v>13.6179004131942</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>11.23919055353146</v>
+        <v>11.38788010130929</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>11.46492620375799</v>
+        <v>11.63692496332465</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 0.1971</t>
+          <t>X &gt; 0.1969</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-6.052344601962922</v>
+        <v>-6.081540396315553</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>3.050755019258958</v>
+        <v>3.049568232814302</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>3.846459824980116</v>
+        <v>3.846306434975794</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.4052563971399081</v>
+        <v>0.4047619047619051</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-3.704461727384363</v>
+        <v>-3.655915807618591</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.1643408736793006</v>
+        <v>0.1882982826289137</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>4.841535276317892</v>
+        <v>4.889546955308212</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>1.993514251578766</v>
+        <v>2.042761813972483</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>7.884913047436946</v>
+        <v>7.958170157216642</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>5.844518060630897</v>
+        <v>5.94386538592547</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>9.211245473799281</v>
+        <v>9.311153509817956</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>11.62657600710698</v>
+        <v>11.75027262813523</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>8.825472772841195</v>
+        <v>8.974162320619023</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>9.051208423067727</v>
+        <v>9.22320718263439</v>
       </c>
     </row>
   </sheetData>
@@ -3904,521 +3904,521 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.1568</t>
+          <t>X &lt; -0.1567</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>9.423845874227553</v>
+        <v>9.394650079874921</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>1.860278828782775</v>
+        <v>1.859092042338119</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>9.798840777361072</v>
+        <v>9.79868738735675</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>7.548113539997047</v>
+        <v>7.547619047619044</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>4.628871605948973</v>
+        <v>4.677417525714745</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.1643408736793006</v>
+        <v>0.1882982826289137</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.0796305144131324</v>
+        <v>0.1276421934034531</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>5.564942823007335</v>
+        <v>5.614190385401052</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>1.93253209505599</v>
+        <v>2.005789204835686</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>4.6540418701547</v>
+        <v>4.753389195449273</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.8779121404659378</v>
+        <v>0.9778201764846131</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>5.674195054726027</v>
+        <v>5.797891675754272</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>6.444520391888808</v>
+        <v>6.593209939666636</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>9.051208423067727</v>
+        <v>9.22320718263439</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; -0.1446</t>
+          <t>X &lt; -0.1445</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>110</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>11.15544760582928</v>
+        <v>11.12625181147665</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>4.089716058219999</v>
+        <v>4.088529271775343</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>10.05858103710133</v>
+        <v>10.05842764709701</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>9.279715271598775</v>
+        <v>9.279220779220772</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>6.014152991230361</v>
+        <v>6.062698910996133</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.8569815663199876</v>
+        <v>0.8809389752696006</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>2.590453025235639</v>
+        <v>2.63846470422596</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>8.48702074508526</v>
+        <v>8.536268307478977</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>4.789674952198851</v>
+        <v>4.862932061978547</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>5.757937974050805</v>
+        <v>5.857285299345378</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>4.644145906699713</v>
+        <v>4.744053942718388</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>8.314887695418669</v>
+        <v>8.438584316446914</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>8.803827751196167</v>
+        <v>8.952517298973994</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>9.029563401422699</v>
+        <v>9.201562160989361</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -0.1324</t>
+          <t>X &lt; -0.1323</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>148</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>11.70827315865484</v>
+        <v>11.67907736430221</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>6.043033011536949</v>
+        <v>6.041846225092293</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>9.702315680835973</v>
+        <v>9.702162290831652</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>9.832540824424335</v>
+        <v>9.832046332046332</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>7.267224244301609</v>
+        <v>7.315770164067381</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>2.834868544206969</v>
+        <v>2.858825953156583</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>2.074482509265124</v>
+        <v>2.122494188255445</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>7.688494946559466</v>
+        <v>7.737742508953183</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>4.924810087333981</v>
+        <v>4.998067197113677</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>2.047864263977097</v>
+        <v>2.14721158927167</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>3.870190132743929</v>
+        <v>3.970098168762604</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>6.607270987801961</v>
+        <v>6.730967608830206</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>5.511444458812875</v>
+        <v>5.660134006590702</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>3.710153082012376</v>
+        <v>3.882151841579038</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.1202</t>
+          <t>X &lt; -0.1201</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>186</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>8.271772141508663</v>
+        <v>8.242576347156032</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>5.047682822638379</v>
+        <v>5.046496036193723</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>8.95398670670054</v>
+        <v>8.953833316696219</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>9.084211850288902</v>
+        <v>9.083717357910899</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>6.395384662784608</v>
+        <v>6.443930582550379</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>4.004586649408949</v>
+        <v>4.028544058358563</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>3.382241881540629</v>
+        <v>3.43025356053095</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>6.140979689366787</v>
+        <v>6.190227251760504</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>3.929459898435411</v>
+        <v>4.002717008215107</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>1.466637876299103</v>
+        <v>1.565985201593676</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.7243023094367587</v>
+        <v>0.8242103454554339</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>2.909218096200682</v>
+        <v>3.032914717228927</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>1.951432834285129</v>
+        <v>2.100122382062956</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>1.639534075909509</v>
+        <v>1.811532835476171</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.108</t>
+          <t>X &lt; -0.1079</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>229</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>7.344411480382675</v>
+        <v>7.315215686030044</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>3.549819273781736</v>
+        <v>3.54863248733708</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>4.901772779856394</v>
+        <v>4.901619389852073</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>5.031997923444756</v>
+        <v>5.031503431066753</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>3.620345924934213</v>
+        <v>3.668891844699985</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1.734313841032176</v>
+        <v>1.758271249981789</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>1.21292225905858</v>
+        <v>1.2609339380489</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>1.619216060686689</v>
+        <v>1.668463623080406</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.6848714587490647</v>
+        <v>0.7581285685287611</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.6017285602882154</v>
+        <v>-0.5023812349936421</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.3697484958409873</v>
+        <v>-0.2698404598223121</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.1013108792217636</v>
+        <v>0.2250075002500083</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.1178412486157754</v>
+        <v>0.266530796393603</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.5297855465725405</v>
+        <v>-0.3577867870058782</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; -0.09577</t>
+          <t>X &lt; -0.09571</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>3.189187062249154</v>
+        <v>2.969340229907537</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.1402120892339198</v>
+        <v>-0.3261656223715974</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1.183229584430286</v>
+        <v>1.334890909861635</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>2.688025174754038</v>
+        <v>2.834637964774942</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.4315225632391062</v>
+        <v>0.6330600566997404</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.6456738538612043</v>
+        <v>-0.4640174381799582</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-1.417669436495068</v>
+        <v>-1.209605034254736</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-1.884738080281807</v>
+        <v>-1.675437794638079</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-2.28936284848843</v>
+        <v>-2.054876157199537</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-4.170209479869833</v>
+        <v>-3.906101998288491</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-3.000340191394635</v>
+        <v>-2.740379432125948</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-3.996889874090854</v>
+        <v>-3.709609955035035</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-3.729755504036568</v>
+        <v>-3.419836374749543</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-4.191305077177731</v>
+        <v>-3.855723019583493</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.08356</t>
+          <t>X &lt; -0.08352</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1.820159238282848</v>
+        <v>1.913480668410607</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.5974784676842049</v>
+        <v>-0.4739859609811745</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.8894705776682841</v>
+        <v>1.00895165392128</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1.288512925557718</v>
+        <v>1.406932209881269</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.4814061681609516</v>
+        <v>0.6495865541840402</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-1.102940232311489</v>
+        <v>-0.9543035302141902</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-1.456467795878737</v>
+        <v>-1.551152648930263</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-1.654719235364396</v>
+        <v>-1.748888894568303</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-1.715701391887173</v>
+        <v>-1.7858615037051</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-4.716157822625632</v>
+        <v>-4.486365687737241</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-3.576772959380449</v>
+        <v>-3.350023561546784</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-4.34884641992835</v>
+        <v>-4.09614636841782</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-3.693728456037462</v>
+        <v>-3.418918236000408</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-4.274444418714154</v>
+        <v>-3.974162918220969</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.07136</t>
+          <t>X &lt; -0.07132</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>467</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>1.266407309936731</v>
+        <v>1.2372115155841</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-1.415442594690262</v>
+        <v>-1.416629381134918</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.7593791683063031</v>
+        <v>0.7592257783019818</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.4613387872694048</v>
+        <v>0.4608442948914018</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.2910835281389268</v>
+        <v>-0.242537608373155</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-1.492638834692272</v>
+        <v>-1.468681425742659</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-1.36321643164581</v>
+        <v>-1.31520475265549</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-1.187886788494652</v>
+        <v>-1.138639226100935</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-1.463001707330065</v>
+        <v>-1.389744597550369</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-4.02598260216098</v>
+        <v>-3.926635276866406</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-3.588285473483282</v>
+        <v>-3.488377437464607</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-4.196305608065849</v>
+        <v>-4.072608987037604</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-3.75992541212873</v>
+        <v>-3.611235864350903</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-3.962455286527465</v>
+        <v>-3.790456526960803</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.05915</t>
+          <t>X &lt; -0.05913</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>591</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>2.172214257113701</v>
+        <v>2.127324937338983</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.3918234263172238</v>
+        <v>0.54414785218313</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.8430757302254577</v>
+        <v>0.6563120561112612</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>1.311710349279139</v>
+        <v>1.460732353649718</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1.281035009381405</v>
+        <v>1.308751340859693</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.7904572892406989</v>
+        <v>-0.6107059733736619</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.8751676485068671</v>
+        <v>-0.6713620625991226</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.6654173413629678</v>
+        <v>-0.4626585666586891</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.5571947601530951</v>
+        <v>-0.4073382082917263</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-2.929956196076866</v>
+        <v>-2.751437059376975</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-2.965452616604395</v>
+        <v>-2.86554458058572</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-3.43868867744704</v>
+        <v>-3.314992056418795</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-3.182020579829825</v>
+        <v>-3.033331032051997</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-2.956284929603292</v>
+        <v>-2.78428617003663</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.04695</t>
+          <t>X &lt; -0.04694</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>760</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>2.519083969465655</v>
+        <v>2.46371016464181</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.671049492019236</v>
+        <v>-0.6901475487862925</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.3815475442783551</v>
+        <v>0.3559050388152372</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1.432825319445662</v>
+        <v>1.532909498878084</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.815588397928927</v>
+        <v>1.829000672062286</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.7971729538797945</v>
+        <v>1.054665772033047</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.07701108959690117</v>
+        <v>0.2086693686714653</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.1138150034584768</v>
+        <v>0.3389610276028918</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.05283284693570067</v>
+        <v>0.2435094898000685</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-1.586559633604693</v>
+        <v>-1.42738797744353</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.528102897128036</v>
+        <v>-1.428194861109361</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-2.15161948161483</v>
+        <v>-2.027922860586585</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-2.177033492822972</v>
+        <v>-2.028343945045144</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-1.424982053122747</v>
+        <v>-1.252983293556085</v>
       </c>
     </row>
     <row r="16">
@@ -4428,1037 +4428,1037 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>2.885715212823783</v>
+        <v>2.775300437269472</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.3180997892604793</v>
+        <v>0.2407491449254522</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.6672178837828113</v>
+        <v>0.5869688733126495</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.9625005714053572</v>
+        <v>0.9282694050135945</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.9561259119266765</v>
+        <v>0.8618532450341831</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.5088190904979371</v>
+        <v>0.6060975376374671</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.001423183661849237</v>
+        <v>0.1226084674394912</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.4889549810620508</v>
+        <v>0.6671004383111097</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.3215898458158719</v>
+        <v>0.4773388416395647</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.060243844131001</v>
+        <v>-0.9237809302892401</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-1.477710959838014</v>
+        <v>-1.387966902678258</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.656098764929489</v>
+        <v>-1.590398390537921</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.757100682072689</v>
+        <v>-1.666746540268591</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.105833116952539</v>
+        <v>-0.9926219758090156</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.02254</t>
+          <t>X &lt; -0.02256</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1203</v>
+        <v>1206</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>2.034411227129276</v>
+        <v>1.990301057028788</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.2575250512154028</v>
+        <v>0.1593948224096877</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1.436904453535753</v>
+        <v>1.334608114028917</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.613500888966477</v>
+        <v>1.547068538398008</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.204647144380111</v>
+        <v>1.057819397446089</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1.382502556957256</v>
+        <v>1.330604916265017</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.7624472820179236</v>
+        <v>0.6919141449586377</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.2953786382311847</v>
+        <v>0.2718054975616297</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.6500240793808914</v>
+        <v>0.6114845847246215</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.2830202364834591</v>
+        <v>-0.3317574459887567</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.4877213947436516</v>
+        <v>-0.572659170183627</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.284598437733294</v>
+        <v>-1.380502069803661</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.455372732443216</v>
+        <v>-1.526903777462003</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.01724571080077197</v>
+        <v>-0.03407782091927913</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.01034</t>
+          <t>X &lt; -0.01036</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1532</v>
+        <v>1535</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.620646469465647</v>
+        <v>1.510640444892523</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.6605020430684831</v>
+        <v>0.5759717903462658</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1.56781399164678</v>
+        <v>1.544101506311719</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1.864850006570649</v>
+        <v>1.868538076709278</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>1.167643568449748</v>
+        <v>1.18473640657448</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1.632051245499255</v>
+        <v>1.688560944474958</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>1.322947684623244</v>
+        <v>1.339763405524664</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.8558790408365056</v>
+        <v>0.9103010323888938</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.7948968843137294</v>
+        <v>0.8447266003400529</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.5772151235043737</v>
+        <v>-0.5282354908598563</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.7819162817645662</v>
+        <v>-0.76139113303919</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.791924552385744</v>
+        <v>-1.774622672004377</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.755156345646938</v>
+        <v>-1.713754539936282</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.8766791810600907</v>
+        <v>-0.8132438798753157</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; 0.001866</t>
+          <t>X &lt; 0.001828</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1956</v>
+        <v>1959</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.9339667421465876</v>
+        <v>0.9180242848133702</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.03804806954412498</v>
+        <v>-0.05570638084019208</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.7172081242998374</v>
+        <v>0.71866126822448</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1.386077515786447</v>
+        <v>1.356417325691062</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.9784022251425171</v>
+        <v>0.8954779206043995</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.202129520052509</v>
+        <v>1.145763119097303</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.9925723782752414</v>
+        <v>0.9099897204101879</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.678877967617332</v>
+        <v>0.6250955108100058</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.7201452998471183</v>
+        <v>0.6674127137097088</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.2831477296115779</v>
+        <v>-0.3317574459887567</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.3344746547429338</v>
+        <v>-0.354639412855704</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-1.322591389913171</v>
+        <v>-1.338894706315131</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.333744288216366</v>
+        <v>-1.348966931081662</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.005759149237278</v>
+        <v>-0.9696754834488956</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; 0.01407</t>
+          <t>X &lt; 0.01402</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2359</v>
+        <v>2363</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.3707949960816137</v>
+        <v>0.3343888072242649</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.09217513760216178</v>
+        <v>0.05757497533432598</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.9042469990463644</v>
+        <v>0.8859187400748283</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1.184806795979647</v>
+        <v>1.184365781710916</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1.177850909900769</v>
+        <v>1.140117276778739</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.498964477566233</v>
+        <v>1.478692128906353</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1.226239094312689</v>
+        <v>1.188522241625265</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.9947249053317933</v>
+        <v>0.9151009564678105</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.9337427488090171</v>
+        <v>0.9017834133298948</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.1261968338350883</v>
+        <v>0.1016298858952922</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.2056229684928965</v>
+        <v>-0.2056117761781024</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.9339566805443553</v>
+        <v>-0.9271662120943134</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.9491492421369045</v>
+        <v>-0.9605729948269541</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.4690685304436499</v>
+        <v>-0.47642806714898</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 0.02627</t>
+          <t>X &lt; 0.02621</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2700</v>
+        <v>2703</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.06304965917960459</v>
+        <v>-0.07827689489435841</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.06699134073259927</v>
+        <v>-0.07707667717621547</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.4817264177642571</v>
+        <v>0.4871809129910218</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.7061749907414239</v>
+        <v>0.674187773155694</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.038518644061817</v>
+        <v>0.9795667039701144</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.208649129526016</v>
+        <v>1.162284335921491</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1.144584798013362</v>
+        <v>1.085294627070645</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.772196709017706</v>
+        <v>0.7138581594874367</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.5631760624875213</v>
+        <v>0.5128582067348262</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.1387042438349297</v>
+        <v>-0.179588798112384</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.4174246470988194</v>
+        <v>-0.4370251407997259</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.6955798081995184</v>
+        <v>-0.7279423177322215</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.7247917774233628</v>
+        <v>-0.7697796348614006</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.4249820531227471</v>
+        <v>-0.4631201784987411</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.03848</t>
+          <t>X &lt; 0.0384</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2967</v>
+        <v>2974</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.07916930564352498</v>
+        <v>-0.08130110461897999</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.3286612633831325</v>
+        <v>-0.3244446889373123</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.2358155672770295</v>
+        <v>0.2533416108551947</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.1826925901779788</v>
+        <v>0.200497893527384</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.6718296569796749</v>
+        <v>0.668190636836492</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.5841319394999758</v>
+        <v>0.5907127695504357</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.6189711244370102</v>
+        <v>0.582107777020326</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.3052025632670805</v>
+        <v>0.2690321878938704</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.599712001710472</v>
+        <v>0.5527608635898247</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.01443717521891585</v>
+        <v>-0.05088980291970557</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.4549079528795801</v>
+        <v>-0.4713856395334233</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.5364967691733469</v>
+        <v>-0.5625153902979605</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.3986111984621985</v>
+        <v>-0.4348012648151567</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.3076918610095092</v>
+        <v>-0.3350276782232129</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.05068</t>
+          <t>X &lt; 0.0506</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3189</v>
+        <v>3196</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.0190839694656475</v>
+        <v>-0.001542177021605085</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.1064816171899281</v>
+        <v>-0.1032639723869835</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.04721029402326593</v>
+        <v>0.0499235225966288</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.1808585618245999</v>
+        <v>-0.1462882096069933</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.111319904417293</v>
+        <v>0.1302070658677792</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.1129212447948831</v>
+        <v>0.1080414607990576</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.1079574369166281</v>
+        <v>0.1268988426757005</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.02876663070837537</v>
+        <v>-0.07198789603018696</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.1154894885397084</v>
+        <v>0.126912068226595</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.3584894581660976</v>
+        <v>-0.3983965188364351</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.6885038996343127</v>
+        <v>-0.6789475634341073</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.8247379562721662</v>
+        <v>-0.8223173834791737</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.7259528130671526</v>
+        <v>-0.7622721343015186</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.764900522862483</v>
+        <v>-0.7773888004396952</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.06289</t>
+          <t>X &lt; 0.06279</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3379</v>
+        <v>3388</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.2095295998558839</v>
+        <v>-0.2019671615526732</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.5364809964220285</v>
+        <v>-0.5344653806310689</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.4431899192150865</v>
+        <v>-0.4417194549918406</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.6217797494710808</v>
+        <v>-0.6196502144118412</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.1991316567855321</v>
+        <v>-0.2099480769879207</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.2105624111205842</v>
+        <v>-0.2155381636103684</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.3383026162859579</v>
+        <v>-0.3485482827870285</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.257235294470803</v>
+        <v>-0.2680387584662682</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.2428501808585182</v>
+        <v>-0.2593785775734716</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.5901078299382263</v>
+        <v>-0.5953304811005893</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.9722188048749416</v>
+        <v>-0.9600826756028482</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-1.010217840866986</v>
+        <v>-1.003625391249521</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.9702443305682138</v>
+        <v>-0.9694226672268158</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.9647867290623893</v>
+        <v>-0.9696302829303534</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.07509</t>
+          <t>X &lt; 0.07498</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3532</v>
+        <v>3542</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.2235796874192317</v>
+        <v>-0.2175661146197569</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.4934569076794659</v>
+        <v>-0.49171322067874</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.5060717014644496</v>
+        <v>-0.5044769405753868</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.6994893701305784</v>
+        <v>-0.6972329472329548</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.3469153189904901</v>
+        <v>-0.3546995171035121</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.5144895734472783</v>
+        <v>-0.5172684511068368</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.6404427042468654</v>
+        <v>-0.6472239660780943</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.4136912090618026</v>
+        <v>-0.4214031079150971</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.3743521971224126</v>
+        <v>-0.3865745633386197</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.6020990477509116</v>
+        <v>-0.6027464906356457</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.017420249915951</v>
+        <v>-1.016941056640505</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.9674089552990282</v>
+        <v>-0.9714300484207286</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.9473494610622737</v>
+        <v>-0.9558808228026194</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.8757181799630729</v>
+        <v>-0.8887822771811642</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.08729</t>
+          <t>X &lt; 0.08717</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3642</v>
+        <v>3652</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.4152525558421516</v>
+        <v>-0.4227994101530186</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.6164589927826398</v>
+        <v>-0.5998391283834508</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.6680944226702223</v>
+        <v>-0.6786730900037412</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.9338663275249885</v>
+        <v>-0.9164000936256613</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.4988820427578418</v>
+        <v>-0.5169738063438913</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.7345501895953319</v>
+        <v>-0.7211474628824135</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.6674756725395952</v>
+        <v>-0.6577662580339734</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.6263165754889073</v>
+        <v>-0.6167711079989218</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.6723486288266471</v>
+        <v>-0.6661901693586145</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.7941988633301307</v>
+        <v>-0.7913122737598499</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.093477238330848</v>
+        <v>-1.117157349409453</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-1.126285840156626</v>
+        <v>-1.153394585876825</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-1.092112158468694</v>
+        <v>-1.122887723050248</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-1.070781064654881</v>
+        <v>-1.105119109547324</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 0.0995</t>
+          <t>X &lt; 0.09937</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3745</v>
+        <v>3756</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.2190746255316895</v>
+        <v>-0.2150733531438149</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.5653520570557333</v>
+        <v>-0.5635649185354126</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.7861280344448005</v>
+        <v>-0.7838147932341002</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.9611756617022706</v>
+        <v>-0.9583112055231027</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.686094018020377</v>
+        <v>-0.6896854907906587</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.9071828597149434</v>
+        <v>-0.907294045694556</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.8709736078327879</v>
+        <v>-0.87396493363552</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.7905052479832548</v>
+        <v>-0.7938752331908745</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.9169917144678124</v>
+        <v>-0.9227632318262948</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.9788888161235363</v>
+        <v>-0.9874922635172894</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.222255568026199</v>
+        <v>-1.230213875124853</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.226563647473832</v>
+        <v>-1.237258733531313</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-1.204908840562318</v>
+        <v>-1.218557301166342</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-1.177986058463212</v>
+        <v>-1.194410343609341</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 0.1117</t>
+          <t>X &lt; 0.1116</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3831</v>
+        <v>3842</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.2696777370900207</v>
+        <v>-0.2662726549777688</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.4100828678084341</v>
+        <v>-0.4088052566956648</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.6607412855525965</v>
+        <v>-0.6588410691335582</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.8549560971262267</v>
+        <v>-0.8524699599466032</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.5199379178605597</v>
+        <v>-0.5228396740231105</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.7554174959358093</v>
+        <v>-0.7554246610940325</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.773988682092984</v>
+        <v>-0.7761175957811233</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.7057671810881203</v>
+        <v>-0.7082034369927612</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.7786253606270108</v>
+        <v>-0.7830258272858188</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.8581577945873349</v>
+        <v>-0.8646926706825084</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-1.022378492219062</v>
+        <v>-1.028496004083841</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.9996772074582623</v>
+        <v>-1.008014870006591</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-1.01397448831797</v>
+        <v>-1.024536612506147</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-1.034744517231346</v>
+        <v>-1.047361221718504</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 0.1239</t>
+          <t>X &lt; 0.1237</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3887</v>
+        <v>3898</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.3014288510471701</v>
+        <v>-0.2984012649278966</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.4116712438854364</v>
+        <v>-0.4104244599149638</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.5361295370859054</v>
+        <v>-0.5346094002761888</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.6999893963276023</v>
+        <v>-0.6979821611346679</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.5314882258687703</v>
+        <v>-0.5336200503087625</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.6822878933602539</v>
+        <v>-0.6821574265364845</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.7531525217597377</v>
+        <v>-0.7546210832260272</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.6926257065878971</v>
+        <v>-0.6943576239666243</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.68822843937361</v>
+        <v>-0.6917694496791569</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.7788251856884472</v>
+        <v>-0.7840641251921525</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.9436082414657463</v>
+        <v>-0.9484258410200468</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.8950050089456241</v>
+        <v>-0.9017420238794287</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.8894008309213035</v>
+        <v>-0.8980271296673763</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.93231418587294</v>
+        <v>-0.9425676958136577</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 0.1361</t>
+          <t>X &lt; 0.1359</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3933</v>
+        <v>3944</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.30149383083846</v>
+        <v>-0.2988406598629751</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.3278435684650987</v>
+        <v>-0.3268581719235257</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.5061432852294914</v>
+        <v>-0.5047260134017932</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.5651190723479189</v>
+        <v>-0.5635161500108481</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.4809348737205141</v>
+        <v>-0.4826176494987777</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.5757420156042983</v>
+        <v>-0.5756307707738273</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.6975026738875698</v>
+        <v>-0.6985500906476076</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.6177358844238441</v>
+        <v>-0.6190826706568089</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.6140833007214184</v>
+        <v>-0.6169362591154055</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.6119329475092172</v>
+        <v>-0.6164183020177987</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.7517336202773777</v>
+        <v>-0.7558654436970755</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.7032479173802244</v>
+        <v>-0.7089989669701353</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.7279927414784169</v>
+        <v>-0.7352347461925035</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.7677229633693869</v>
+        <v>-0.7763098655642082</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 0.1483</t>
+          <t>X &lt; 0.1481</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3966</v>
+        <v>3975</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.2316071589585817</v>
+        <v>-0.253341513954183</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.2459482774443345</v>
+        <v>-0.2683578842088821</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.3757344588183926</v>
+        <v>-0.372626496952627</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.4834089281451455</v>
+        <v>-0.505198064169214</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.4546863455335028</v>
+        <v>-0.4789221185767119</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.445575966735781</v>
+        <v>-0.4686604586883547</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.617335913738799</v>
+        <v>-0.6412942108920774</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.5169159023559189</v>
+        <v>-0.5409393379276111</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.4885924867334097</v>
+        <v>-0.4888267319913098</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.4431153806549375</v>
+        <v>-0.4695670390676554</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.5834131303831427</v>
+        <v>-0.6094814108169686</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.6358087855197496</v>
+        <v>-0.6630683683086147</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.6386178798050466</v>
+        <v>-0.6670180952092792</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.6761166976008184</v>
+        <v>-0.7058134822353423</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 0.1605</t>
+          <t>X &lt; 0.1603</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4001</v>
+        <v>4012</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.1640251486210502</v>
+        <v>-0.1622857379304676</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.2421145831047866</v>
+        <v>-0.2414002420507941</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.1997349241059538</v>
+        <v>-0.199182006485799</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.3551524784522115</v>
+        <v>-0.3541592668892548</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.3064092395563165</v>
+        <v>-0.307720025948548</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.2698013539276332</v>
+        <v>-0.2701238922111742</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.4158071816233715</v>
+        <v>-0.416795536901418</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.3702063801728102</v>
+        <v>-0.3713745722893407</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.367589151645376</v>
+        <v>-0.3698287047628028</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.3299067654793291</v>
+        <v>-0.3334064789958049</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.445764183210386</v>
+        <v>-0.4489722092118811</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.4973667501108281</v>
+        <v>-0.5014890630883428</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.4788036603707795</v>
+        <v>-0.4840864660623581</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.4889660571217576</v>
+        <v>-0.4952564740147167</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 0.1727</t>
+          <t>X &lt; 0.1725</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4040</v>
+        <v>4050</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.1986559762535691</v>
+        <v>-0.1842442393590531</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.2174723111598809</v>
+        <v>-0.228197821908914</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.2039803955415707</v>
+        <v>-0.1900557089953097</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.3072656487154717</v>
+        <v>-0.3177339901477865</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.2147699751586458</v>
+        <v>-0.2270276226328463</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.2497378012689495</v>
+        <v>-0.26113728262726</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.3457286581662089</v>
+        <v>-0.3577035347325221</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.3050522338389285</v>
+        <v>-0.3170578535394881</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.3524758512622128</v>
+        <v>-0.3651813782187432</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.2491657036760131</v>
+        <v>-0.2628205444901042</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.3658601643996136</v>
+        <v>-0.3791993152498989</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.4660938168839692</v>
+        <v>-0.4800192911991417</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.4022643502188714</v>
+        <v>-0.4171108512021746</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.4101305679742353</v>
+        <v>-0.4258227997289268</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 0.1849</t>
+          <t>X &lt; 0.1847</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4065</v>
+        <v>4076</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.004211763736904572</v>
+        <v>-0.003386464163092739</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.0818004311772853</v>
+        <v>-0.08154722706827755</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.09531315506568205</v>
+        <v>-0.09505234489534331</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.1725992850102571</v>
+        <v>-0.1721208307111439</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.08394135428666516</v>
+        <v>-0.08507008867005794</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.1168371511766111</v>
+        <v>-0.1171912001377464</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.1881681571183478</v>
+        <v>-0.1890017308819125</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.07687912316242773</v>
+        <v>-0.07804731320606351</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.1980400355161365</v>
+        <v>-0.1995526231476461</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.1497007131405894</v>
+        <v>-0.1520729894246671</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.217747362273208</v>
+        <v>-0.2199523868187114</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.2925289842871663</v>
+        <v>-0.2951978405819276</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.2316326074319193</v>
+        <v>-0.2351652661920127</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.2380201835040552</v>
+        <v>-0.2421883965982872</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 0.1971</t>
+          <t>X &lt; 0.1969</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4090</v>
+        <v>4101</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.1147456804088591</v>
+        <v>0.1150704794397086</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.04529568771324932</v>
+        <v>-0.04514886627915615</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.08550798774849255</v>
+        <v>-0.0852759255948996</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.01518495013070975</v>
+        <v>-0.01513361364978749</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.0696876005585807</v>
+        <v>0.06844985105364287</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.01444196828991551</v>
+        <v>0.0138843944160385</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.05693863606864369</v>
+        <v>-0.05782634649547447</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.002024296221627253</v>
+        <v>0.000951664054227308</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.09432993180602978</v>
+        <v>-0.09566511288750945</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.05145048800008567</v>
+        <v>-0.05346655537723422</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.1203078169526535</v>
+        <v>-0.1221519761191061</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.1699607894298225</v>
+        <v>-0.1721882889637598</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.1119741198733593</v>
+        <v>-0.1148999254398149</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.1169135934650498</v>
+        <v>-0.1203327205251199</v>
       </c>
     </row>
   </sheetData>
